--- a/快乐羊毛系统/功能测试需要的文件2026.03.17/最终版测试用例/快乐羊毛系统完整测试用例2026.03.17（付仕菊）-V3.0完善版v2.xlsx
+++ b/快乐羊毛系统/功能测试需要的文件2026.03.17/最终版测试用例/快乐羊毛系统完整测试用例2026.03.17（付仕菊）-V3.0完善版v2.xlsx
@@ -1199,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J582"/>
+  <dimension ref="A1:J580"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="6.5" customWidth="1" style="3" min="1" max="3"/>
@@ -3101,22 +3101,31 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>用户已选择10元面额并发起微信支付</t>
+          <t>1. 用户已进入支付确认页
+2. 通用券订单已创建</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>1. 在微信支付过程中断开网络。
-2. 恢复网络后查看订单状态</t>
+          <t>1. 点击微信支付，唤起支付弹窗。
+2. 在输入支付密码前关闭网络（开启飞行模式）。
+3. 尝试完成支付。
+4. 恢复网络后查看订单状态</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>1. 支付流程中断，提示网络异常。
-2. 恢复网络后订单状态为"待支付"或"已取消"，不会出现扣款但无卡密的情况</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr"/>
+          <t>1. 支付失败，微信提示网络异常。
+2. 不产生扣款。
+3. 恢复网络后订单状态为"待支付"或"已取消"。
+4. 不产生无主卡密</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>确保断网不会产生资金异常</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="24" customHeight="1" s="3">
       <c r="A46" s="4" t="inlineStr"/>
@@ -9750,24 +9759,31 @@
       </c>
       <c r="G204" s="4" t="inlineStr">
         <is>
-          <t>用户首次使用小程序</t>
+          <t>1. 用户首次打开小程序
+2. 准备拒绝授权</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>1. 点击"微信一键登录"。
-2. 在手机号授权弹窗中点击"拒绝"。
-3. 观察页面状态</t>
+          <t>1. 触发登录流程。
+2. 弹出手机号授权弹窗。
+3. 点击"拒绝"。
+4. 观察后续处理</t>
         </is>
       </c>
       <c r="I204" s="4" t="inlineStr">
         <is>
-          <t>1. 登录按钮正常响应。
-2. 弹出手机号授权弹窗。
-3. 停留在登录页面，提示"需要获取手机号才能完成登录"，可再次点击登录按钮</t>
-        </is>
-      </c>
-      <c r="J204" s="4" t="inlineStr"/>
+          <t>1. 提示"需要授权手机号才能使用完整功能"。
+2. 提供重新授权入口/按钮。
+3. 不出现白屏或崩溃。
+4. 部分功能可浏览（如免费资料区），下单等核心功能需登录</t>
+        </is>
+      </c>
+      <c r="J204" s="4" t="inlineStr">
+        <is>
+          <t>必须有优雅的拒绝授权降级方案</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="36" customHeight="1" s="3">
       <c r="A205" s="4" t="inlineStr"/>
@@ -20041,6 +20057,7 @@
       </c>
       <c r="J453" s="4" t="inlineStr"/>
     </row>
+    <row r="454"/>
     <row r="455">
       <c r="A455" s="7" t="inlineStr">
         <is>
@@ -20527,45 +20544,45 @@
       <c r="B466" s="8" t="inlineStr"/>
       <c r="C466" s="8" t="inlineStr">
         <is>
-          <t>wlyc-003</t>
+          <t>wlyc-004</t>
         </is>
       </c>
       <c r="D466" s="8" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E466" s="8" t="n"/>
       <c r="F466" s="8" t="inlineStr">
         <is>
-          <t>验证支付过程中网络断开的处理</t>
+          <t>验证支付过程中WiFi切换到4G的影响</t>
         </is>
       </c>
       <c r="G466" s="8" t="inlineStr">
         <is>
-          <t>1. 用户已进入支付确认页
-2. 通用券订单已创建</t>
+          <t>1. 设备连接WiFi
+2. 用户正在进行餐饮扫码支付</t>
         </is>
       </c>
       <c r="H466" s="8" t="inlineStr">
         <is>
-          <t>1. 点击微信支付，唤起支付弹窗。
-2. 在输入支付密码前关闭网络（开启飞行模式）。
-3. 尝试完成支付。
-4. 恢复网络后查看订单状态</t>
+          <t>1. 用户扫码进入支付确认页。
+2. 点击支付唤起微信支付弹窗。
+3. 输入支付密码过程中关闭WiFi（自动切换到4G）。
+4. 完成支付</t>
         </is>
       </c>
       <c r="I466" s="8" t="inlineStr">
         <is>
-          <t>1. 支付失败，微信提示网络异常。
-2. 不产生扣款。
-3. 恢复网络后订单状态为"待支付"或"已取消"。
-4. 不产生无主卡密</t>
+          <t>1. 网络切换不影响支付流程。
+2. 支付正常完成或提示网络变化需重试。
+3. 不会出现重复扣款。
+4. 订单状态正确</t>
         </is>
       </c>
       <c r="J466" s="8" t="inlineStr">
         <is>
-          <t>确保断网不会产生资金异常</t>
+          <t>模拟真实场景：用户在店内WiFi不稳定</t>
         </is>
       </c>
     </row>
@@ -20574,7 +20591,7 @@
       <c r="B467" s="8" t="inlineStr"/>
       <c r="C467" s="8" t="inlineStr">
         <is>
-          <t>wlyc-004</t>
+          <t>wlyc-005</t>
         </is>
       </c>
       <c r="D467" s="8" t="inlineStr">
@@ -20585,34 +20602,34 @@
       <c r="E467" s="8" t="n"/>
       <c r="F467" s="8" t="inlineStr">
         <is>
-          <t>验证支付过程中WiFi切换到4G的影响</t>
+          <t>验证断网环境下凭证图片上传的处理</t>
         </is>
       </c>
       <c r="G467" s="8" t="inlineStr">
         <is>
-          <t>1. 设备连接WiFi
-2. 用户正在进行餐饮扫码支付</t>
+          <t>1. 用户在人工辅助模式下单页
+2. 已输入消费金额</t>
         </is>
       </c>
       <c r="H467" s="8" t="inlineStr">
         <is>
-          <t>1. 用户扫码进入支付确认页。
-2. 点击支付唤起微信支付弹窗。
-3. 输入支付密码过程中关闭WiFi（自动切换到4G）。
-4. 完成支付</t>
+          <t>1. 选择一张凭证图片开始上传。
+2. 上传过程中断开网络。
+3. 观察上传结果提示。
+4. 恢复网络后重新上传</t>
         </is>
       </c>
       <c r="I467" s="8" t="inlineStr">
         <is>
-          <t>1. 网络切换不影响支付流程。
-2. 支付正常完成或提示网络变化需重试。
-3. 不会出现重复扣款。
-4. 订单状态正确</t>
+          <t>1. 上传失败，提示"网络异常，上传失败"。
+2. 已上传成功的图片不受影响（如有多张）。
+3. 恢复网络后可重新选择上传。
+4. 不产生损坏的图片数据</t>
         </is>
       </c>
       <c r="J467" s="8" t="inlineStr">
         <is>
-          <t>模拟真实场景：用户在店内WiFi不稳定</t>
+          <t>验证图片上传的断点续传或失败回滚</t>
         </is>
       </c>
     </row>
@@ -20621,7 +20638,7 @@
       <c r="B468" s="8" t="inlineStr"/>
       <c r="C468" s="8" t="inlineStr">
         <is>
-          <t>wlyc-005</t>
+          <t>wlyc-006</t>
         </is>
       </c>
       <c r="D468" s="8" t="inlineStr">
@@ -20632,34 +20649,34 @@
       <c r="E468" s="8" t="n"/>
       <c r="F468" s="8" t="inlineStr">
         <is>
-          <t>验证断网环境下凭证图片上传的处理</t>
+          <t>验证弱网下电影选座界面的加载与操作</t>
         </is>
       </c>
       <c r="G468" s="8" t="inlineStr">
         <is>
-          <t>1. 用户在人工辅助模式下单页
-2. 已输入消费金额</t>
+          <t>1. 弱网环境（模拟2G/3G）
+2. 用户已选择影片和影院</t>
         </is>
       </c>
       <c r="H468" s="8" t="inlineStr">
         <is>
-          <t>1. 选择一张凭证图片开始上传。
-2. 上传过程中断开网络。
-3. 观察上传结果提示。
-4. 恢复网络后重新上传</t>
+          <t>1. 进入选座页面。
+2. 观察座位图加载过程。
+3. 尝试选择座位。
+4. 尝试提交订单</t>
         </is>
       </c>
       <c r="I468" s="8" t="inlineStr">
         <is>
-          <t>1. 上传失败，提示"网络异常，上传失败"。
-2. 已上传成功的图片不受影响（如有多张）。
-3. 恢复网络后可重新选择上传。
-4. 不产生损坏的图片数据</t>
+          <t>1. 座位图有loading提示，不白屏。
+2. 座位图加载完成后可正常操作。
+3. 选座操作响应正常（可接受轻微延迟）。
+4. 提交订单正常</t>
         </is>
       </c>
       <c r="J468" s="8" t="inlineStr">
         <is>
-          <t>验证图片上传的断点续传或失败回滚</t>
+          <t>座位图数据量较大，弱网影响明显</t>
         </is>
       </c>
     </row>
@@ -20668,7 +20685,7 @@
       <c r="B469" s="8" t="inlineStr"/>
       <c r="C469" s="8" t="inlineStr">
         <is>
-          <t>wlyc-006</t>
+          <t>wlyc-007</t>
         </is>
       </c>
       <c r="D469" s="8" t="inlineStr">
@@ -20679,63 +20696,16 @@
       <c r="E469" s="8" t="n"/>
       <c r="F469" s="8" t="inlineStr">
         <is>
-          <t>验证弱网下电影选座界面的加载与操作</t>
+          <t>验证断网恢复后数据不丢失</t>
         </is>
       </c>
       <c r="G469" s="8" t="inlineStr">
-        <is>
-          <t>1. 弱网环境（模拟2G/3G）
-2. 用户已选择影片和影院</t>
-        </is>
-      </c>
-      <c r="H469" s="8" t="inlineStr">
-        <is>
-          <t>1. 进入选座页面。
-2. 观察座位图加载过程。
-3. 尝试选择座位。
-4. 尝试提交订单</t>
-        </is>
-      </c>
-      <c r="I469" s="8" t="inlineStr">
-        <is>
-          <t>1. 座位图有loading提示，不白屏。
-2. 座位图加载完成后可正常操作。
-3. 选座操作响应正常（可接受轻微延迟）。
-4. 提交订单正常</t>
-        </is>
-      </c>
-      <c r="J469" s="8" t="inlineStr">
-        <is>
-          <t>座位图数据量较大，弱网影响明显</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" s="8" t="inlineStr"/>
-      <c r="B470" s="8" t="inlineStr"/>
-      <c r="C470" s="8" t="inlineStr">
-        <is>
-          <t>wlyc-007</t>
-        </is>
-      </c>
-      <c r="D470" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E470" s="8" t="n"/>
-      <c r="F470" s="8" t="inlineStr">
-        <is>
-          <t>验证断网恢复后数据不丢失</t>
-        </is>
-      </c>
-      <c r="G470" s="8" t="inlineStr">
         <is>
           <t>1. 用户已登录小程序
 2. 正在浏览订单列表</t>
         </is>
       </c>
-      <c r="H470" s="8" t="inlineStr">
+      <c r="H469" s="8" t="inlineStr">
         <is>
           <t>1. 断开网络。
 2. 尝试下拉刷新订单列表。
@@ -20744,7 +20714,7 @@
 5. 再次下拉刷新</t>
         </is>
       </c>
-      <c r="I470" s="8" t="inlineStr">
+      <c r="I469" s="8" t="inlineStr">
         <is>
           <t>1. 断网时提示"网络异常，请检查网络"。
 2. 已加载的数据仍可查看（缓存）。
@@ -20752,45 +20722,45 @@
 4. 操作状态不丢失</t>
         </is>
       </c>
-      <c r="J470" s="8" t="inlineStr">
+      <c r="J469" s="8" t="inlineStr">
         <is>
           <t>验证离线缓存和网络恢复机制</t>
         </is>
       </c>
     </row>
-    <row r="471">
-      <c r="A471" s="8" t="inlineStr"/>
-      <c r="B471" s="8" t="inlineStr"/>
-      <c r="C471" s="8" t="inlineStr">
+    <row r="470">
+      <c r="A470" s="8" t="inlineStr"/>
+      <c r="B470" s="8" t="inlineStr"/>
+      <c r="C470" s="8" t="inlineStr">
         <is>
           <t>wlyc-008</t>
         </is>
       </c>
-      <c r="D471" s="8" t="inlineStr">
+      <c r="D470" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E471" s="8" t="n"/>
-      <c r="F471" s="8" t="inlineStr">
+      <c r="E470" s="8" t="n"/>
+      <c r="F470" s="8" t="inlineStr">
         <is>
           <t>验证弱网下外卖红包中间页跳转超时处理</t>
         </is>
       </c>
-      <c r="G471" s="8" t="inlineStr">
+      <c r="G470" s="8" t="inlineStr">
         <is>
           <t>1. 弱网环境（极慢网络，下行50kbps）
 2. 用户在外卖区</t>
         </is>
       </c>
-      <c r="H471" s="8" t="inlineStr">
+      <c r="H470" s="8" t="inlineStr">
         <is>
           <t>1. 点击美团红包Icon。
 2. 观察中间页加载。
 3. 等待超过5秒</t>
         </is>
       </c>
-      <c r="I471" s="8" t="inlineStr">
+      <c r="I470" s="8" t="inlineStr">
         <is>
           <t>1. 中间页显示loading动画。
 2. 5秒后显示"加载失败，请重试"。
@@ -20798,51 +20768,51 @@
 4. 点击重试可重新加载</t>
         </is>
       </c>
-      <c r="J471" s="8" t="inlineStr">
+      <c r="J470" s="8" t="inlineStr">
         <is>
           <t>验证5秒超时机制</t>
         </is>
       </c>
     </row>
-    <row r="472">
-      <c r="A472" s="9" t="inlineStr">
+    <row r="471">
+      <c r="A471" s="9" t="inlineStr">
         <is>
           <t>用户端</t>
         </is>
       </c>
-      <c r="B472" s="9" t="inlineStr">
+      <c r="B471" s="9" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="C472" s="9" t="inlineStr">
+      <c r="C471" s="9" t="inlineStr">
         <is>
           <t>yh-yc-001</t>
         </is>
       </c>
-      <c r="D472" s="9" t="inlineStr">
+      <c r="D471" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E472" s="9" t="inlineStr">
+      <c r="E471" s="9" t="inlineStr">
         <is>
           <t>用户操作异常
 (用户端)</t>
         </is>
       </c>
-      <c r="F472" s="9" t="inlineStr">
+      <c r="F471" s="9" t="inlineStr">
         <is>
           <t>验证支付过程中杀掉小程序进程后的订单状态</t>
         </is>
       </c>
-      <c r="G472" s="9" t="inlineStr">
+      <c r="G471" s="9" t="inlineStr">
         <is>
           <t>1. 用户已创建通用券订单
 2. 已唤起微信支付弹窗</t>
         </is>
       </c>
-      <c r="H472" s="9" t="inlineStr">
+      <c r="H471" s="9" t="inlineStr">
         <is>
           <t>1. 在微信支付弹窗显示时，上滑杀掉小程序进程。
 2. 重新打开小程序。
@@ -20850,7 +20820,7 @@
 4. 如果微信已扣款，检查订单状态是否正确更新</t>
         </is>
       </c>
-      <c r="I472" s="9" t="inlineStr">
+      <c r="I471" s="9" t="inlineStr">
         <is>
           <t>1. 重新打开后不出现白屏/崩溃。
 2. 如果支付未完成，订单状态为"待支付"。
@@ -20858,9 +20828,53 @@
 4. 不出现"已扣款但订单未更新"的情况</t>
         </is>
       </c>
-      <c r="J472" s="9" t="inlineStr">
+      <c r="J471" s="9" t="inlineStr">
         <is>
           <t>核心场景：防止资金状态不一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="8" t="inlineStr"/>
+      <c r="B472" s="8" t="inlineStr"/>
+      <c r="C472" s="8" t="inlineStr">
+        <is>
+          <t>yh-yc-002</t>
+        </is>
+      </c>
+      <c r="D472" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E472" s="8" t="n"/>
+      <c r="F472" s="8" t="inlineStr">
+        <is>
+          <t>验证支付过程中来电话/微信视频通话的影响</t>
+        </is>
+      </c>
+      <c r="G472" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户正在进行微信支付（支付弹窗已唤起）</t>
+        </is>
+      </c>
+      <c r="H472" s="8" t="inlineStr">
+        <is>
+          <t>1. 此时接到电话或微信视频通话。
+2. 接听后挂断。
+3. 回到小程序查看支付状态</t>
+        </is>
+      </c>
+      <c r="I472" s="8" t="inlineStr">
+        <is>
+          <t>1. 来电不导致支付流程崩溃。
+2. 挂断后可继续完成支付或重新发起。
+3. 订单状态正确</t>
+        </is>
+      </c>
+      <c r="J472" s="8" t="inlineStr">
+        <is>
+          <t>模拟真实使用场景</t>
         </is>
       </c>
     </row>
@@ -20869,7 +20883,7 @@
       <c r="B473" s="8" t="inlineStr"/>
       <c r="C473" s="8" t="inlineStr">
         <is>
-          <t>yh-yc-002</t>
+          <t>yh-yc-003</t>
         </is>
       </c>
       <c r="D473" s="8" t="inlineStr">
@@ -20880,31 +20894,31 @@
       <c r="E473" s="8" t="n"/>
       <c r="F473" s="8" t="inlineStr">
         <is>
-          <t>验证支付过程中来电话/微信视频通话的影响</t>
+          <t>验证连续快速切换底部Tab页不产生异常</t>
         </is>
       </c>
       <c r="G473" s="8" t="inlineStr">
         <is>
-          <t>1. 用户正在进行微信支付（支付弹窗已唤起）</t>
+          <t>用户已登录小程序</t>
         </is>
       </c>
       <c r="H473" s="8" t="inlineStr">
         <is>
-          <t>1. 此时接到电话或微信视频通话。
-2. 接听后挂断。
-3. 回到小程序查看支付状态</t>
+          <t>1. 快速连续点击底部Tab（首页-&gt;外卖-&gt;餐饮-&gt;个人中心），每个Tab停留不超过0.5秒。
+2. 连续切换10次以上。
+3. 最终停留在个人中心页</t>
         </is>
       </c>
       <c r="I473" s="8" t="inlineStr">
         <is>
-          <t>1. 来电不导致支付流程崩溃。
-2. 挂断后可继续完成支付或重新发起。
-3. 订单状态正确</t>
+          <t>1. 不出现白屏、卡顿或崩溃。
+2. 不出现数据错乱（如个人中心显示外卖页数据）。
+3. 最终页面数据正确加载</t>
         </is>
       </c>
       <c r="J473" s="8" t="inlineStr">
         <is>
-          <t>模拟真实使用场景</t>
+          <t>防止竞态条件导致的数据混乱</t>
         </is>
       </c>
     </row>
@@ -20913,7 +20927,7 @@
       <c r="B474" s="8" t="inlineStr"/>
       <c r="C474" s="8" t="inlineStr">
         <is>
-          <t>yh-yc-003</t>
+          <t>yh-yc-004</t>
         </is>
       </c>
       <c r="D474" s="8" t="inlineStr">
@@ -20924,59 +20938,15 @@
       <c r="E474" s="8" t="n"/>
       <c r="F474" s="8" t="inlineStr">
         <is>
-          <t>验证连续快速切换底部Tab页不产生异常</t>
+          <t>验证快速返回+前进操作数据不重复加载</t>
         </is>
       </c>
       <c r="G474" s="8" t="inlineStr">
         <is>
-          <t>用户已登录小程序</t>
+          <t>用户在免费资料区已加载2页数据</t>
         </is>
       </c>
       <c r="H474" s="8" t="inlineStr">
-        <is>
-          <t>1. 快速连续点击底部Tab（首页-&gt;外卖-&gt;餐饮-&gt;个人中心），每个Tab停留不超过0.5秒。
-2. 连续切换10次以上。
-3. 最终停留在个人中心页</t>
-        </is>
-      </c>
-      <c r="I474" s="8" t="inlineStr">
-        <is>
-          <t>1. 不出现白屏、卡顿或崩溃。
-2. 不出现数据错乱（如个人中心显示外卖页数据）。
-3. 最终页面数据正确加载</t>
-        </is>
-      </c>
-      <c r="J474" s="8" t="inlineStr">
-        <is>
-          <t>防止竞态条件导致的数据混乱</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" s="8" t="inlineStr"/>
-      <c r="B475" s="8" t="inlineStr"/>
-      <c r="C475" s="8" t="inlineStr">
-        <is>
-          <t>yh-yc-004</t>
-        </is>
-      </c>
-      <c r="D475" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E475" s="8" t="n"/>
-      <c r="F475" s="8" t="inlineStr">
-        <is>
-          <t>验证快速返回+前进操作数据不重复加载</t>
-        </is>
-      </c>
-      <c r="G475" s="8" t="inlineStr">
-        <is>
-          <t>用户在免费资料区已加载2页数据</t>
-        </is>
-      </c>
-      <c r="H475" s="8" t="inlineStr">
         <is>
           <t>1. 点击某条资料进入详情页。
 2. 立即点击返回。
@@ -20985,7 +20955,7 @@
 5. 检查列表数据</t>
         </is>
       </c>
-      <c r="I475" s="8" t="inlineStr">
+      <c r="I474" s="8" t="inlineStr">
         <is>
           <t>1. 列表保持原滑动位置。
 2. 数据不重复加载/不出现重复条目。
@@ -20993,37 +20963,37 @@
 4. 页面响应流畅</t>
         </is>
       </c>
-      <c r="J475" s="8" t="inlineStr">
+      <c r="J474" s="8" t="inlineStr">
         <is>
           <t>验证列表缓存和位置恢复</t>
         </is>
       </c>
     </row>
-    <row r="476">
-      <c r="A476" s="8" t="inlineStr"/>
-      <c r="B476" s="8" t="inlineStr"/>
-      <c r="C476" s="8" t="inlineStr">
+    <row r="475">
+      <c r="A475" s="8" t="inlineStr"/>
+      <c r="B475" s="8" t="inlineStr"/>
+      <c r="C475" s="8" t="inlineStr">
         <is>
           <t>yh-yc-005</t>
         </is>
       </c>
-      <c r="D476" s="8" t="inlineStr">
+      <c r="D475" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E476" s="8" t="n"/>
-      <c r="F476" s="8" t="inlineStr">
+      <c r="E475" s="8" t="n"/>
+      <c r="F475" s="8" t="inlineStr">
         <is>
           <t>验证多设备同时登录同一账号的行为</t>
         </is>
       </c>
-      <c r="G476" s="8" t="inlineStr">
+      <c r="G475" s="8" t="inlineStr">
         <is>
           <t>同一微信号在手机A和手机B上登录微信</t>
         </is>
       </c>
-      <c r="H476" s="8" t="inlineStr">
+      <c r="H475" s="8" t="inlineStr">
         <is>
           <t>1. 在手机A上打开快乐羊毛小程序并登录。
 2. 在手机B上也打开快乐羊毛小程序。
@@ -21032,7 +21002,7 @@
 5. 在手机B上操作退款</t>
         </is>
       </c>
-      <c r="I476" s="8" t="inlineStr">
+      <c r="I475" s="8" t="inlineStr">
         <is>
           <t>1. 两台设备都能正常使用小程序。
 2. 手机A下单后，手机B刷新可看到新订单。
@@ -21040,9 +21010,53 @@
 4. 不出现并发操作导致的数据异常</t>
         </is>
       </c>
+      <c r="J475" s="8" t="inlineStr">
+        <is>
+          <t>微信小程序多端登录场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="8" t="inlineStr"/>
+      <c r="B476" s="8" t="inlineStr"/>
+      <c r="C476" s="8" t="inlineStr">
+        <is>
+          <t>yh-yc-006</t>
+        </is>
+      </c>
+      <c r="D476" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E476" s="8" t="n"/>
+      <c r="F476" s="8" t="inlineStr">
+        <is>
+          <t>验证长时间不操作后session过期的处理</t>
+        </is>
+      </c>
+      <c r="G476" s="8" t="inlineStr">
+        <is>
+          <t>用户已登录小程序</t>
+        </is>
+      </c>
+      <c r="H476" s="8" t="inlineStr">
+        <is>
+          <t>1. 打开小程序后放置不操作超过30分钟。
+2. 30分钟后尝试操作（如查看订单、发起支付）。
+3. 观察系统响应</t>
+        </is>
+      </c>
+      <c r="I476" s="8" t="inlineStr">
+        <is>
+          <t>1. 如session未过期，操作正常继续。
+2. 如session已过期，自动重新登录（微信静默登录）或提示重新授权。
+3. 不出现"操作失败"但无原因提示的情况</t>
+        </is>
+      </c>
       <c r="J476" s="8" t="inlineStr">
         <is>
-          <t>微信小程序多端登录场景</t>
+          <t>验证session过期的用户体验</t>
         </is>
       </c>
     </row>
@@ -21051,7 +21065,7 @@
       <c r="B477" s="8" t="inlineStr"/>
       <c r="C477" s="8" t="inlineStr">
         <is>
-          <t>yh-yc-006</t>
+          <t>yh-yc-007</t>
         </is>
       </c>
       <c r="D477" s="8" t="inlineStr">
@@ -21062,117 +21076,73 @@
       <c r="E477" s="8" t="n"/>
       <c r="F477" s="8" t="inlineStr">
         <is>
-          <t>验证长时间不操作后session过期的处理</t>
+          <t>验证频繁下拉刷新不产生重复数据</t>
         </is>
       </c>
       <c r="G477" s="8" t="inlineStr">
         <is>
-          <t>用户已登录小程序</t>
+          <t>用户在订单列表页，已有10条订单数据</t>
         </is>
       </c>
       <c r="H477" s="8" t="inlineStr">
-        <is>
-          <t>1. 打开小程序后放置不操作超过30分钟。
-2. 30分钟后尝试操作（如查看订单、发起支付）。
-3. 观察系统响应</t>
-        </is>
-      </c>
-      <c r="I477" s="8" t="inlineStr">
-        <is>
-          <t>1. 如session未过期，操作正常继续。
-2. 如session已过期，自动重新登录（微信静默登录）或提示重新授权。
-3. 不出现"操作失败"但无原因提示的情况</t>
-        </is>
-      </c>
-      <c r="J477" s="8" t="inlineStr">
-        <is>
-          <t>验证session过期的用户体验</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" s="8" t="inlineStr"/>
-      <c r="B478" s="8" t="inlineStr"/>
-      <c r="C478" s="8" t="inlineStr">
-        <is>
-          <t>yh-yc-007</t>
-        </is>
-      </c>
-      <c r="D478" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E478" s="8" t="n"/>
-      <c r="F478" s="8" t="inlineStr">
-        <is>
-          <t>验证频繁下拉刷新不产生重复数据</t>
-        </is>
-      </c>
-      <c r="G478" s="8" t="inlineStr">
-        <is>
-          <t>用户在订单列表页，已有10条订单数据</t>
-        </is>
-      </c>
-      <c r="H478" s="8" t="inlineStr">
         <is>
           <t>1. 连续快速下拉刷新5次（间隔&lt;1秒）。
 2. 等待所有刷新请求完成。
 3. 检查列表数据</t>
         </is>
       </c>
-      <c r="I478" s="8" t="inlineStr">
+      <c r="I477" s="8" t="inlineStr">
         <is>
           <t>1. 不出现重复的订单数据。
 2. 数据条数正确（仍为10条）。
 3. 不出现loading卡住的情况</t>
         </is>
       </c>
-      <c r="J478" s="8" t="inlineStr">
+      <c r="J477" s="8" t="inlineStr">
         <is>
           <t>防止重复请求导致数据重复</t>
         </is>
       </c>
     </row>
-    <row r="479">
-      <c r="A479" s="9" t="inlineStr">
+    <row r="478">
+      <c r="A478" s="9" t="inlineStr">
         <is>
           <t>商家端</t>
         </is>
       </c>
-      <c r="B479" s="9" t="inlineStr">
+      <c r="B478" s="9" t="inlineStr">
         <is>
           <t>1.5h</t>
         </is>
       </c>
-      <c r="C479" s="9" t="inlineStr">
+      <c r="C478" s="9" t="inlineStr">
         <is>
           <t>sj-hj-001</t>
         </is>
       </c>
-      <c r="D479" s="9" t="inlineStr">
+      <c r="D478" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E479" s="9" t="inlineStr">
+      <c r="E478" s="9" t="inlineStr">
         <is>
           <t>商家端环境测试
 (小程序端)</t>
         </is>
       </c>
-      <c r="F479" s="9" t="inlineStr">
+      <c r="F478" s="9" t="inlineStr">
         <is>
           <t>验证商家端小程序在iOS设备上收银台完整流程</t>
         </is>
       </c>
-      <c r="G479" s="9" t="inlineStr">
+      <c r="G478" s="9" t="inlineStr">
         <is>
           <t>1. iPhone设备，已安装微信最新版
 2. 商家品牌主账号已登录</t>
         </is>
       </c>
-      <c r="H479" s="9" t="inlineStr">
+      <c r="H478" s="9" t="inlineStr">
         <is>
           <t>1. 打开商家端小程序。
 2. 进入收银台，输入消费金额100元。
@@ -21182,7 +21152,7 @@
 6. 查看订单详情</t>
         </is>
       </c>
-      <c r="I479" s="9" t="inlineStr">
+      <c r="I478" s="9" t="inlineStr">
         <is>
           <t>1. 小程序正常打开，菜单完整。
 2. 金额输入键盘正常唤起，数字输入正确。
@@ -21192,38 +21162,38 @@
 6. 订单信息完整</t>
         </is>
       </c>
-      <c r="J479" s="9" t="inlineStr">
+      <c r="J478" s="9" t="inlineStr">
         <is>
           <t>iOS设备数字键盘与Android可能有差异</t>
         </is>
       </c>
     </row>
-    <row r="480">
-      <c r="A480" s="8" t="inlineStr"/>
-      <c r="B480" s="8" t="inlineStr"/>
-      <c r="C480" s="8" t="inlineStr">
+    <row r="479">
+      <c r="A479" s="8" t="inlineStr"/>
+      <c r="B479" s="8" t="inlineStr"/>
+      <c r="C479" s="8" t="inlineStr">
         <is>
           <t>sj-hj-002</t>
         </is>
       </c>
-      <c r="D480" s="8" t="inlineStr">
+      <c r="D479" s="8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E480" s="8" t="n"/>
-      <c r="F480" s="8" t="inlineStr">
+      <c r="E479" s="8" t="n"/>
+      <c r="F479" s="8" t="inlineStr">
         <is>
           <t>验证商家端小程序在Android设备上收银台完整流程</t>
         </is>
       </c>
-      <c r="G480" s="8" t="inlineStr">
+      <c r="G479" s="8" t="inlineStr">
         <is>
           <t>1. Android设备（华为/小米），已安装微信最新版
 2. 商家品牌主账号已登录</t>
         </is>
       </c>
-      <c r="H480" s="8" t="inlineStr">
+      <c r="H479" s="8" t="inlineStr">
         <is>
           <t>1. 打开商家端小程序。
 2. 进入收银台，输入消费金额99.50元。
@@ -21233,7 +21203,7 @@
 6. 查看订单管理列表</t>
         </is>
       </c>
-      <c r="I480" s="8" t="inlineStr">
+      <c r="I479" s="8" t="inlineStr">
         <is>
           <t>1. 小程序正常打开。
 2. 金额输入正常，小数点输入正确。
@@ -21243,47 +21213,47 @@
 6. 订单列表展示正确</t>
         </is>
       </c>
-      <c r="J480" s="8" t="inlineStr">
+      <c r="J479" s="8" t="inlineStr">
         <is>
           <t>关注Android各品牌机型差异</t>
         </is>
       </c>
     </row>
-    <row r="481">
-      <c r="A481" s="9" t="inlineStr">
+    <row r="480">
+      <c r="A480" s="9" t="inlineStr">
         <is>
           <t>商家端</t>
         </is>
       </c>
-      <c r="B481" s="9" t="inlineStr"/>
-      <c r="C481" s="9" t="inlineStr">
+      <c r="B480" s="9" t="inlineStr"/>
+      <c r="C480" s="9" t="inlineStr">
         <is>
           <t>sj-hj-003</t>
         </is>
       </c>
-      <c r="D481" s="9" t="inlineStr">
+      <c r="D480" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E481" s="9" t="inlineStr">
+      <c r="E480" s="9" t="inlineStr">
         <is>
           <t>商家端环境测试
 (PC端)</t>
         </is>
       </c>
-      <c r="F481" s="9" t="inlineStr">
+      <c r="F480" s="9" t="inlineStr">
         <is>
           <t>验证商家端PC版在Chrome浏览器上完整流程</t>
         </is>
       </c>
-      <c r="G481" s="9" t="inlineStr">
+      <c r="G480" s="9" t="inlineStr">
         <is>
           <t>1. Chrome最新版浏览器
 2. 商家品牌主账号已登录PC端后台</t>
         </is>
       </c>
-      <c r="H481" s="9" t="inlineStr">
+      <c r="H480" s="9" t="inlineStr">
         <is>
           <t>1. 打开商家端PC后台。
 2. 查看订单管理列表。
@@ -21293,7 +21263,7 @@
 6. 查看数据统计</t>
         </is>
       </c>
-      <c r="I481" s="9" t="inlineStr">
+      <c r="I480" s="9" t="inlineStr">
         <is>
           <t>1. 页面正常加载，布局完整。
 2. 订单列表分页正常。
@@ -21303,38 +21273,38 @@
 6. 数据统计图表正常显示</t>
         </is>
       </c>
-      <c r="J481" s="9" t="inlineStr">
+      <c r="J480" s="9" t="inlineStr">
         <is>
           <t>Chrome为主要测试浏览器</t>
         </is>
       </c>
     </row>
-    <row r="482">
-      <c r="A482" s="8" t="inlineStr"/>
-      <c r="B482" s="8" t="inlineStr"/>
-      <c r="C482" s="8" t="inlineStr">
+    <row r="481">
+      <c r="A481" s="8" t="inlineStr"/>
+      <c r="B481" s="8" t="inlineStr"/>
+      <c r="C481" s="8" t="inlineStr">
         <is>
           <t>sj-hj-004</t>
         </is>
       </c>
-      <c r="D482" s="8" t="inlineStr">
+      <c r="D481" s="8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E482" s="8" t="n"/>
-      <c r="F482" s="8" t="inlineStr">
+      <c r="E481" s="8" t="n"/>
+      <c r="F481" s="8" t="inlineStr">
         <is>
           <t>验证商家端PC版在Edge浏览器上的兼容性</t>
         </is>
       </c>
-      <c r="G482" s="8" t="inlineStr">
+      <c r="G481" s="8" t="inlineStr">
         <is>
           <t>1. Edge最新版浏览器
 2. 商家品牌主账号</t>
         </is>
       </c>
-      <c r="H482" s="8" t="inlineStr">
+      <c r="H481" s="8" t="inlineStr">
         <is>
           <t>1. 在Edge浏览器中打开商家端后台。
 2. 执行收银台操作（输入金额、生成二维码）。
@@ -21343,7 +21313,7 @@
 5. 退款操作</t>
         </is>
       </c>
-      <c r="I482" s="8" t="inlineStr">
+      <c r="I481" s="8" t="inlineStr">
         <is>
           <t>1. 页面布局与Chrome一致，无错位。
 2. 二维码正常生成。
@@ -21352,46 +21322,46 @@
 5. 退款弹窗正常显示</t>
         </is>
       </c>
-      <c r="J482" s="8" t="inlineStr">
+      <c r="J481" s="8" t="inlineStr">
         <is>
           <t>验证Edge浏览器兼容性</t>
         </is>
       </c>
     </row>
-    <row r="483">
-      <c r="A483" s="9" t="inlineStr">
+    <row r="482">
+      <c r="A482" s="9" t="inlineStr">
         <is>
           <t>商家端</t>
         </is>
       </c>
-      <c r="B483" s="9" t="inlineStr"/>
-      <c r="C483" s="9" t="inlineStr">
+      <c r="B482" s="9" t="inlineStr"/>
+      <c r="C482" s="9" t="inlineStr">
         <is>
           <t>sj-hj-005</t>
         </is>
       </c>
-      <c r="D483" s="9" t="inlineStr">
+      <c r="D482" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E483" s="9" t="inlineStr">
+      <c r="E482" s="9" t="inlineStr">
         <is>
           <t>商家端异常测试</t>
         </is>
       </c>
-      <c r="F483" s="9" t="inlineStr">
+      <c r="F482" s="9" t="inlineStr">
         <is>
           <t>验证商家端收银台弱网下生成二维码</t>
         </is>
       </c>
-      <c r="G483" s="9" t="inlineStr">
+      <c r="G482" s="9" t="inlineStr">
         <is>
           <t>1. 弱网环境
 2. 商家已输入消费金额</t>
         </is>
       </c>
-      <c r="H483" s="9" t="inlineStr">
+      <c r="H482" s="9" t="inlineStr">
         <is>
           <t>1. 在弱网环境下点击"生成收款码"。
 2. 观察生成过程。
@@ -21399,7 +21369,7 @@
 4. 恢复网络后重试</t>
         </is>
       </c>
-      <c r="I483" s="9" t="inlineStr">
+      <c r="I482" s="9" t="inlineStr">
         <is>
           <t>1. 显示生成中loading。
 2. 超时后提示"网络不稳定，请重试"。
@@ -21407,9 +21377,56 @@
 4. 恢复网络后重试成功</t>
         </is>
       </c>
-      <c r="J483" s="9" t="inlineStr">
+      <c r="J482" s="9" t="inlineStr">
         <is>
           <t>商家在店内WiFi可能不稳定</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="8" t="inlineStr"/>
+      <c r="B483" s="8" t="inlineStr"/>
+      <c r="C483" s="8" t="inlineStr">
+        <is>
+          <t>sj-hj-006</t>
+        </is>
+      </c>
+      <c r="D483" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E483" s="8" t="n"/>
+      <c r="F483" s="8" t="inlineStr">
+        <is>
+          <t>验证商家端核销验证码时网络中断的处理</t>
+        </is>
+      </c>
+      <c r="G483" s="8" t="inlineStr">
+        <is>
+          <t>1. 商家正在输入核销验证码
+2. 人工辅助模式订单</t>
+        </is>
+      </c>
+      <c r="H483" s="8" t="inlineStr">
+        <is>
+          <t>1. 输入正确的验证码。
+2. 点击"确认核销"时断开网络。
+3. 观察结果。
+4. 恢复网络后重新核销</t>
+        </is>
+      </c>
+      <c r="I483" s="8" t="inlineStr">
+        <is>
+          <t>1. 提示"网络异常，核销失败"。
+2. 订单状态未变更（仍为"待核销"）。
+3. 恢复网络后重新输入验证码可成功核销。
+4. 不出现重复核销</t>
+        </is>
+      </c>
+      <c r="J483" s="8" t="inlineStr">
+        <is>
+          <t>防止网络中断导致核销状态不一致</t>
         </is>
       </c>
     </row>
@@ -21418,7 +21435,7 @@
       <c r="B484" s="8" t="inlineStr"/>
       <c r="C484" s="8" t="inlineStr">
         <is>
-          <t>sj-hj-006</t>
+          <t>sj-hj-007</t>
         </is>
       </c>
       <c r="D484" s="8" t="inlineStr">
@@ -21429,63 +21446,16 @@
       <c r="E484" s="8" t="n"/>
       <c r="F484" s="8" t="inlineStr">
         <is>
-          <t>验证商家端核销验证码时网络中断的处理</t>
+          <t>验证门店子账号在禁用状态下的所有操作被拒绝</t>
         </is>
       </c>
       <c r="G484" s="8" t="inlineStr">
-        <is>
-          <t>1. 商家正在输入核销验证码
-2. 人工辅助模式订单</t>
-        </is>
-      </c>
-      <c r="H484" s="8" t="inlineStr">
-        <is>
-          <t>1. 输入正确的验证码。
-2. 点击"确认核销"时断开网络。
-3. 观察结果。
-4. 恢复网络后重新核销</t>
-        </is>
-      </c>
-      <c r="I484" s="8" t="inlineStr">
-        <is>
-          <t>1. 提示"网络异常，核销失败"。
-2. 订单状态未变更（仍为"待核销"）。
-3. 恢复网络后重新输入验证码可成功核销。
-4. 不出现重复核销</t>
-        </is>
-      </c>
-      <c r="J484" s="8" t="inlineStr">
-        <is>
-          <t>防止网络中断导致核销状态不一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" s="8" t="inlineStr"/>
-      <c r="B485" s="8" t="inlineStr"/>
-      <c r="C485" s="8" t="inlineStr">
-        <is>
-          <t>sj-hj-007</t>
-        </is>
-      </c>
-      <c r="D485" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E485" s="8" t="n"/>
-      <c r="F485" s="8" t="inlineStr">
-        <is>
-          <t>验证门店子账号在禁用状态下的所有操作被拒绝</t>
-        </is>
-      </c>
-      <c r="G485" s="8" t="inlineStr">
         <is>
           <t>1. 品牌主账号已创建门店子账号A
 2. 子账号A已登录</t>
         </is>
       </c>
-      <c r="H485" s="8" t="inlineStr">
+      <c r="H484" s="8" t="inlineStr">
         <is>
           <t>1. 品牌主账号禁用子账号A。
 2. 子账号A刷新页面/重新打开小程序。
@@ -21494,7 +21464,7 @@
 5. 尝试发起退款</t>
         </is>
       </c>
-      <c r="I485" s="8" t="inlineStr">
+      <c r="I484" s="8" t="inlineStr">
         <is>
           <t>1. 子账号A被强制退出登录或下次操作提示"账号已被禁用"。
 2. 无法进入收银台。
@@ -21502,38 +21472,38 @@
 4. 无法进行任何操作</t>
         </is>
       </c>
-      <c r="J485" s="8" t="inlineStr">
+      <c r="J484" s="8" t="inlineStr">
         <is>
           <t>在线禁用的即时生效验证</t>
         </is>
       </c>
     </row>
-    <row r="486">
-      <c r="A486" s="8" t="inlineStr"/>
-      <c r="B486" s="8" t="inlineStr"/>
-      <c r="C486" s="8" t="inlineStr">
+    <row r="485">
+      <c r="A485" s="8" t="inlineStr"/>
+      <c r="B485" s="8" t="inlineStr"/>
+      <c r="C485" s="8" t="inlineStr">
         <is>
           <t>sj-hj-008</t>
         </is>
       </c>
-      <c r="D486" s="8" t="inlineStr">
+      <c r="D485" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E486" s="8" t="n"/>
-      <c r="F486" s="8" t="inlineStr">
+      <c r="E485" s="8" t="n"/>
+      <c r="F485" s="8" t="inlineStr">
         <is>
           <t>验证商家端PC浏览器最小化/切后台后恢复数据状态</t>
         </is>
       </c>
-      <c r="G486" s="8" t="inlineStr">
+      <c r="G485" s="8" t="inlineStr">
         <is>
           <t>1. 商家端PC后台已打开订单管理页
 2. 已加载订单列表数据</t>
         </is>
       </c>
-      <c r="H486" s="8" t="inlineStr">
+      <c r="H485" s="8" t="inlineStr">
         <is>
           <t>1. 将浏览器最小化或切换到其他应用。
 2. 等待5分钟。
@@ -21541,59 +21511,59 @@
 4. 尝试操作（翻页、筛选）</t>
         </is>
       </c>
-      <c r="I486" s="8" t="inlineStr">
+      <c r="I485" s="8" t="inlineStr">
         <is>
           <t>1. 页面数据保持不变。
 2. 操作正常响应（如session未过期）。
 3. 如session过期，提示重新登录</t>
         </is>
       </c>
-      <c r="J486" s="8" t="inlineStr">
+      <c r="J485" s="8" t="inlineStr">
         <is>
           <t>验证session管理和页面状态保持</t>
         </is>
       </c>
     </row>
-    <row r="487">
-      <c r="A487" s="9" t="inlineStr">
+    <row r="486">
+      <c r="A486" s="9" t="inlineStr">
         <is>
           <t>管理后台</t>
         </is>
       </c>
-      <c r="B487" s="9" t="inlineStr">
+      <c r="B486" s="9" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="C487" s="9" t="inlineStr">
+      <c r="C486" s="9" t="inlineStr">
         <is>
           <t>ht-hj-001</t>
         </is>
       </c>
-      <c r="D487" s="9" t="inlineStr">
+      <c r="D486" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E487" s="9" t="inlineStr">
+      <c r="E486" s="9" t="inlineStr">
         <is>
           <t>管理后台环境测试
 (PC端)</t>
         </is>
       </c>
-      <c r="F487" s="9" t="inlineStr">
+      <c r="F486" s="9" t="inlineStr">
         <is>
           <t>验证管理后台在Chrome浏览器上完整功能正常</t>
         </is>
       </c>
-      <c r="G487" s="9" t="inlineStr">
+      <c r="G486" s="9" t="inlineStr">
         <is>
           <t>1. Chrome最新版浏览器
 2. 管理员账号(admin/admin123)
 3. 后台地址: https://red.jinyedaojia.com/</t>
         </is>
       </c>
-      <c r="H487" s="9" t="inlineStr">
+      <c r="H486" s="9" t="inlineStr">
         <is>
           <t>1. 登录管理后台。
 2. 订单列表查看与筛选。
@@ -21604,7 +21574,7 @@
 7. 退款审核操作</t>
         </is>
       </c>
-      <c r="I487" s="9" t="inlineStr">
+      <c r="I486" s="9" t="inlineStr">
         <is>
           <t>1. 登录成功，后台首页正常。
 2. 订单列表加载正常，筛选有效。
@@ -21615,38 +21585,38 @@
 7. 退款审核流程完整</t>
         </is>
       </c>
-      <c r="J487" s="9" t="inlineStr">
+      <c r="J486" s="9" t="inlineStr">
         <is>
           <t>Chrome为主要测试浏览器</t>
         </is>
       </c>
     </row>
-    <row r="488">
-      <c r="A488" s="8" t="inlineStr"/>
-      <c r="B488" s="8" t="inlineStr"/>
-      <c r="C488" s="8" t="inlineStr">
+    <row r="487">
+      <c r="A487" s="8" t="inlineStr"/>
+      <c r="B487" s="8" t="inlineStr"/>
+      <c r="C487" s="8" t="inlineStr">
         <is>
           <t>ht-hj-002</t>
         </is>
       </c>
-      <c r="D488" s="8" t="inlineStr">
+      <c r="D487" s="8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E488" s="8" t="n"/>
-      <c r="F488" s="8" t="inlineStr">
+      <c r="E487" s="8" t="n"/>
+      <c r="F487" s="8" t="inlineStr">
         <is>
           <t>验证管理后台在Edge浏览器上的兼容性</t>
         </is>
       </c>
-      <c r="G488" s="8" t="inlineStr">
+      <c r="G487" s="8" t="inlineStr">
         <is>
           <t>1. Edge最新版浏览器
 2. 管理员账号</t>
         </is>
       </c>
-      <c r="H488" s="8" t="inlineStr">
+      <c r="H487" s="8" t="inlineStr">
         <is>
           <t>1. 在Edge中登录后台。
 2. 查看订单列表（表格渲染）。
@@ -21655,7 +21625,7 @@
 5. 查看分佣明细</t>
         </is>
       </c>
-      <c r="I488" s="8" t="inlineStr">
+      <c r="I487" s="8" t="inlineStr">
         <is>
           <t>1. 页面布局与Chrome一致。
 2. 表格数据展示正常。
@@ -21664,53 +21634,53 @@
 5. 分佣明细数据正确</t>
         </is>
       </c>
-      <c r="J488" s="8" t="inlineStr">
+      <c r="J487" s="8" t="inlineStr">
         <is>
           <t>验证Edge兼容性</t>
         </is>
       </c>
     </row>
-    <row r="489">
-      <c r="A489" s="9" t="inlineStr">
+    <row r="488">
+      <c r="A488" s="9" t="inlineStr">
         <is>
           <t>管理后台</t>
         </is>
       </c>
-      <c r="B489" s="9" t="inlineStr"/>
-      <c r="C489" s="9" t="inlineStr">
+      <c r="B488" s="9" t="inlineStr"/>
+      <c r="C488" s="9" t="inlineStr">
         <is>
           <t>ht-hj-003</t>
         </is>
       </c>
-      <c r="D489" s="9" t="inlineStr">
+      <c r="D488" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E489" s="9" t="inlineStr">
+      <c r="E488" s="9" t="inlineStr">
         <is>
           <t>管理后台异常测试</t>
         </is>
       </c>
-      <c r="F489" s="9" t="inlineStr">
+      <c r="F488" s="9" t="inlineStr">
         <is>
           <t>验证管理后台操作过程中网络超时的处理</t>
         </is>
       </c>
-      <c r="G489" s="9" t="inlineStr">
+      <c r="G488" s="9" t="inlineStr">
         <is>
           <t>1. 管理员已登录后台
 2. 使用Charles模拟网络延迟(&gt;10秒)</t>
         </is>
       </c>
-      <c r="H489" s="9" t="inlineStr">
+      <c r="H488" s="9" t="inlineStr">
         <is>
           <t>1. 在高延迟环境下点击"一键同步"。
 2. 在高延迟环境下提交退款审核。
 3. 在高延迟环境下上传Excel文件</t>
         </is>
       </c>
-      <c r="I489" s="9" t="inlineStr">
+      <c r="I488" s="9" t="inlineStr">
         <is>
           <t>1. 同步操作显示loading，超时后提示"请求超时，请重试"。
 2. 退款审核提交后等待，不因超时产生重复操作。
@@ -21718,9 +21688,56 @@
 4. 所有操作不因超时产生脏数据</t>
         </is>
       </c>
-      <c r="J489" s="9" t="inlineStr">
+      <c r="J488" s="9" t="inlineStr">
         <is>
           <t>后台操作的容错能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="8" t="inlineStr"/>
+      <c r="B489" s="8" t="inlineStr"/>
+      <c r="C489" s="8" t="inlineStr">
+        <is>
+          <t>ht-hj-004</t>
+        </is>
+      </c>
+      <c r="D489" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E489" s="8" t="n"/>
+      <c r="F489" s="8" t="inlineStr">
+        <is>
+          <t>验证管理后台多运营人员并发操作退款审核</t>
+        </is>
+      </c>
+      <c r="G489" s="8" t="inlineStr">
+        <is>
+          <t>1. 准备2个运营管理员账号(A和B)
+2. 1笔待审核的退款订单</t>
+        </is>
+      </c>
+      <c r="H489" s="8" t="inlineStr">
+        <is>
+          <t>1. 运营A和运营B同时打开同一笔退款审核页面。
+2. 运营A点击"审核通过"。
+3. 运营B随后（&lt;2秒）也点击"审核通过"。
+4. 检查退款结果</t>
+        </is>
+      </c>
+      <c r="I489" s="8" t="inlineStr">
+        <is>
+          <t>1. 运营A审核通过成功。
+2. 运营B操作时提示"该订单已被审核"或页面自动刷新。
+3. 退款金额只退一次，不重复退款。
+4. 审核记录只有一条</t>
+        </is>
+      </c>
+      <c r="J489" s="8" t="inlineStr">
+        <is>
+          <t>防止并发审核导致重复退款——资金安全</t>
         </is>
       </c>
     </row>
@@ -21729,7 +21746,7 @@
       <c r="B490" s="8" t="inlineStr"/>
       <c r="C490" s="8" t="inlineStr">
         <is>
-          <t>ht-hj-004</t>
+          <t>ht-hj-005</t>
         </is>
       </c>
       <c r="D490" s="8" t="inlineStr">
@@ -21740,63 +21757,16 @@
       <c r="E490" s="8" t="n"/>
       <c r="F490" s="8" t="inlineStr">
         <is>
-          <t>验证管理后台多运营人员并发操作退款审核</t>
+          <t>验证管理后台浏览器刷新/前进后退操作的稳定性</t>
         </is>
       </c>
       <c r="G490" s="8" t="inlineStr">
-        <is>
-          <t>1. 准备2个运营管理员账号(A和B)
-2. 1笔待审核的退款订单</t>
-        </is>
-      </c>
-      <c r="H490" s="8" t="inlineStr">
-        <is>
-          <t>1. 运营A和运营B同时打开同一笔退款审核页面。
-2. 运营A点击"审核通过"。
-3. 运营B随后（&lt;2秒）也点击"审核通过"。
-4. 检查退款结果</t>
-        </is>
-      </c>
-      <c r="I490" s="8" t="inlineStr">
-        <is>
-          <t>1. 运营A审核通过成功。
-2. 运营B操作时提示"该订单已被审核"或页面自动刷新。
-3. 退款金额只退一次，不重复退款。
-4. 审核记录只有一条</t>
-        </is>
-      </c>
-      <c r="J490" s="8" t="inlineStr">
-        <is>
-          <t>防止并发审核导致重复退款——资金安全</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" s="8" t="inlineStr"/>
-      <c r="B491" s="8" t="inlineStr"/>
-      <c r="C491" s="8" t="inlineStr">
-        <is>
-          <t>ht-hj-005</t>
-        </is>
-      </c>
-      <c r="D491" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E491" s="8" t="n"/>
-      <c r="F491" s="8" t="inlineStr">
-        <is>
-          <t>验证管理后台浏览器刷新/前进后退操作的稳定性</t>
-        </is>
-      </c>
-      <c r="G491" s="8" t="inlineStr">
         <is>
           <t>1. 管理员已登录后台
 2. 正在进行分佣配置修改（已输入数据未保存）</t>
         </is>
       </c>
-      <c r="H491" s="8" t="inlineStr">
+      <c r="H490" s="8" t="inlineStr">
         <is>
           <t>1. 输入新的分佣比例但未点击保存。
 2. 按F5刷新页面。
@@ -21805,7 +21775,7 @@
 5. 再前进回来</t>
         </is>
       </c>
-      <c r="I491" s="8" t="inlineStr">
+      <c r="I490" s="8" t="inlineStr">
         <is>
           <t>1. 刷新后未保存的数据丢失，恢复原始值（正常行为）。
 2. 或弹出"有未保存修改，是否离开？"确认框。
@@ -21813,45 +21783,45 @@
 4. 页面数据正确</t>
         </is>
       </c>
-      <c r="J491" s="8" t="inlineStr">
+      <c r="J490" s="8" t="inlineStr">
         <is>
           <t>浏览器原生操作的处理</t>
         </is>
       </c>
     </row>
-    <row r="492">
-      <c r="A492" s="8" t="inlineStr"/>
-      <c r="B492" s="8" t="inlineStr"/>
-      <c r="C492" s="8" t="inlineStr">
+    <row r="491">
+      <c r="A491" s="8" t="inlineStr"/>
+      <c r="B491" s="8" t="inlineStr"/>
+      <c r="C491" s="8" t="inlineStr">
         <is>
           <t>ht-hj-006</t>
         </is>
       </c>
-      <c r="D492" s="8" t="inlineStr">
+      <c r="D491" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E492" s="8" t="n"/>
-      <c r="F492" s="8" t="inlineStr">
+      <c r="E491" s="8" t="n"/>
+      <c r="F491" s="8" t="inlineStr">
         <is>
           <t>验证管理后台token过期后的操作处理</t>
         </is>
       </c>
-      <c r="G492" s="8" t="inlineStr">
+      <c r="G491" s="8" t="inlineStr">
         <is>
           <t>1. 管理员已登录后台
 2. 长时间不操作（或手动清除cookie/token）</t>
         </is>
       </c>
-      <c r="H492" s="8" t="inlineStr">
+      <c r="H491" s="8" t="inlineStr">
         <is>
           <t>1. 打开浏览器开发者工具，手动清除登录token。
 2. 尝试操作（如点击订单列表翻页）。
 3. 观察系统响应</t>
         </is>
       </c>
-      <c r="I492" s="8" t="inlineStr">
+      <c r="I491" s="8" t="inlineStr">
         <is>
           <t>1. 提示"登录已过期，请重新登录"。
 2. 自动跳转到登录页。
@@ -21859,45 +21829,45 @@
 4. 不返回500错误页面</t>
         </is>
       </c>
-      <c r="J492" s="8" t="inlineStr">
+      <c r="J491" s="8" t="inlineStr">
         <is>
           <t>验证鉴权过期的用户体验</t>
         </is>
       </c>
     </row>
-    <row r="493">
-      <c r="A493" s="9" t="inlineStr">
+    <row r="492">
+      <c r="A492" s="9" t="inlineStr">
         <is>
           <t>管理后台</t>
         </is>
       </c>
-      <c r="B493" s="9" t="inlineStr">
+      <c r="B492" s="9" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="C493" s="9" t="inlineStr">
+      <c r="C492" s="9" t="inlineStr">
         <is>
           <t>sd-yz-001</t>
         </is>
       </c>
-      <c r="D493" s="9" t="inlineStr">
+      <c r="D492" s="9" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E493" s="9" t="inlineStr">
+      <c r="E492" s="9" t="inlineStr">
         <is>
           <t>三端数据一致性
 验证</t>
         </is>
       </c>
-      <c r="F493" s="9" t="inlineStr">
+      <c r="F492" s="9" t="inlineStr">
         <is>
           <t>验证餐饮扫码支付后三端订单数据一致性</t>
         </is>
       </c>
-      <c r="G493" s="9" t="inlineStr">
+      <c r="G492" s="9" t="inlineStr">
         <is>
           <t>1. 商家端已登录
 2. 用户端已登录
@@ -21905,7 +21875,7 @@
 4. 分佣比例已配置（平台50%/代理商50%）</t>
         </is>
       </c>
-      <c r="H493" s="9" t="inlineStr">
+      <c r="H492" s="9" t="inlineStr">
         <is>
           <t>1. 商家端输入消费金额100元，生成收款码。
 2. 用户端扫码支付（8折=实付80元）。
@@ -21914,7 +21884,7 @@
 5. 检查管理后台订单列表和分佣明细</t>
         </is>
       </c>
-      <c r="I493" s="9" t="inlineStr">
+      <c r="I492" s="9" t="inlineStr">
         <is>
           <t>1. 用户端：订单状态"已完成"，原价100/优惠20/实付80。
 2. 商家端：订单显示实付80元，今日流水+80。
@@ -21922,38 +21892,38 @@
 4. 三端订单号一致、金额一致、状态一致</t>
         </is>
       </c>
-      <c r="J493" s="9" t="inlineStr">
+      <c r="J492" s="9" t="inlineStr">
         <is>
           <t>三端必须完全一致，任何差异都是P0级Bug</t>
         </is>
       </c>
     </row>
-    <row r="494">
-      <c r="A494" s="8" t="inlineStr"/>
-      <c r="B494" s="8" t="inlineStr"/>
-      <c r="C494" s="8" t="inlineStr">
+    <row r="493">
+      <c r="A493" s="8" t="inlineStr"/>
+      <c r="B493" s="8" t="inlineStr"/>
+      <c r="C493" s="8" t="inlineStr">
         <is>
           <t>sd-yz-002</t>
         </is>
       </c>
-      <c r="D494" s="8" t="inlineStr">
+      <c r="D493" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E494" s="8" t="n"/>
-      <c r="F494" s="8" t="inlineStr">
+      <c r="E493" s="8" t="n"/>
+      <c r="F493" s="8" t="inlineStr">
         <is>
           <t>验证全额退款后三端数据一致性</t>
         </is>
       </c>
-      <c r="G494" s="8" t="inlineStr">
+      <c r="G493" s="8" t="inlineStr">
         <is>
           <t>1. 上一用例已完成的餐饮扫码订单（实付80元）
 2. 三端均已确认数据一致</t>
         </is>
       </c>
-      <c r="H494" s="8" t="inlineStr">
+      <c r="H493" s="8" t="inlineStr">
         <is>
           <t>1. 商家端发起全额退款（80元）。
 2. 管理后台审核通过退款。
@@ -21962,7 +21932,7 @@
 5. 检查管理后台分佣明细变化</t>
         </is>
       </c>
-      <c r="I494" s="8" t="inlineStr">
+      <c r="I493" s="8" t="inlineStr">
         <is>
           <t>1. 用户端：订单状态"已退款"，退款金额80元，收到退款通知。
 2. 商家端：订单状态"已退款"，今日流水扣减80元。
@@ -21970,38 +21940,38 @@
 4. 三端状态和金额完全一致</t>
         </is>
       </c>
-      <c r="J494" s="8" t="inlineStr">
+      <c r="J493" s="8" t="inlineStr">
         <is>
           <t>退款后三端一致性比下单更容易出问题</t>
         </is>
       </c>
     </row>
-    <row r="495">
-      <c r="A495" s="8" t="inlineStr"/>
-      <c r="B495" s="8" t="inlineStr"/>
-      <c r="C495" s="8" t="inlineStr">
+    <row r="494">
+      <c r="A494" s="8" t="inlineStr"/>
+      <c r="B494" s="8" t="inlineStr"/>
+      <c r="C494" s="8" t="inlineStr">
         <is>
           <t>sd-yz-003</t>
         </is>
       </c>
-      <c r="D495" s="8" t="inlineStr">
+      <c r="D494" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E495" s="8" t="n"/>
-      <c r="F495" s="8" t="inlineStr">
+      <c r="E494" s="8" t="n"/>
+      <c r="F494" s="8" t="inlineStr">
         <is>
           <t>验证部分退款后三端数据一致性</t>
         </is>
       </c>
-      <c r="G495" s="8" t="inlineStr">
+      <c r="G494" s="8" t="inlineStr">
         <is>
           <t>1. 一笔已完成的餐饮扫码订单（实付80元）
 2. 分佣已生成</t>
         </is>
       </c>
-      <c r="H495" s="8" t="inlineStr">
+      <c r="H494" s="8" t="inlineStr">
         <is>
           <t>1. 管理后台执行部分退款30元。
 2. 检查用户端订单状态和金额。
@@ -22011,7 +21981,7 @@
 6. 再次检查三端</t>
         </is>
       </c>
-      <c r="I495" s="8" t="inlineStr">
+      <c r="I494" s="8" t="inlineStr">
         <is>
           <t>1. 第一次退款后：三端订单状态"部分退款"，退款金额30元。
 2. 分佣明细按新利润重算。
@@ -22019,38 +21989,38 @@
 4. 分佣全部冲抵为0</t>
         </is>
       </c>
-      <c r="J495" s="8" t="inlineStr">
+      <c r="J494" s="8" t="inlineStr">
         <is>
           <t>部分退款的分佣重算是最复杂的一致性场景</t>
         </is>
       </c>
     </row>
-    <row r="496">
-      <c r="A496" s="8" t="inlineStr"/>
-      <c r="B496" s="8" t="inlineStr"/>
-      <c r="C496" s="8" t="inlineStr">
+    <row r="495">
+      <c r="A495" s="8" t="inlineStr"/>
+      <c r="B495" s="8" t="inlineStr"/>
+      <c r="C495" s="8" t="inlineStr">
         <is>
           <t>sd-yz-004</t>
         </is>
       </c>
-      <c r="D496" s="8" t="inlineStr">
+      <c r="D495" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E496" s="8" t="n"/>
-      <c r="F496" s="8" t="inlineStr">
+      <c r="E495" s="8" t="n"/>
+      <c r="F495" s="8" t="inlineStr">
         <is>
           <t>验证人工辅助核销后三端数据一致性</t>
         </is>
       </c>
-      <c r="G496" s="8" t="inlineStr">
+      <c r="G495" s="8" t="inlineStr">
         <is>
           <t>1. 用户端已提交人工辅助订单（消费100元/8.5折）
 2. 三端已登录</t>
         </is>
       </c>
-      <c r="H496" s="8" t="inlineStr">
+      <c r="H495" s="8" t="inlineStr">
         <is>
           <t>1. 用户端提交凭证+金额。
 2. 管理后台审核通过，输入验证码下发。
@@ -22059,7 +22029,7 @@
 5. 检查三端订单状态</t>
         </is>
       </c>
-      <c r="I496" s="8" t="inlineStr">
+      <c r="I495" s="8" t="inlineStr">
         <is>
           <t>1. 用户端：收到验证码通知，订单状态"已完成"。
 2. 商家端：核销成功，订单记录出现。
@@ -22067,9 +22037,56 @@
 4. 三端信息完全一致</t>
         </is>
       </c>
+      <c r="J495" s="8" t="inlineStr">
+        <is>
+          <t>人工辅助流程跨三端交互最多，容易不一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="8" t="inlineStr"/>
+      <c r="B496" s="8" t="inlineStr"/>
+      <c r="C496" s="8" t="inlineStr">
+        <is>
+          <t>sd-yz-005</t>
+        </is>
+      </c>
+      <c r="D496" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E496" s="8" t="n"/>
+      <c r="F496" s="8" t="inlineStr">
+        <is>
+          <t>验证佣金/余额三端数据一致性</t>
+        </is>
+      </c>
+      <c r="G496" s="8" t="inlineStr">
+        <is>
+          <t>1. 代理商账号已有多笔佣金记录
+2. 部分佣金"待结算"，部分"可提现"</t>
+        </is>
+      </c>
+      <c r="H496" s="8" t="inlineStr">
+        <is>
+          <t>1. 在用户端（代理商视角）查看"预估收入"和"可提现余额"。
+2. 在管理后台查看该代理商的佣金汇总。
+3. 对比两端金额。
+4. 完成一笔新订单，再次对比</t>
+        </is>
+      </c>
+      <c r="I496" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户端"预估收入"=后台"待结算"总额。
+2. 用户端"可提现余额"=后台"可提现"总额。
+3. 新订单完成后，用户端佣金及时更新。
+4. 两端数据完全一致</t>
+        </is>
+      </c>
       <c r="J496" s="8" t="inlineStr">
         <is>
-          <t>人工辅助流程跨三端交互最多，容易不一致</t>
+          <t>佣金金额的准确性直接影响用户信任</t>
         </is>
       </c>
     </row>
@@ -22078,7 +22095,7 @@
       <c r="B497" s="8" t="inlineStr"/>
       <c r="C497" s="8" t="inlineStr">
         <is>
-          <t>sd-yz-005</t>
+          <t>sd-yz-006</t>
         </is>
       </c>
       <c r="D497" s="8" t="inlineStr">
@@ -22089,63 +22106,16 @@
       <c r="E497" s="8" t="n"/>
       <c r="F497" s="8" t="inlineStr">
         <is>
-          <t>验证佣金/余额三端数据一致性</t>
+          <t>验证虚拟商品发货后三端数据一致性</t>
         </is>
       </c>
       <c r="G497" s="8" t="inlineStr">
-        <is>
-          <t>1. 代理商账号已有多笔佣金记录
-2. 部分佣金"待结算"，部分"可提现"</t>
-        </is>
-      </c>
-      <c r="H497" s="8" t="inlineStr">
-        <is>
-          <t>1. 在用户端（代理商视角）查看"预估收入"和"可提现余额"。
-2. 在管理后台查看该代理商的佣金汇总。
-3. 对比两端金额。
-4. 完成一笔新订单，再次对比</t>
-        </is>
-      </c>
-      <c r="I497" s="8" t="inlineStr">
-        <is>
-          <t>1. 用户端"预估收入"=后台"待结算"总额。
-2. 用户端"可提现余额"=后台"可提现"总额。
-3. 新订单完成后，用户端佣金及时更新。
-4. 两端数据完全一致</t>
-        </is>
-      </c>
-      <c r="J497" s="8" t="inlineStr">
-        <is>
-          <t>佣金金额的准确性直接影响用户信任</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" s="8" t="inlineStr"/>
-      <c r="B498" s="8" t="inlineStr"/>
-      <c r="C498" s="8" t="inlineStr">
-        <is>
-          <t>sd-yz-006</t>
-        </is>
-      </c>
-      <c r="D498" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E498" s="8" t="n"/>
-      <c r="F498" s="8" t="inlineStr">
-        <is>
-          <t>验证虚拟商品发货后三端数据一致性</t>
-        </is>
-      </c>
-      <c r="G498" s="8" t="inlineStr">
         <is>
           <t>1. 用户已购买通用券10元面额
 2. 三端已登录</t>
         </is>
       </c>
-      <c r="H498" s="8" t="inlineStr">
+      <c r="H497" s="8" t="inlineStr">
         <is>
           <t>1. 用户端完成支付。
 2. 等待API发货完成。
@@ -22154,7 +22124,7 @@
 5. 确认无退款按钮显示</t>
         </is>
       </c>
-      <c r="I498" s="8" t="inlineStr">
+      <c r="I497" s="8" t="inlineStr">
         <is>
           <t>1. 用户端：订单COMPLETED，展示卡密和有效期。
 2. 管理后台：订单COMPLETED，发货记录完整。
@@ -22163,59 +22133,59 @@
 5. 分佣明细正确</t>
         </is>
       </c>
-      <c r="J498" s="8" t="inlineStr">
+      <c r="J497" s="8" t="inlineStr">
         <is>
           <t>虚拟商品的不可退款特性需三端一致</t>
         </is>
       </c>
     </row>
-    <row r="499">
-      <c r="A499" s="9" t="inlineStr">
+    <row r="498">
+      <c r="A498" s="9" t="inlineStr">
         <is>
           <t>管理后台</t>
         </is>
       </c>
-      <c r="B499" s="9" t="inlineStr">
+      <c r="B498" s="9" t="inlineStr">
         <is>
           <t>1.5h</t>
         </is>
       </c>
-      <c r="C499" s="9" t="inlineStr">
+      <c r="C498" s="9" t="inlineStr">
         <is>
           <t>txjs-001</t>
         </is>
       </c>
-      <c r="D499" s="9" t="inlineStr">
+      <c r="D498" s="9" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E499" s="9" t="inlineStr">
+      <c r="E498" s="9" t="inlineStr">
         <is>
           <t>提现结算
 完整流程</t>
         </is>
       </c>
-      <c r="F499" s="9" t="inlineStr">
+      <c r="F498" s="9" t="inlineStr">
         <is>
           <t>验证佣金从"待结算"到"可提现"的状态流转</t>
         </is>
       </c>
-      <c r="G499" s="9" t="inlineStr">
+      <c r="G498" s="9" t="inlineStr">
         <is>
           <t>1. 代理商账号已有一笔已完成订单的佣金
 2. 佣金状态为"待结算"
 3. 结算周期已配置</t>
         </is>
       </c>
-      <c r="H499" s="9" t="inlineStr">
+      <c r="H498" s="9" t="inlineStr">
         <is>
           <t>1. 查看代理商佣金明细，确认佣金状态为"待结算"。
 2. 等待结算周期到达（或测试环境手动推进）。
 3. 再次查看佣金状态</t>
         </is>
       </c>
-      <c r="I499" s="9" t="inlineStr">
+      <c r="I498" s="9" t="inlineStr">
         <is>
           <t>1. 结算周期前，佣金状态为"待结算"，不可提现。
 2. 结算周期到达后，佣金状态自动变为"可提现"。
@@ -22223,38 +22193,38 @@
 4. 待结算余额减少相应金额</t>
         </is>
       </c>
-      <c r="J499" s="9" t="inlineStr">
+      <c r="J498" s="9" t="inlineStr">
         <is>
           <t>结算周期（T+7/T+15/T+30）待确认Q12</t>
         </is>
       </c>
     </row>
-    <row r="500">
-      <c r="A500" s="8" t="inlineStr"/>
-      <c r="B500" s="8" t="inlineStr"/>
-      <c r="C500" s="8" t="inlineStr">
+    <row r="499">
+      <c r="A499" s="8" t="inlineStr"/>
+      <c r="B499" s="8" t="inlineStr"/>
+      <c r="C499" s="8" t="inlineStr">
         <is>
           <t>txjs-002</t>
         </is>
       </c>
-      <c r="D500" s="8" t="inlineStr">
+      <c r="D499" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E500" s="8" t="n"/>
-      <c r="F500" s="8" t="inlineStr">
+      <c r="E499" s="8" t="n"/>
+      <c r="F499" s="8" t="inlineStr">
         <is>
           <t>验证分销员/代理商申请提现的完整流程</t>
         </is>
       </c>
-      <c r="G500" s="8" t="inlineStr">
+      <c r="G499" s="8" t="inlineStr">
         <is>
           <t>1. 代理商有可提现余额20元
 2. 管理后台有运营审核权限</t>
         </is>
       </c>
-      <c r="H500" s="8" t="inlineStr">
+      <c r="H499" s="8" t="inlineStr">
         <is>
           <t>1. 代理商在个人中心申请提现20元。
 2. 管理后台查看提现申请列表。
@@ -22263,7 +22233,7 @@
 5. 检查代理商余额变化</t>
         </is>
       </c>
-      <c r="I500" s="8" t="inlineStr">
+      <c r="I499" s="8" t="inlineStr">
         <is>
           <t>1. 提现申请提交成功，状态"审核中"。
 2. 后台提现列表出现该申请。
@@ -22272,38 +22242,38 @@
 5. 代理商可提现余额减少20元</t>
         </is>
       </c>
-      <c r="J500" s="8" t="inlineStr">
+      <c r="J499" s="8" t="inlineStr">
         <is>
           <t>资金流转的完整链路</t>
         </is>
       </c>
     </row>
-    <row r="501">
-      <c r="A501" s="8" t="inlineStr"/>
-      <c r="B501" s="8" t="inlineStr"/>
-      <c r="C501" s="8" t="inlineStr">
+    <row r="500">
+      <c r="A500" s="8" t="inlineStr"/>
+      <c r="B500" s="8" t="inlineStr"/>
+      <c r="C500" s="8" t="inlineStr">
         <is>
           <t>txjs-003</t>
         </is>
       </c>
-      <c r="D501" s="8" t="inlineStr">
+      <c r="D500" s="8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E501" s="8" t="n"/>
-      <c r="F501" s="8" t="inlineStr">
+      <c r="E500" s="8" t="n"/>
+      <c r="F500" s="8" t="inlineStr">
         <is>
           <t>验证提现审核拒绝的处理</t>
         </is>
       </c>
-      <c r="G501" s="8" t="inlineStr">
+      <c r="G500" s="8" t="inlineStr">
         <is>
           <t>1. 代理商已申请提现
 2. 管理后台运营准备审核</t>
         </is>
       </c>
-      <c r="H501" s="8" t="inlineStr">
+      <c r="H500" s="8" t="inlineStr">
         <is>
           <t>1. 管理后台查看提现申请。
 2. 选择"拒绝"并填写拒绝原因。
@@ -22311,7 +22281,7 @@
 4. 检查代理商端的变化</t>
         </is>
       </c>
-      <c r="I501" s="8" t="inlineStr">
+      <c r="I500" s="8" t="inlineStr">
         <is>
           <t>1. 提现状态变为"已拒绝"。
 2. 金额退回"可提现"余额。
@@ -22320,37 +22290,37 @@
 5. 代理商可重新申请提现</t>
         </is>
       </c>
-      <c r="J501" s="8" t="inlineStr">
+      <c r="J500" s="8" t="inlineStr">
         <is>
           <t>拒绝后金额必须正确退回</t>
         </is>
       </c>
     </row>
-    <row r="502">
-      <c r="A502" s="8" t="inlineStr"/>
-      <c r="B502" s="8" t="inlineStr"/>
-      <c r="C502" s="8" t="inlineStr">
+    <row r="501">
+      <c r="A501" s="8" t="inlineStr"/>
+      <c r="B501" s="8" t="inlineStr"/>
+      <c r="C501" s="8" t="inlineStr">
         <is>
           <t>txjs-004</t>
         </is>
       </c>
-      <c r="D502" s="8" t="inlineStr">
+      <c r="D501" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E502" s="8" t="n"/>
-      <c r="F502" s="8" t="inlineStr">
+      <c r="E501" s="8" t="n"/>
+      <c r="F501" s="8" t="inlineStr">
         <is>
           <t>验证提现金额校验规则</t>
         </is>
       </c>
-      <c r="G502" s="8" t="inlineStr">
+      <c r="G501" s="8" t="inlineStr">
         <is>
           <t>代理商可提现余额为50.00元</t>
         </is>
       </c>
-      <c r="H502" s="8" t="inlineStr">
+      <c r="H501" s="8" t="inlineStr">
         <is>
           <t>1. 尝试提现0元。
 2. 尝试提现-10元。
@@ -22359,7 +22329,7 @@
 5. 尝试提现0.01元（最小金额）</t>
         </is>
       </c>
-      <c r="I502" s="8" t="inlineStr">
+      <c r="I501" s="8" t="inlineStr">
         <is>
           <t>1. 提现0元：提示"提现金额必须大于0"。
 2. 提现-10元：输入被拦截。
@@ -22368,38 +22338,38 @@
 5. 提现0.01元：成功或提示低于最低提现金额</t>
         </is>
       </c>
-      <c r="J502" s="8" t="inlineStr">
+      <c r="J501" s="8" t="inlineStr">
         <is>
           <t>最低提现金额待确认Q9</t>
         </is>
       </c>
     </row>
-    <row r="503">
-      <c r="A503" s="8" t="inlineStr"/>
-      <c r="B503" s="8" t="inlineStr"/>
-      <c r="C503" s="8" t="inlineStr">
+    <row r="502">
+      <c r="A502" s="8" t="inlineStr"/>
+      <c r="B502" s="8" t="inlineStr"/>
+      <c r="C502" s="8" t="inlineStr">
         <is>
           <t>txjs-005</t>
         </is>
       </c>
-      <c r="D503" s="8" t="inlineStr">
+      <c r="D502" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E503" s="8" t="n"/>
-      <c r="F503" s="8" t="inlineStr">
+      <c r="E502" s="8" t="n"/>
+      <c r="F502" s="8" t="inlineStr">
         <is>
           <t>验证佣金已提现后退款产生欠款的处理</t>
         </is>
       </c>
-      <c r="G503" s="8" t="inlineStr">
+      <c r="G502" s="8" t="inlineStr">
         <is>
           <t>1. 订单已完成，代理商佣金20元已提现完毕
 2. 代理商当前可提现余额为0</t>
         </is>
       </c>
-      <c r="H503" s="8" t="inlineStr">
+      <c r="H502" s="8" t="inlineStr">
         <is>
           <t>1. 对该已完成订单执行全额退款。
 2. 检查代理商佣金明细。
@@ -22408,7 +22378,7 @@
 5. 检查新佣金是否自动抵扣欠款</t>
         </is>
       </c>
-      <c r="I503" s="8" t="inlineStr">
+      <c r="I502" s="8" t="inlineStr">
         <is>
           <t>1. 退款成功。
 2. 佣金明细新增冲抵记录-20元。
@@ -22418,97 +22388,97 @@
 6. 直到欠款清零</t>
         </is>
       </c>
-      <c r="J503" s="8" t="inlineStr">
+      <c r="J502" s="8" t="inlineStr">
         <is>
           <t>最复杂的资金场景——已提现后退款</t>
         </is>
       </c>
     </row>
-    <row r="504">
-      <c r="A504" s="8" t="inlineStr"/>
-      <c r="B504" s="8" t="inlineStr"/>
-      <c r="C504" s="8" t="inlineStr">
+    <row r="503">
+      <c r="A503" s="8" t="inlineStr"/>
+      <c r="B503" s="8" t="inlineStr"/>
+      <c r="C503" s="8" t="inlineStr">
         <is>
           <t>txjs-006</t>
         </is>
       </c>
-      <c r="D504" s="8" t="inlineStr">
+      <c r="D503" s="8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E504" s="8" t="n"/>
-      <c r="F504" s="8" t="inlineStr">
+      <c r="E503" s="8" t="n"/>
+      <c r="F503" s="8" t="inlineStr">
         <is>
           <t>验证待结算状态不可提现</t>
         </is>
       </c>
-      <c r="G504" s="8" t="inlineStr">
+      <c r="G503" s="8" t="inlineStr">
         <is>
           <t>1. 代理商有一笔新订单佣金（待结算状态）
 2. 可提现余额为0</t>
         </is>
       </c>
-      <c r="H504" s="8" t="inlineStr">
+      <c r="H503" s="8" t="inlineStr">
         <is>
           <t>1. 代理商查看余额：待结算&gt;0，可提现=0。
 2. 尝试申请提现。
 3. 观察结果</t>
         </is>
       </c>
-      <c r="I504" s="8" t="inlineStr">
+      <c r="I503" s="8" t="inlineStr">
         <is>
           <t>1. 提现页面显示"可提现余额：0.00元"。
 2. 无法提交提现申请。
 3. 或提示"当前无可提现余额"</t>
         </is>
       </c>
-      <c r="J504" s="8" t="inlineStr">
+      <c r="J503" s="8" t="inlineStr">
         <is>
           <t>待结算的佣金不能直接提现</t>
         </is>
       </c>
     </row>
-    <row r="505">
-      <c r="A505" s="9" t="inlineStr">
+    <row r="504">
+      <c r="A504" s="9" t="inlineStr">
         <is>
           <t>管理后台</t>
         </is>
       </c>
-      <c r="B505" s="9" t="inlineStr">
+      <c r="B504" s="9" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="C505" s="9" t="inlineStr">
+      <c r="C504" s="9" t="inlineStr">
         <is>
           <t>tk-fy-001</t>
         </is>
       </c>
-      <c r="D505" s="9" t="inlineStr">
+      <c r="D504" s="9" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E505" s="9" t="inlineStr">
+      <c r="E504" s="9" t="inlineStr">
         <is>
           <t>退款分佣冲抵
 (深度验证)</t>
         </is>
       </c>
-      <c r="F505" s="9" t="inlineStr">
+      <c r="F504" s="9" t="inlineStr">
         <is>
           <t>验证全额退款后各角色佣金冲抵正确（无分销员场景）</t>
         </is>
       </c>
-      <c r="G505" s="9" t="inlineStr">
+      <c r="G504" s="9" t="inlineStr">
         <is>
           <t>1. 订单实付100元，成本60元，利润40元
 2. 平台50%(20元)，代理商50%(20元)
 3. 佣金状态：待结算</t>
         </is>
       </c>
-      <c r="H505" s="9" t="inlineStr">
+      <c r="H504" s="9" t="inlineStr">
         <is>
           <t>1. 对该订单执行全额退款。
 2. 查看平台佣金明细。
@@ -22516,7 +22486,7 @@
 4. 验证冲抵金额</t>
         </is>
       </c>
-      <c r="I505" s="9" t="inlineStr">
+      <c r="I504" s="9" t="inlineStr">
         <is>
           <t>1. 平台佣金明细新增冲抵记录：-20.00元。
 2. 代理商佣金明细新增冲抵记录：-20.00元。
@@ -22524,44 +22494,44 @@
 4. 冲抵总和(-40元)=原利润(-40元)</t>
         </is>
       </c>
-      <c r="J505" s="9" t="inlineStr">
+      <c r="J504" s="9" t="inlineStr">
         <is>
           <t>分佣冲抵的基础场景</t>
         </is>
       </c>
     </row>
-    <row r="506">
-      <c r="A506" s="8" t="inlineStr"/>
-      <c r="B506" s="8" t="inlineStr"/>
-      <c r="C506" s="8" t="inlineStr">
+    <row r="505">
+      <c r="A505" s="8" t="inlineStr"/>
+      <c r="B505" s="8" t="inlineStr"/>
+      <c r="C505" s="8" t="inlineStr">
         <is>
           <t>tk-fy-002</t>
         </is>
       </c>
-      <c r="D506" s="8" t="inlineStr">
+      <c r="D505" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E506" s="8" t="n"/>
-      <c r="F506" s="8" t="inlineStr">
+      <c r="E505" s="8" t="n"/>
+      <c r="F505" s="8" t="inlineStr">
         <is>
           <t>验证全额退款后多级分销员的佣金连锁冲抵</t>
         </is>
       </c>
-      <c r="G506" s="8" t="inlineStr">
+      <c r="G505" s="8" t="inlineStr">
         <is>
           <t>1. 利润40元，平台20元，代理商实得14元，一级4元，二级2元
 2. 全部处于"待结算"状态</t>
         </is>
       </c>
-      <c r="H506" s="8" t="inlineStr">
+      <c r="H505" s="8" t="inlineStr">
         <is>
           <t>1. 执行全额退款。
 2. 逐一检查各角色佣金明细冲抵记录</t>
         </is>
       </c>
-      <c r="I506" s="8" t="inlineStr">
+      <c r="I505" s="8" t="inlineStr">
         <is>
           <t>1. 平台冲抵：-20.00元。
 2. 代理商冲抵：-14.00元。
@@ -22570,9 +22540,56 @@
 5. 合计冲抵-(20+14+4+2)=-40元=利润</t>
         </is>
       </c>
+      <c r="J505" s="8" t="inlineStr">
+        <is>
+          <t>多级分销退款是分佣最复杂场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="8" t="inlineStr"/>
+      <c r="B506" s="8" t="inlineStr"/>
+      <c r="C506" s="8" t="inlineStr">
+        <is>
+          <t>tk-fy-003</t>
+        </is>
+      </c>
+      <c r="D506" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E506" s="8" t="n"/>
+      <c r="F506" s="8" t="inlineStr">
+        <is>
+          <t>验证部分退款后分佣重算的正确性</t>
+        </is>
+      </c>
+      <c r="G506" s="8" t="inlineStr">
+        <is>
+          <t>1. 订单实付100元，成本60元，利润40元
+2. 平台50%(20元)，代理商50%(20元)</t>
+        </is>
+      </c>
+      <c r="H506" s="8" t="inlineStr">
+        <is>
+          <t>1. 执行部分退款40元。
+2. 计算新利润=新实付(60)-成本(60)=0元。
+3. 检查各角色佣金调整。
+4. 验证冲抵金额</t>
+        </is>
+      </c>
+      <c r="I506" s="8" t="inlineStr">
+        <is>
+          <t>1. 新利润为0元（或按比例退还成本后重算）。
+2. 平台佣金调整为0，冲抵记录-20元。
+3. 代理商佣金调整为0，冲抵记录-20元。
+4. 冲抵金额精确到分</t>
+        </is>
+      </c>
       <c r="J506" s="8" t="inlineStr">
         <is>
-          <t>多级分销退款是分佣最复杂场景</t>
+          <t>部分退款成本是否按比例退需确认</t>
         </is>
       </c>
     </row>
@@ -22581,7 +22598,7 @@
       <c r="B507" s="8" t="inlineStr"/>
       <c r="C507" s="8" t="inlineStr">
         <is>
-          <t>tk-fy-003</t>
+          <t>tk-fy-004</t>
         </is>
       </c>
       <c r="D507" s="8" t="inlineStr">
@@ -22592,34 +22609,33 @@
       <c r="E507" s="8" t="n"/>
       <c r="F507" s="8" t="inlineStr">
         <is>
-          <t>验证部分退款后分佣重算的正确性</t>
+          <t>验证多次部分退款后累计冲抵的正确性</t>
         </is>
       </c>
       <c r="G507" s="8" t="inlineStr">
         <is>
           <t>1. 订单实付100元，成本60元，利润40元
-2. 平台50%(20元)，代理商50%(20元)</t>
+2. 分佣已生成</t>
         </is>
       </c>
       <c r="H507" s="8" t="inlineStr">
         <is>
-          <t>1. 执行部分退款40元。
-2. 计算新利润=新实付(60)-成本(60)=0元。
-3. 检查各角色佣金调整。
-4. 验证冲抵金额</t>
+          <t>1. 第一次部分退款30元，检查分佣调整。
+2. 第二次部分退款20元，检查分佣再次调整。
+3. 第三次尝试退款60元（超出剩余可退50元）</t>
         </is>
       </c>
       <c r="I507" s="8" t="inlineStr">
         <is>
-          <t>1. 新利润为0元（或按比例退还成本后重算）。
-2. 平台佣金调整为0，冲抵记录-20元。
-3. 代理商佣金调整为0，冲抵记录-20元。
-4. 冲抵金额精确到分</t>
+          <t>1. 第一次退款后分佣按新利润重算。
+2. 第二次退款后分佣再次重算。
+3. 第三次退款被拦截："退款金额不能超过剩余可退50元"。
+4. 累计冲抵金额正确</t>
         </is>
       </c>
       <c r="J507" s="8" t="inlineStr">
         <is>
-          <t>部分退款成本是否按比例退需确认</t>
+          <t>多次退款的累积计算</t>
         </is>
       </c>
     </row>
@@ -22628,7 +22644,7 @@
       <c r="B508" s="8" t="inlineStr"/>
       <c r="C508" s="8" t="inlineStr">
         <is>
-          <t>tk-fy-004</t>
+          <t>tk-fy-005</t>
         </is>
       </c>
       <c r="D508" s="8" t="inlineStr">
@@ -22639,33 +22655,34 @@
       <c r="E508" s="8" t="n"/>
       <c r="F508" s="8" t="inlineStr">
         <is>
-          <t>验证多次部分退款后累计冲抵的正确性</t>
+          <t>验证混合状态下退款冲抵（部分已提现/部分待结算）</t>
         </is>
       </c>
       <c r="G508" s="8" t="inlineStr">
         <is>
-          <t>1. 订单实付100元，成本60元，利润40元
-2. 分佣已生成</t>
+          <t>1. 利润40元，平台佣金20元(待结算)，代理商20元(已提现)
+2. 一级分销员4元(待结算)</t>
         </is>
       </c>
       <c r="H508" s="8" t="inlineStr">
         <is>
-          <t>1. 第一次部分退款30元，检查分佣调整。
-2. 第二次部分退款20元，检查分佣再次调整。
-3. 第三次尝试退款60元（超出剩余可退50元）</t>
+          <t>1. 执行全额退款。
+2. 检查平台佣金（待结算→冲抵）。
+3. 检查代理商佣金（已提现→欠款）。
+4. 检查一级分销员佣金冲抵</t>
         </is>
       </c>
       <c r="I508" s="8" t="inlineStr">
         <is>
-          <t>1. 第一次退款后分佣按新利润重算。
-2. 第二次退款后分佣再次重算。
-3. 第三次退款被拦截："退款金额不能超过剩余可退50元"。
-4. 累计冲抵金额正确</t>
+          <t>1. 平台：待结算余额-20元（直接冲抵）。
+2. 代理商：产生欠款记录20元（因已提现）。
+3. 一级分销员：待结算余额-4元（直接冲抵）。
+4. 各角色冲抵/欠款机制独立运作</t>
         </is>
       </c>
       <c r="J508" s="8" t="inlineStr">
         <is>
-          <t>多次退款的累积计算</t>
+          <t>混合状态是实际业务中最常见的</t>
         </is>
       </c>
     </row>
@@ -22674,74 +22691,27 @@
       <c r="B509" s="8" t="inlineStr"/>
       <c r="C509" s="8" t="inlineStr">
         <is>
-          <t>tk-fy-005</t>
+          <t>tk-fy-006</t>
         </is>
       </c>
       <c r="D509" s="8" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E509" s="8" t="n"/>
       <c r="F509" s="8" t="inlineStr">
         <is>
-          <t>验证混合状态下退款冲抵（部分已提现/部分待结算）</t>
+          <t>验证修改分佣比例后已完成订单的佣金不变</t>
         </is>
       </c>
       <c r="G509" s="8" t="inlineStr">
-        <is>
-          <t>1. 利润40元，平台佣金20元(待结算)，代理商20元(已提现)
-2. 一级分销员4元(待结算)</t>
-        </is>
-      </c>
-      <c r="H509" s="8" t="inlineStr">
-        <is>
-          <t>1. 执行全额退款。
-2. 检查平台佣金（待结算→冲抵）。
-3. 检查代理商佣金（已提现→欠款）。
-4. 检查一级分销员佣金冲抵</t>
-        </is>
-      </c>
-      <c r="I509" s="8" t="inlineStr">
-        <is>
-          <t>1. 平台：待结算余额-20元（直接冲抵）。
-2. 代理商：产生欠款记录20元（因已提现）。
-3. 一级分销员：待结算余额-4元（直接冲抵）。
-4. 各角色冲抵/欠款机制独立运作</t>
-        </is>
-      </c>
-      <c r="J509" s="8" t="inlineStr">
-        <is>
-          <t>混合状态是实际业务中最常见的</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" s="8" t="inlineStr"/>
-      <c r="B510" s="8" t="inlineStr"/>
-      <c r="C510" s="8" t="inlineStr">
-        <is>
-          <t>tk-fy-006</t>
-        </is>
-      </c>
-      <c r="D510" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E510" s="8" t="n"/>
-      <c r="F510" s="8" t="inlineStr">
-        <is>
-          <t>验证修改分佣比例后已完成订单的佣金不变</t>
-        </is>
-      </c>
-      <c r="G510" s="8" t="inlineStr">
         <is>
           <t>1. 订单A在分佣比例50%/50%时完成，佣金已生成
 2. 管理后台准备修改分佣比例</t>
         </is>
       </c>
-      <c r="H510" s="8" t="inlineStr">
+      <c r="H509" s="8" t="inlineStr">
         <is>
           <t>1. 查看订单A的分佣明细（平台20/代理商20）。
 2. 将分佣比例修改为30%/70%。
@@ -22749,57 +22719,57 @@
 4. 创建新订单B，查看新订单的分佣</t>
         </is>
       </c>
-      <c r="I510" s="8" t="inlineStr">
+      <c r="I509" s="8" t="inlineStr">
         <is>
           <t>1. 订单A分佣不变（仍为20/20）。
 2. 新订单B按新比例计算（12/28）。
 3. 历史数据不被篡改</t>
         </is>
       </c>
-      <c r="J510" s="8" t="inlineStr">
+      <c r="J509" s="8" t="inlineStr">
         <is>
           <t>分佣比例修改的隔离性</t>
         </is>
       </c>
     </row>
-    <row r="511">
-      <c r="A511" s="9" t="inlineStr">
+    <row r="510">
+      <c r="A510" s="9" t="inlineStr">
         <is>
           <t>管理后台</t>
         </is>
       </c>
-      <c r="B511" s="9" t="inlineStr">
+      <c r="B510" s="9" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="C511" s="9" t="inlineStr">
+      <c r="C510" s="9" t="inlineStr">
         <is>
           <t>aq-zq-001</t>
         </is>
       </c>
-      <c r="D511" s="9" t="inlineStr">
+      <c r="D510" s="9" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E511" s="9" t="inlineStr">
+      <c r="E510" s="9" t="inlineStr">
         <is>
           <t>安全测试增强</t>
         </is>
       </c>
-      <c r="F511" s="9" t="inlineStr">
+      <c r="F510" s="9" t="inlineStr">
         <is>
           <t>验证支付回调签名验证（防伪造支付成功）</t>
         </is>
       </c>
-      <c r="G511" s="9" t="inlineStr">
+      <c r="G510" s="9" t="inlineStr">
         <is>
           <t>1. Postman/抓包工具
 2. 已知微信支付回调URL</t>
         </is>
       </c>
-      <c r="H511" s="9" t="inlineStr">
+      <c r="H510" s="9" t="inlineStr">
         <is>
           <t>1. 使用Postman构造一个伪造的微信支付成功回调报文。
 2. 发送到系统的支付回调接口。
@@ -22807,7 +22777,7 @@
 4. 检查是否有订单状态被错误修改</t>
         </is>
       </c>
-      <c r="I511" s="9" t="inlineStr">
+      <c r="I510" s="9" t="inlineStr">
         <is>
           <t>1. 系统验证签名失败，拒绝处理。
 2. 返回错误状态码。
@@ -22815,9 +22785,55 @@
 4. 日志记录该异常请求</t>
         </is>
       </c>
-      <c r="J511" s="9" t="inlineStr">
+      <c r="J510" s="9" t="inlineStr">
         <is>
           <t>支付安全第一要务——防伪造回调</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="8" t="inlineStr"/>
+      <c r="B511" s="8" t="inlineStr"/>
+      <c r="C511" s="8" t="inlineStr">
+        <is>
+          <t>aq-zq-002</t>
+        </is>
+      </c>
+      <c r="D511" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E511" s="8" t="n"/>
+      <c r="F511" s="8" t="inlineStr">
+        <is>
+          <t>验证支付回调幂等性（防重复处理）</t>
+        </is>
+      </c>
+      <c r="G511" s="8" t="inlineStr">
+        <is>
+          <t>1. 一笔已完成支付的订单
+2. 已有合法的支付回调记录</t>
+        </is>
+      </c>
+      <c r="H511" s="8" t="inlineStr">
+        <is>
+          <t>1. 模拟微信重发支付成功回调（同一订单号）。
+2. 连续发送3次相同回调。
+3. 检查订单和卡密</t>
+        </is>
+      </c>
+      <c r="I511" s="8" t="inlineStr">
+        <is>
+          <t>1. 第一次回调正常处理。
+2. 后续重复回调被识别为重复，不再处理。
+3. 不重复发放卡密。
+4. 不重复计算分佣</t>
+        </is>
+      </c>
+      <c r="J511" s="8" t="inlineStr">
+        <is>
+          <t>微信可能重复发送回调</t>
         </is>
       </c>
     </row>
@@ -22826,7 +22842,7 @@
       <c r="B512" s="8" t="inlineStr"/>
       <c r="C512" s="8" t="inlineStr">
         <is>
-          <t>aq-zq-002</t>
+          <t>aq-zq-003</t>
         </is>
       </c>
       <c r="D512" s="8" t="inlineStr">
@@ -22837,33 +22853,33 @@
       <c r="E512" s="8" t="n"/>
       <c r="F512" s="8" t="inlineStr">
         <is>
-          <t>验证支付回调幂等性（防重复处理）</t>
+          <t>验证通过API绕过前端直接退款虚拟商品被拦截</t>
         </is>
       </c>
       <c r="G512" s="8" t="inlineStr">
         <is>
-          <t>1. 一笔已完成支付的订单
-2. 已有合法的支付回调记录</t>
+          <t>1. 一笔已完成的通用券订单（COMPLETED）
+2. 前端无退款按钮
+3. Postman工具</t>
         </is>
       </c>
       <c r="H512" s="8" t="inlineStr">
         <is>
-          <t>1. 模拟微信重发支付成功回调（同一订单号）。
-2. 连续发送3次相同回调。
-3. 检查订单和卡密</t>
+          <t>1. 使用Postman直接调用退款接口。
+2. 传入该虚拟商品订单ID。
+3. 观察后端响应</t>
         </is>
       </c>
       <c r="I512" s="8" t="inlineStr">
         <is>
-          <t>1. 第一次回调正常处理。
-2. 后续重复回调被识别为重复，不再处理。
-3. 不重复发放卡密。
-4. 不重复计算分佣</t>
+          <t>1. 后端返回拒绝："该订单类型不支持退款"或返回403。
+2. 订单状态不变。
+3. 不产生退款记录</t>
         </is>
       </c>
       <c r="J512" s="8" t="inlineStr">
         <is>
-          <t>微信可能重复发送回调</t>
+          <t>核心安全：后端必须独立校验，不依赖前端</t>
         </is>
       </c>
     </row>
@@ -22872,7 +22888,7 @@
       <c r="B513" s="8" t="inlineStr"/>
       <c r="C513" s="8" t="inlineStr">
         <is>
-          <t>aq-zq-003</t>
+          <t>aq-zq-004</t>
         </is>
       </c>
       <c r="D513" s="8" t="inlineStr">
@@ -22883,33 +22899,34 @@
       <c r="E513" s="8" t="n"/>
       <c r="F513" s="8" t="inlineStr">
         <is>
-          <t>验证通过API绕过前端直接退款虚拟商品被拦截</t>
+          <t>验证SQL注入防护</t>
         </is>
       </c>
       <c r="G513" s="8" t="inlineStr">
         <is>
-          <t>1. 一笔已完成的通用券订单（COMPLETED）
-2. 前端无退款按钮
-3. Postman工具</t>
+          <t>1. 登录管理后台
+2. 找到各搜索/输入框</t>
         </is>
       </c>
       <c r="H513" s="8" t="inlineStr">
         <is>
-          <t>1. 使用Postman直接调用退款接口。
-2. 传入该虚拟商品订单ID。
-3. 观察后端响应</t>
+          <t>1. 在订单搜索框输入：' OR 1=1 --。
+2. 在登录密码框输入：' OR '1'='1。
+3. 在商家名称输入框输入：'; DROP TABLE orders; --。
+4. 观察各响应</t>
         </is>
       </c>
       <c r="I513" s="8" t="inlineStr">
         <is>
-          <t>1. 后端返回拒绝："该订单类型不支持退款"或返回403。
-2. 订单状态不变。
-3. 不产生退款记录</t>
+          <t>1. 搜索框：返回空结果或正常结果，无SQL错误信息暴露。
+2. 登录框：登录失败，无异常。
+3. 商家名称：保存成功但作为纯文本存储。
+4. 无任何数据库错误信息泄露到前端</t>
         </is>
       </c>
       <c r="J513" s="8" t="inlineStr">
         <is>
-          <t>核心安全：后端必须独立校验，不依赖前端</t>
+          <t>SQL注入是OWASP Top 10</t>
         </is>
       </c>
     </row>
@@ -22918,7 +22935,7 @@
       <c r="B514" s="8" t="inlineStr"/>
       <c r="C514" s="8" t="inlineStr">
         <is>
-          <t>aq-zq-004</t>
+          <t>aq-zq-005</t>
         </is>
       </c>
       <c r="D514" s="8" t="inlineStr">
@@ -22929,34 +22946,34 @@
       <c r="E514" s="8" t="n"/>
       <c r="F514" s="8" t="inlineStr">
         <is>
-          <t>验证SQL注入防护</t>
+          <t>验证XSS跨站脚本攻击防护</t>
         </is>
       </c>
       <c r="G514" s="8" t="inlineStr">
         <is>
-          <t>1. 登录管理后台
-2. 找到各搜索/输入框</t>
+          <t>1. 管理后台已登录
+2. 准备XSS payload</t>
         </is>
       </c>
       <c r="H514" s="8" t="inlineStr">
         <is>
-          <t>1. 在订单搜索框输入：' OR 1=1 --。
-2. 在登录密码框输入：' OR '1'='1。
-3. 在商家名称输入框输入：'; DROP TABLE orders; --。
-4. 观察各响应</t>
+          <t>1. 在商家名称输入：&lt;script&gt;alert("xss")&lt;/script&gt;。
+2. 在退款原因输入：&lt;img src=x onerror=alert(1)&gt;。
+3. 在驳回理由输入：&lt;svg onload=alert(1)&gt;。
+4. 保存后在各端查看显示</t>
         </is>
       </c>
       <c r="I514" s="8" t="inlineStr">
         <is>
-          <t>1. 搜索框：返回空结果或正常结果，无SQL错误信息暴露。
-2. 登录框：登录失败，无异常。
-3. 商家名称：保存成功但作为纯文本存储。
-4. 无任何数据库错误信息泄露到前端</t>
+          <t>1. 所有输入内容被HTML转义后存储/展示。
+2. 不执行任何脚本。
+3. 在用户端/商家端查看时也不会触发XSS。
+4. 特殊字符作为纯文本显示</t>
         </is>
       </c>
       <c r="J514" s="8" t="inlineStr">
         <is>
-          <t>SQL注入是OWASP Top 10</t>
+          <t>XSS可导致用户信息泄露</t>
         </is>
       </c>
     </row>
@@ -22965,7 +22982,7 @@
       <c r="B515" s="8" t="inlineStr"/>
       <c r="C515" s="8" t="inlineStr">
         <is>
-          <t>aq-zq-005</t>
+          <t>aq-zq-006</t>
         </is>
       </c>
       <c r="D515" s="8" t="inlineStr">
@@ -22976,34 +22993,34 @@
       <c r="E515" s="8" t="n"/>
       <c r="F515" s="8" t="inlineStr">
         <is>
-          <t>验证XSS跨站脚本攻击防护</t>
+          <t>验证水平越权防护——用户A操作用户B的订单</t>
         </is>
       </c>
       <c r="G515" s="8" t="inlineStr">
         <is>
-          <t>1. 管理后台已登录
-2. 准备XSS payload</t>
+          <t>1. 用户A和用户B各有一笔订单
+2. 用户A已登录</t>
         </is>
       </c>
       <c r="H515" s="8" t="inlineStr">
         <is>
-          <t>1. 在商家名称输入：&lt;script&gt;alert("xss")&lt;/script&gt;。
-2. 在退款原因输入：&lt;img src=x onerror=alert(1)&gt;。
-3. 在驳回理由输入：&lt;svg onload=alert(1)&gt;。
-4. 保存后在各端查看显示</t>
+          <t>1. 抓包获取用户A查看订单详情的请求。
+2. 将请求中的订单ID替换为用户B的订单ID。
+3. 发送请求。
+4. 同理尝试对用户B的订单执行退款</t>
         </is>
       </c>
       <c r="I515" s="8" t="inlineStr">
         <is>
-          <t>1. 所有输入内容被HTML转义后存储/展示。
-2. 不执行任何脚本。
-3. 在用户端/商家端查看时也不会触发XSS。
-4. 特殊字符作为纯文本显示</t>
+          <t>1. 查看请求返回403"无权限"或404。
+2. 不返回用户B的订单数据。
+3. 退款请求被拒绝。
+4. 日志记录越权尝试</t>
         </is>
       </c>
       <c r="J515" s="8" t="inlineStr">
         <is>
-          <t>XSS可导致用户信息泄露</t>
+          <t>水平越权是最常见的权限漏洞</t>
         </is>
       </c>
     </row>
@@ -23012,7 +23029,7 @@
       <c r="B516" s="8" t="inlineStr"/>
       <c r="C516" s="8" t="inlineStr">
         <is>
-          <t>aq-zq-006</t>
+          <t>aq-zq-007</t>
         </is>
       </c>
       <c r="D516" s="8" t="inlineStr">
@@ -23023,34 +23040,33 @@
       <c r="E516" s="8" t="n"/>
       <c r="F516" s="8" t="inlineStr">
         <is>
-          <t>验证水平越权防护——用户A操作用户B的订单</t>
+          <t>验证垂直越权防护——普通用户调管理后台API</t>
         </is>
       </c>
       <c r="G516" s="8" t="inlineStr">
         <is>
-          <t>1. 用户A和用户B各有一笔订单
-2. 用户A已登录</t>
+          <t>1. 普通用户token
+2. 管理后台API地址</t>
         </is>
       </c>
       <c r="H516" s="8" t="inlineStr">
         <is>
-          <t>1. 抓包获取用户A查看订单详情的请求。
-2. 将请求中的订单ID替换为用户B的订单ID。
-3. 发送请求。
-4. 同理尝试对用户B的订单执行退款</t>
+          <t>1. 使用普通用户token调用后台"修改分佣比例"接口。
+2. 使用普通用户token调用"退款审核"接口。
+3. 使用普通用户token调用"Excel导入"接口</t>
         </is>
       </c>
       <c r="I516" s="8" t="inlineStr">
         <is>
-          <t>1. 查看请求返回403"无权限"或404。
-2. 不返回用户B的订单数据。
-3. 退款请求被拒绝。
-4. 日志记录越权尝试</t>
+          <t>1. 所有请求返回403"无权限"。
+2. 分佣比例不被修改。
+3. 无退款被处理。
+4. 无Excel被导入</t>
         </is>
       </c>
       <c r="J516" s="8" t="inlineStr">
         <is>
-          <t>水平越权是最常见的权限漏洞</t>
+          <t>垂直越权可导致普通用户获取管理员能力</t>
         </is>
       </c>
     </row>
@@ -23059,44 +23075,44 @@
       <c r="B517" s="8" t="inlineStr"/>
       <c r="C517" s="8" t="inlineStr">
         <is>
-          <t>aq-zq-007</t>
+          <t>aq-zq-008</t>
         </is>
       </c>
       <c r="D517" s="8" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E517" s="8" t="n"/>
       <c r="F517" s="8" t="inlineStr">
         <is>
-          <t>验证垂直越权防护——普通用户调管理后台API</t>
+          <t>验证文件上传安全——恶意文件伪装</t>
         </is>
       </c>
       <c r="G517" s="8" t="inlineStr">
         <is>
-          <t>1. 普通用户token
-2. 管理后台API地址</t>
+          <t>1. 准备恶意文件：将.php文件后缀改为.jpg
+2. 人工辅助模式凭证上传</t>
         </is>
       </c>
       <c r="H517" s="8" t="inlineStr">
         <is>
-          <t>1. 使用普通用户token调用后台"修改分佣比例"接口。
-2. 使用普通用户token调用"退款审核"接口。
-3. 使用普通用户token调用"Excel导入"接口</t>
+          <t>1. 将一个PHP脚本文件重命名为test.jpg。
+2. 尝试通过凭证上传接口上传。
+3. 检查后端是否检测文件实际类型。
+4. 检查是否能通过URL直接访问上传的文件</t>
         </is>
       </c>
       <c r="I517" s="8" t="inlineStr">
         <is>
-          <t>1. 所有请求返回403"无权限"。
-2. 分佣比例不被修改。
-3. 无退款被处理。
-4. 无Excel被导入</t>
+          <t>1. 后端检测文件实际MIME类型，拒绝非图片文件。
+2. 或上传成功但无法执行（OSS配置不允许执行脚本）。
+3. 上传的文件URL无法直接访问执行</t>
         </is>
       </c>
       <c r="J517" s="8" t="inlineStr">
         <is>
-          <t>垂直越权可导致普通用户获取管理员能力</t>
+          <t>防止Web Shell上传</t>
         </is>
       </c>
     </row>
@@ -23105,7 +23121,7 @@
       <c r="B518" s="8" t="inlineStr"/>
       <c r="C518" s="8" t="inlineStr">
         <is>
-          <t>aq-zq-008</t>
+          <t>aq-zq-009</t>
         </is>
       </c>
       <c r="D518" s="8" t="inlineStr">
@@ -23116,33 +23132,33 @@
       <c r="E518" s="8" t="n"/>
       <c r="F518" s="8" t="inlineStr">
         <is>
-          <t>验证文件上传安全——恶意文件伪装</t>
+          <t>验证验证码暴力破解防护</t>
         </is>
       </c>
       <c r="G518" s="8" t="inlineStr">
         <is>
-          <t>1. 准备恶意文件：将.php文件后缀改为.jpg
-2. 人工辅助模式凭证上传</t>
+          <t>1. 一笔已下发验证码的人工辅助订单
+2. 商家端核销页面</t>
         </is>
       </c>
       <c r="H518" s="8" t="inlineStr">
         <is>
-          <t>1. 将一个PHP脚本文件重命名为test.jpg。
-2. 尝试通过凭证上传接口上传。
-3. 检查后端是否检测文件实际类型。
-4. 检查是否能通过URL直接访问上传的文件</t>
+          <t>1. 连续输入5次错误的验证码。
+2. 第6次输入正确的验证码。
+3. 等待15分钟后再输入正确验证码</t>
         </is>
       </c>
       <c r="I518" s="8" t="inlineStr">
         <is>
-          <t>1. 后端检测文件实际MIME类型，拒绝非图片文件。
-2. 或上传成功但无法执行（OSS配置不允许执行脚本）。
-3. 上传的文件URL无法直接访问执行</t>
+          <t>1. 第1-5次：每次提示"验证码错误"。
+2. 第5次后：提示"错误次数过多，请15分钟后重试"。
+3. 第6次（锁定期内）：即使输入正确也被拒绝。
+4. 15分钟后：输入正确验证码成功核销</t>
         </is>
       </c>
       <c r="J518" s="8" t="inlineStr">
         <is>
-          <t>防止Web Shell上传</t>
+          <t>防止暴力枚举验证码</t>
         </is>
       </c>
     </row>
@@ -23151,7 +23167,7 @@
       <c r="B519" s="8" t="inlineStr"/>
       <c r="C519" s="8" t="inlineStr">
         <is>
-          <t>aq-zq-009</t>
+          <t>aq-zq-010</t>
         </is>
       </c>
       <c r="D519" s="8" t="inlineStr">
@@ -23162,61 +23178,15 @@
       <c r="E519" s="8" t="n"/>
       <c r="F519" s="8" t="inlineStr">
         <is>
-          <t>验证验证码暴力破解防护</t>
+          <t>验证数据脱敏——敏感信息显示</t>
         </is>
       </c>
       <c r="G519" s="8" t="inlineStr">
         <is>
-          <t>1. 一笔已下发验证码的人工辅助订单
-2. 商家端核销页面</t>
+          <t>1. 系统中已有用户手机号、商家联系电话等敏感数据</t>
         </is>
       </c>
       <c r="H519" s="8" t="inlineStr">
-        <is>
-          <t>1. 连续输入5次错误的验证码。
-2. 第6次输入正确的验证码。
-3. 等待15分钟后再输入正确验证码</t>
-        </is>
-      </c>
-      <c r="I519" s="8" t="inlineStr">
-        <is>
-          <t>1. 第1-5次：每次提示"验证码错误"。
-2. 第5次后：提示"错误次数过多，请15分钟后重试"。
-3. 第6次（锁定期内）：即使输入正确也被拒绝。
-4. 15分钟后：输入正确验证码成功核销</t>
-        </is>
-      </c>
-      <c r="J519" s="8" t="inlineStr">
-        <is>
-          <t>防止暴力枚举验证码</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" s="8" t="inlineStr"/>
-      <c r="B520" s="8" t="inlineStr"/>
-      <c r="C520" s="8" t="inlineStr">
-        <is>
-          <t>aq-zq-010</t>
-        </is>
-      </c>
-      <c r="D520" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E520" s="8" t="n"/>
-      <c r="F520" s="8" t="inlineStr">
-        <is>
-          <t>验证数据脱敏——敏感信息显示</t>
-        </is>
-      </c>
-      <c r="G520" s="8" t="inlineStr">
-        <is>
-          <t>1. 系统中已有用户手机号、商家联系电话等敏感数据</t>
-        </is>
-      </c>
-      <c r="H520" s="8" t="inlineStr">
         <is>
           <t>1. 查看用户列表中的手机号显示。
 2. 查看商家信息中的联系电话显示。
@@ -23224,7 +23194,7 @@
 4. 检查推广海报中是否包含完整手机号</t>
         </is>
       </c>
-      <c r="I520" s="8" t="inlineStr">
+      <c r="I519" s="8" t="inlineStr">
         <is>
           <t>1. 用户手机号显示为138****8001格式。
 2. 商家电话适当脱敏。
@@ -23232,49 +23202,49 @@
 4. 推广海报不泄露完整手机号</t>
         </is>
       </c>
-      <c r="J520" s="8" t="inlineStr">
+      <c r="J519" s="8" t="inlineStr">
         <is>
           <t>个人信息保护</t>
         </is>
       </c>
     </row>
-    <row r="521">
-      <c r="A521" s="8" t="inlineStr">
+    <row r="520">
+      <c r="A520" s="8" t="inlineStr">
         <is>
           <t>用户端</t>
         </is>
       </c>
-      <c r="B521" s="8" t="inlineStr"/>
-      <c r="C521" s="8" t="inlineStr">
+      <c r="B520" s="8" t="inlineStr"/>
+      <c r="C520" s="8" t="inlineStr">
         <is>
           <t>aq-zq-011</t>
         </is>
       </c>
-      <c r="D521" s="8" t="inlineStr">
+      <c r="D520" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E521" s="8" t="n"/>
-      <c r="F521" s="8" t="inlineStr">
+      <c r="E520" s="8" t="n"/>
+      <c r="F520" s="8" t="inlineStr">
         <is>
           <t>验证快速双击支付按钮的防重复提交</t>
         </is>
       </c>
-      <c r="G521" s="8" t="inlineStr">
+      <c r="G520" s="8" t="inlineStr">
         <is>
           <t>1. 用户在通用券订单确认页
 2. 已勾选协议</t>
         </is>
       </c>
-      <c r="H521" s="8" t="inlineStr">
+      <c r="H520" s="8" t="inlineStr">
         <is>
           <t>1. 快速连续点击支付按钮2次（间隔&lt;0.5秒）。
 2. 观察支付弹窗。
 3. 完成支付后检查订单</t>
         </is>
       </c>
-      <c r="I521" s="8" t="inlineStr">
+      <c r="I520" s="8" t="inlineStr">
         <is>
           <t>1. 支付按钮第一次点击后立即置灰/loading。
 2. 只唤起一次支付弹窗。
@@ -23282,38 +23252,38 @@
 4. 不出现重复扣款</t>
         </is>
       </c>
-      <c r="J521" s="8" t="inlineStr">
+      <c r="J520" s="8" t="inlineStr">
         <is>
           <t>防重复提交——资金安全</t>
         </is>
       </c>
     </row>
-    <row r="522">
-      <c r="A522" s="8" t="inlineStr"/>
-      <c r="B522" s="8" t="inlineStr"/>
-      <c r="C522" s="8" t="inlineStr">
+    <row r="521">
+      <c r="A521" s="8" t="inlineStr"/>
+      <c r="B521" s="8" t="inlineStr"/>
+      <c r="C521" s="8" t="inlineStr">
         <is>
           <t>aq-zq-012</t>
         </is>
       </c>
-      <c r="D522" s="8" t="inlineStr">
+      <c r="D521" s="8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E522" s="8" t="n"/>
-      <c r="F522" s="8" t="inlineStr">
+      <c r="E521" s="8" t="n"/>
+      <c r="F521" s="8" t="inlineStr">
         <is>
           <t>验证并发扫码支付的原子性</t>
         </is>
       </c>
-      <c r="G522" s="8" t="inlineStr">
+      <c r="G521" s="8" t="inlineStr">
         <is>
           <t>1. 商家已生成一个收款二维码
 2. 准备2个用户账号A和B</t>
         </is>
       </c>
-      <c r="H522" s="8" t="inlineStr">
+      <c r="H521" s="8" t="inlineStr">
         <is>
           <t>1. 用户A扫码进入支付页面。
 2. 用户B也扫码。
@@ -23321,7 +23291,7 @@
 4. 用户B尝试支付</t>
         </is>
       </c>
-      <c r="I522" s="8" t="inlineStr">
+      <c r="I521" s="8" t="inlineStr">
         <is>
           <t>1. 用户A支付成功。
 2. 用户B扫码时提示"该订单正在支付中"或支付时提示"该订单已被支付"。
@@ -23329,51 +23299,51 @@
 4. 不出现资金异常</t>
         </is>
       </c>
-      <c r="J522" s="8" t="inlineStr">
+      <c r="J521" s="8" t="inlineStr">
         <is>
           <t>使用2台手机实际操作</t>
         </is>
       </c>
     </row>
-    <row r="523">
-      <c r="A523" s="9" t="inlineStr">
+    <row r="522">
+      <c r="A522" s="9" t="inlineStr">
         <is>
           <t>管理后台</t>
         </is>
       </c>
-      <c r="B523" s="9" t="inlineStr">
+      <c r="B522" s="9" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="C523" s="9" t="inlineStr">
+      <c r="C522" s="9" t="inlineStr">
         <is>
           <t>fwq-001</t>
         </is>
       </c>
-      <c r="D523" s="9" t="inlineStr">
+      <c r="D522" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E523" s="9" t="inlineStr">
+      <c r="E522" s="9" t="inlineStr">
         <is>
           <t>服务端异常
 容错测试</t>
         </is>
       </c>
-      <c r="F523" s="9" t="inlineStr">
+      <c r="F522" s="9" t="inlineStr">
         <is>
           <t>验证第三方API（骑士）超时时虚拟商品发货的容错处理</t>
         </is>
       </c>
-      <c r="G523" s="9" t="inlineStr">
+      <c r="G522" s="9" t="inlineStr">
         <is>
           <t>1. 用户已购买通用券并支付成功
 2. 骑士API响应时间&gt;10秒</t>
         </is>
       </c>
-      <c r="H523" s="9" t="inlineStr">
+      <c r="H522" s="9" t="inlineStr">
         <is>
           <t>1. 支付成功后系统调用骑士API发货。
 2. API超时（模拟或实际遇到）。
@@ -23382,7 +23352,7 @@
 5. 检查后台运营可操作性</t>
         </is>
       </c>
-      <c r="I523" s="9" t="inlineStr">
+      <c r="I522" s="9" t="inlineStr">
         <is>
           <t>1. 订单状态变为FAIL。
 2. 用户端显示"发货中"或"发货失败"。
@@ -23390,9 +23360,56 @@
 4. 不出现"已扣款但无订单记录"</t>
         </is>
       </c>
-      <c r="J523" s="9" t="inlineStr">
+      <c r="J522" s="9" t="inlineStr">
         <is>
           <t>第三方API不可控，必须有容错</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="8" t="inlineStr"/>
+      <c r="B523" s="8" t="inlineStr"/>
+      <c r="C523" s="8" t="inlineStr">
+        <is>
+          <t>fwq-002</t>
+        </is>
+      </c>
+      <c r="D523" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E523" s="8" t="n"/>
+      <c r="F523" s="8" t="inlineStr">
+        <is>
+          <t>验证第三方API重复回调的幂等处理</t>
+        </is>
+      </c>
+      <c r="G523" s="8" t="inlineStr">
+        <is>
+          <t>1. 一笔通用券订单支付成功
+2. 骑士API可能重复发送发货成功回调</t>
+        </is>
+      </c>
+      <c r="H523" s="8" t="inlineStr">
+        <is>
+          <t>1. 第一次回调：发货成功，卡密下发。
+2. 模拟第二次相同回调。
+3. 检查是否重复发放卡密。
+4. 检查订单状态</t>
+        </is>
+      </c>
+      <c r="I523" s="8" t="inlineStr">
+        <is>
+          <t>1. 第一次回调正常处理，卡密展示。
+2. 第二次回调被识别为重复，不处理。
+3. 卡密不重复发放（仍是同一个）。
+4. 订单状态不变</t>
+        </is>
+      </c>
+      <c r="J523" s="8" t="inlineStr">
+        <is>
+          <t>幂等性是金融级要求</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23418,7 @@
       <c r="B524" s="8" t="inlineStr"/>
       <c r="C524" s="8" t="inlineStr">
         <is>
-          <t>fwq-002</t>
+          <t>fwq-003</t>
         </is>
       </c>
       <c r="D524" s="8" t="inlineStr">
@@ -23412,34 +23429,34 @@
       <c r="E524" s="8" t="n"/>
       <c r="F524" s="8" t="inlineStr">
         <is>
-          <t>验证第三方API重复回调的幂等处理</t>
+          <t>验证OSS服务不可用时的降级处理</t>
         </is>
       </c>
       <c r="G524" s="8" t="inlineStr">
         <is>
-          <t>1. 一笔通用券订单支付成功
-2. 骑士API可能重复发送发货成功回调</t>
+          <t>1. 选品仓库执行一键同步
+2. 阿里云OSS不可用（模拟）</t>
         </is>
       </c>
       <c r="H524" s="8" t="inlineStr">
         <is>
-          <t>1. 第一次回调：发货成功，卡密下发。
-2. 模拟第二次相同回调。
-3. 检查是否重复发放卡密。
-4. 检查订单状态</t>
+          <t>1. 点击一键同步。
+2. 同步过程中OSS上传失败。
+3. 检查同步结果。
+4. 检查商品数据</t>
         </is>
       </c>
       <c r="I524" s="8" t="inlineStr">
         <is>
-          <t>1. 第一次回调正常处理，卡密展示。
-2. 第二次回调被识别为重复，不处理。
-3. 卡密不重复发放（仍是同一个）。
-4. 订单状态不变</t>
+          <t>1. 商品文本数据（名称/价格/库存）正常入库。
+2. 图片标记为"待重新转存"。
+3. 前端展示默认占位图。
+4. 提示"部分资源上传失败"</t>
         </is>
       </c>
       <c r="J524" s="8" t="inlineStr">
         <is>
-          <t>幂等性是金融级要求</t>
+          <t>验证图片和文本数据的解耦</t>
         </is>
       </c>
     </row>
@@ -23448,45 +23465,43 @@
       <c r="B525" s="8" t="inlineStr"/>
       <c r="C525" s="8" t="inlineStr">
         <is>
-          <t>fwq-003</t>
+          <t>fwq-004</t>
         </is>
       </c>
       <c r="D525" s="8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E525" s="8" t="n"/>
       <c r="F525" s="8" t="inlineStr">
         <is>
-          <t>验证OSS服务不可用时的降级处理</t>
+          <t>验证数据库连接异常时的友好错误提示</t>
         </is>
       </c>
       <c r="G525" s="8" t="inlineStr">
         <is>
-          <t>1. 选品仓库执行一键同步
-2. 阿里云OSS不可用（模拟）</t>
+          <t>1. 管理后台正常使用中</t>
         </is>
       </c>
       <c r="H525" s="8" t="inlineStr">
         <is>
-          <t>1. 点击一键同步。
-2. 同步过程中OSS上传失败。
-3. 检查同步结果。
-4. 检查商品数据</t>
+          <t>1. 模拟数据库连接短暂中断。
+2. 尝试查询订单列表。
+3. 检查页面展示</t>
         </is>
       </c>
       <c r="I525" s="8" t="inlineStr">
         <is>
-          <t>1. 商品文本数据（名称/价格/库存）正常入库。
-2. 图片标记为"待重新转存"。
-3. 前端展示默认占位图。
-4. 提示"部分资源上传失败"</t>
+          <t>1. 返回友好错误提示"系统繁忙，请稍后重试"。
+2. 不暴露数据库连接字符串/技术栈信息。
+3. 不出现500错误的原始堆栈信息。
+4. 数据库恢复后自动恢复正常</t>
         </is>
       </c>
       <c r="J525" s="8" t="inlineStr">
         <is>
-          <t>验证图片和文本数据的解耦</t>
+          <t>防止技术细节泄露</t>
         </is>
       </c>
     </row>
@@ -23495,72 +23510,27 @@
       <c r="B526" s="8" t="inlineStr"/>
       <c r="C526" s="8" t="inlineStr">
         <is>
-          <t>fwq-004</t>
+          <t>fwq-005</t>
         </is>
       </c>
       <c r="D526" s="8" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E526" s="8" t="n"/>
       <c r="F526" s="8" t="inlineStr">
         <is>
-          <t>验证数据库连接异常时的友好错误提示</t>
+          <t>验证微信订阅消息API限流时的降级处理</t>
         </is>
       </c>
       <c r="G526" s="8" t="inlineStr">
-        <is>
-          <t>1. 管理后台正常使用中</t>
-        </is>
-      </c>
-      <c r="H526" s="8" t="inlineStr">
-        <is>
-          <t>1. 模拟数据库连接短暂中断。
-2. 尝试查询订单列表。
-3. 检查页面展示</t>
-        </is>
-      </c>
-      <c r="I526" s="8" t="inlineStr">
-        <is>
-          <t>1. 返回友好错误提示"系统繁忙，请稍后重试"。
-2. 不暴露数据库连接字符串/技术栈信息。
-3. 不出现500错误的原始堆栈信息。
-4. 数据库恢复后自动恢复正常</t>
-        </is>
-      </c>
-      <c r="J526" s="8" t="inlineStr">
-        <is>
-          <t>防止技术细节泄露</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" s="8" t="inlineStr"/>
-      <c r="B527" s="8" t="inlineStr"/>
-      <c r="C527" s="8" t="inlineStr">
-        <is>
-          <t>fwq-005</t>
-        </is>
-      </c>
-      <c r="D527" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E527" s="8" t="n"/>
-      <c r="F527" s="8" t="inlineStr">
-        <is>
-          <t>验证微信订阅消息API限流时的降级处理</t>
-        </is>
-      </c>
-      <c r="G527" s="8" t="inlineStr">
         <is>
           <t>1. 运营审核通过人工辅助订单
 2. 微信API限流/不可用</t>
         </is>
       </c>
-      <c r="H527" s="8" t="inlineStr">
+      <c r="H526" s="8" t="inlineStr">
         <is>
           <t>1. 运营下发验证码。
 2. 订阅消息发送失败（微信API限流）。
@@ -23568,7 +23538,7 @@
 4. 短信也失败时检查兜底方案</t>
         </is>
       </c>
-      <c r="I527" s="8" t="inlineStr">
+      <c r="I526" s="8" t="inlineStr">
         <is>
           <t>1. 订阅消息失败后自动尝试短信。
 2. 短信也失败后提示运营"通知发送失败"。
@@ -23576,50 +23546,50 @@
 4. 不影响订单正常流程</t>
         </is>
       </c>
-      <c r="J527" s="8" t="inlineStr">
+      <c r="J526" s="8" t="inlineStr">
         <is>
           <t>消息推送的三级降级策略</t>
         </is>
       </c>
     </row>
-    <row r="528">
-      <c r="A528" s="9" t="inlineStr">
+    <row r="527">
+      <c r="A527" s="9" t="inlineStr">
         <is>
           <t>管理后台</t>
         </is>
       </c>
-      <c r="B528" s="9" t="inlineStr">
+      <c r="B527" s="9" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="C528" s="9" t="inlineStr">
+      <c r="C527" s="9" t="inlineStr">
         <is>
           <t>xn-001</t>
         </is>
       </c>
-      <c r="D528" s="9" t="inlineStr">
+      <c r="D527" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E528" s="9" t="inlineStr">
+      <c r="E527" s="9" t="inlineStr">
         <is>
           <t>性能与数据边界
 测试</t>
         </is>
       </c>
-      <c r="F528" s="9" t="inlineStr">
+      <c r="F527" s="9" t="inlineStr">
         <is>
           <t>验证订单列表10000+条数据的分页加载性能</t>
         </is>
       </c>
-      <c r="G528" s="9" t="inlineStr">
+      <c r="G527" s="9" t="inlineStr">
         <is>
           <t>1. 系统中已有10000+条订单数据</t>
         </is>
       </c>
-      <c r="H528" s="9" t="inlineStr">
+      <c r="H527" s="9" t="inlineStr">
         <is>
           <t>1. 打开管理后台订单列表。
 2. 记录首页加载时间。
@@ -23628,7 +23598,7 @@
 5. 导出报表</t>
         </is>
       </c>
-      <c r="I528" s="9" t="inlineStr">
+      <c r="I527" s="9" t="inlineStr">
         <is>
           <t>1. 首页加载时间&lt;3秒。
 2. 翻页响应&lt;2秒。
@@ -23636,9 +23606,54 @@
 4. 导出不超时（大数据量可异步导出）</t>
         </is>
       </c>
-      <c r="J528" s="9" t="inlineStr">
+      <c r="J527" s="9" t="inlineStr">
         <is>
           <t>生产环境数据量会持续增长</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="8" t="inlineStr"/>
+      <c r="B528" s="8" t="inlineStr"/>
+      <c r="C528" s="8" t="inlineStr">
+        <is>
+          <t>xn-002</t>
+        </is>
+      </c>
+      <c r="D528" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E528" s="8" t="n"/>
+      <c r="F528" s="8" t="inlineStr">
+        <is>
+          <t>验证佣金明细10000+条记录的展示性能</t>
+        </is>
+      </c>
+      <c r="G528" s="8" t="inlineStr">
+        <is>
+          <t>1. 某代理商有10000+条佣金明细记录</t>
+        </is>
+      </c>
+      <c r="H528" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户端查看佣金明细列表。
+2. 滚动加载更多。
+3. 检查总金额汇总的准确性</t>
+        </is>
+      </c>
+      <c r="I528" s="8" t="inlineStr">
+        <is>
+          <t>1. 首屏加载&lt;2秒。
+2. 滚动加载新数据&lt;1秒。
+3. 总金额汇总准确（与后台一致）。
+4. 不出现内存溢出/页面卡死</t>
+        </is>
+      </c>
+      <c r="J528" s="8" t="inlineStr">
+        <is>
+          <t>小程序内存有限，大数据量需注意</t>
         </is>
       </c>
     </row>
@@ -23647,43 +23662,43 @@
       <c r="B529" s="8" t="inlineStr"/>
       <c r="C529" s="8" t="inlineStr">
         <is>
-          <t>xn-002</t>
+          <t>xn-003</t>
         </is>
       </c>
       <c r="D529" s="8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E529" s="8" t="n"/>
       <c r="F529" s="8" t="inlineStr">
         <is>
-          <t>验证佣金明细10000+条记录的展示性能</t>
+          <t>验证选品仓库批量操作100+条数据的性能</t>
         </is>
       </c>
       <c r="G529" s="8" t="inlineStr">
         <is>
-          <t>1. 某代理商有10000+条佣金明细记录</t>
+          <t>1. 选品仓库中有100+条商品</t>
         </is>
       </c>
       <c r="H529" s="8" t="inlineStr">
         <is>
-          <t>1. 用户端查看佣金明细列表。
-2. 滚动加载更多。
-3. 检查总金额汇总的准确性</t>
+          <t>1. 全选100+条商品。
+2. 执行批量上架。
+3. 记录操作响应时间。
+4. 验证所有商品状态变更正确</t>
         </is>
       </c>
       <c r="I529" s="8" t="inlineStr">
         <is>
-          <t>1. 首屏加载&lt;2秒。
-2. 滚动加载新数据&lt;1秒。
-3. 总金额汇总准确（与后台一致）。
-4. 不出现内存溢出/页面卡死</t>
+          <t>1. 批量操作响应&lt;5秒。
+2. 所有100+条商品状态正确变更。
+3. 不出现部分成功部分失败（或有明确提示）</t>
         </is>
       </c>
       <c r="J529" s="8" t="inlineStr">
         <is>
-          <t>小程序内存有限，大数据量需注意</t>
+          <t>批量操作的性能基线</t>
         </is>
       </c>
     </row>
@@ -23692,7 +23707,7 @@
       <c r="B530" s="8" t="inlineStr"/>
       <c r="C530" s="8" t="inlineStr">
         <is>
-          <t>xn-003</t>
+          <t>xn-004</t>
         </is>
       </c>
       <c r="D530" s="8" t="inlineStr">
@@ -23703,60 +23718,15 @@
       <c r="E530" s="8" t="n"/>
       <c r="F530" s="8" t="inlineStr">
         <is>
-          <t>验证选品仓库批量操作100+条数据的性能</t>
+          <t>验证长文本输入的展示边界</t>
         </is>
       </c>
       <c r="G530" s="8" t="inlineStr">
         <is>
-          <t>1. 选品仓库中有100+条商品</t>
+          <t>1. 管理后台已登录</t>
         </is>
       </c>
       <c r="H530" s="8" t="inlineStr">
-        <is>
-          <t>1. 全选100+条商品。
-2. 执行批量上架。
-3. 记录操作响应时间。
-4. 验证所有商品状态变更正确</t>
-        </is>
-      </c>
-      <c r="I530" s="8" t="inlineStr">
-        <is>
-          <t>1. 批量操作响应&lt;5秒。
-2. 所有100+条商品状态正确变更。
-3. 不出现部分成功部分失败（或有明确提示）</t>
-        </is>
-      </c>
-      <c r="J530" s="8" t="inlineStr">
-        <is>
-          <t>批量操作的性能基线</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" s="8" t="inlineStr"/>
-      <c r="B531" s="8" t="inlineStr"/>
-      <c r="C531" s="8" t="inlineStr">
-        <is>
-          <t>xn-004</t>
-        </is>
-      </c>
-      <c r="D531" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E531" s="8" t="n"/>
-      <c r="F531" s="8" t="inlineStr">
-        <is>
-          <t>验证长文本输入的展示边界</t>
-        </is>
-      </c>
-      <c r="G531" s="8" t="inlineStr">
-        <is>
-          <t>1. 管理后台已登录</t>
-        </is>
-      </c>
-      <c r="H531" s="8" t="inlineStr">
         <is>
           <t>1. 商家名称输入200个字符，保存。
 2. 退款原因输入1000字，提交。
@@ -23764,7 +23734,7 @@
 4. 在各端查看这些长文本的展示</t>
         </is>
       </c>
-      <c r="I531" s="8" t="inlineStr">
+      <c r="I530" s="8" t="inlineStr">
         <is>
           <t>1. 长商家名称：保存成功或提示长度限制。
 2. 长退款原因：保存成功或提示长度限制。
@@ -23772,41 +23742,41 @@
 4. 超长文本有截断+展开/收起</t>
         </is>
       </c>
-      <c r="J531" s="8" t="inlineStr">
+      <c r="J530" s="8" t="inlineStr">
         <is>
           <t>防止长文本破坏UI布局</t>
         </is>
       </c>
     </row>
-    <row r="532">
-      <c r="A532" s="8" t="inlineStr">
+    <row r="531">
+      <c r="A531" s="8" t="inlineStr">
         <is>
           <t>用户端</t>
         </is>
       </c>
-      <c r="B532" s="8" t="inlineStr"/>
-      <c r="C532" s="8" t="inlineStr">
+      <c r="B531" s="8" t="inlineStr"/>
+      <c r="C531" s="8" t="inlineStr">
         <is>
           <t>xn-005</t>
         </is>
       </c>
-      <c r="D532" s="8" t="inlineStr">
+      <c r="D531" s="8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E532" s="8" t="n"/>
-      <c r="F532" s="8" t="inlineStr">
+      <c r="E531" s="8" t="n"/>
+      <c r="F531" s="8" t="inlineStr">
         <is>
           <t>验证小程序首页正常网络加载性能</t>
         </is>
       </c>
-      <c r="G532" s="8" t="inlineStr">
+      <c r="G531" s="8" t="inlineStr">
         <is>
           <t>正常WiFi/4G网络环境</t>
         </is>
       </c>
-      <c r="H532" s="8" t="inlineStr">
+      <c r="H531" s="8" t="inlineStr">
         <is>
           <t>1. 冷启动小程序（杀掉进程后重新打开）。
 2. 使用Chrome DevTools Performance面板记录。
@@ -23814,7 +23784,7 @@
 4. 重复3次取平均值</t>
         </is>
       </c>
-      <c r="I532" s="8" t="inlineStr">
+      <c r="I531" s="8" t="inlineStr">
         <is>
           <t>1. 首屏加载时间&lt;2秒。
 2. 图片懒加载正常。
@@ -23822,100 +23792,100 @@
 4. JS错误控制台无报错</t>
         </is>
       </c>
-      <c r="J532" s="8" t="inlineStr">
+      <c r="J531" s="8" t="inlineStr">
         <is>
           <t>性能验收标准：正常网络&lt;2秒</t>
         </is>
       </c>
     </row>
-    <row r="533">
-      <c r="A533" s="8" t="inlineStr">
+    <row r="532">
+      <c r="A532" s="8" t="inlineStr">
         <is>
           <t>用户端</t>
         </is>
       </c>
-      <c r="B533" s="8" t="inlineStr"/>
-      <c r="C533" s="8" t="inlineStr">
+      <c r="B532" s="8" t="inlineStr"/>
+      <c r="C532" s="8" t="inlineStr">
         <is>
           <t>xn-006</t>
         </is>
       </c>
-      <c r="D533" s="8" t="inlineStr">
+      <c r="D532" s="8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E533" s="8" t="n"/>
-      <c r="F533" s="8" t="inlineStr">
+      <c r="E532" s="8" t="n"/>
+      <c r="F532" s="8" t="inlineStr">
         <is>
           <t>验证支付响应时间在3秒以内</t>
         </is>
       </c>
-      <c r="G533" s="8" t="inlineStr">
+      <c r="G532" s="8" t="inlineStr">
         <is>
           <t>1. 通用券订单已确认
 2. 正常网络环境</t>
         </is>
       </c>
-      <c r="H533" s="8" t="inlineStr">
+      <c r="H532" s="8" t="inlineStr">
         <is>
           <t>1. 点击支付按钮开始计时。
 2. 到支付结果展示停止计时。
 3. 重复5次取平均值</t>
         </is>
       </c>
-      <c r="I533" s="8" t="inlineStr">
+      <c r="I532" s="8" t="inlineStr">
         <is>
           <t>1. 从点击支付到结果展示&lt;3秒。
 2. 支付过程有loading提示。
 3. 不出现"支付成功但页面无反应"的情况</t>
         </is>
       </c>
-      <c r="J533" s="8" t="inlineStr">
+      <c r="J532" s="8" t="inlineStr">
         <is>
           <t>性能验收标准：支付响应&lt;3秒</t>
         </is>
       </c>
     </row>
-    <row r="534">
-      <c r="A534" s="9" t="inlineStr">
+    <row r="533">
+      <c r="A533" s="9" t="inlineStr">
         <is>
           <t>管理后台</t>
         </is>
       </c>
-      <c r="B534" s="9" t="inlineStr">
+      <c r="B533" s="9" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="C534" s="9" t="inlineStr">
+      <c r="C533" s="9" t="inlineStr">
         <is>
           <t>excel-001</t>
         </is>
       </c>
-      <c r="D534" s="9" t="inlineStr">
+      <c r="D533" s="9" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E534" s="9" t="inlineStr">
+      <c r="E533" s="9" t="inlineStr">
         <is>
           <t>Excel佣金导入
 (完整测试)</t>
         </is>
       </c>
-      <c r="F534" s="9" t="inlineStr">
+      <c r="F533" s="9" t="inlineStr">
         <is>
           <t>验证正常Excel佣金导入后分佣自动计算</t>
         </is>
       </c>
-      <c r="G534" s="9" t="inlineStr">
+      <c r="G533" s="9" t="inlineStr">
         <is>
           <t>1. 准备正常Excel文件（含用户ID/订单金额/佣金金额）
 2. 分佣比例已配置</t>
         </is>
       </c>
-      <c r="H534" s="9" t="inlineStr">
+      <c r="H533" s="9" t="inlineStr">
         <is>
           <t>1. 上传正常Excel文件。
 2. 确认导入。
@@ -23924,7 +23894,7 @@
 5. 验证分佣按比例计算</t>
         </is>
       </c>
-      <c r="I534" s="9" t="inlineStr">
+      <c r="I533" s="9" t="inlineStr">
         <is>
           <t>1. 导入成功，提示"成功导入X条"。
 2. 佣金数据正确入库。
@@ -23932,9 +23902,51 @@
 4. 不扣除成本，直接按导入佣金分</t>
         </is>
       </c>
-      <c r="J534" s="9" t="inlineStr">
+      <c r="J533" s="9" t="inlineStr">
         <is>
           <t>CPS类业务的佣金来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="8" t="inlineStr"/>
+      <c r="B534" s="8" t="inlineStr"/>
+      <c r="C534" s="8" t="inlineStr">
+        <is>
+          <t>excel-002</t>
+        </is>
+      </c>
+      <c r="D534" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E534" s="8" t="n"/>
+      <c r="F534" s="8" t="inlineStr">
+        <is>
+          <t>验证空Excel文件导入的错误提示</t>
+        </is>
+      </c>
+      <c r="G534" s="8" t="inlineStr">
+        <is>
+          <t>准备一个空Excel文件（只有表头无数据）</t>
+        </is>
+      </c>
+      <c r="H534" s="8" t="inlineStr">
+        <is>
+          <t>1. 上传空Excel文件。
+2. 点击导入</t>
+        </is>
+      </c>
+      <c r="I534" s="8" t="inlineStr">
+        <is>
+          <t>1. 提示"文件无数据"。
+2. 不产生任何导入记录</t>
+        </is>
+      </c>
+      <c r="J534" s="8" t="inlineStr">
+        <is>
+          <t>空文件校验</t>
         </is>
       </c>
     </row>
@@ -23943,7 +23955,7 @@
       <c r="B535" s="8" t="inlineStr"/>
       <c r="C535" s="8" t="inlineStr">
         <is>
-          <t>excel-002</t>
+          <t>excel-003</t>
         </is>
       </c>
       <c r="D535" s="8" t="inlineStr">
@@ -23954,29 +23966,29 @@
       <c r="E535" s="8" t="n"/>
       <c r="F535" s="8" t="inlineStr">
         <is>
-          <t>验证空Excel文件导入的错误提示</t>
+          <t>验证Excel缺少必填列的错误提示</t>
         </is>
       </c>
       <c r="G535" s="8" t="inlineStr">
         <is>
-          <t>准备一个空Excel文件（只有表头无数据）</t>
+          <t>准备Excel文件，缺少"佣金金额"列</t>
         </is>
       </c>
       <c r="H535" s="8" t="inlineStr">
         <is>
-          <t>1. 上传空Excel文件。
+          <t>1. 上传缺列Excel文件。
 2. 点击导入</t>
         </is>
       </c>
       <c r="I535" s="8" t="inlineStr">
         <is>
-          <t>1. 提示"文件无数据"。
+          <t>1. 提示"缺少必要字段：佣金金额"。
 2. 不产生任何导入记录</t>
         </is>
       </c>
       <c r="J535" s="8" t="inlineStr">
         <is>
-          <t>空文件校验</t>
+          <t>模板校验</t>
         </is>
       </c>
     </row>
@@ -23985,7 +23997,7 @@
       <c r="B536" s="8" t="inlineStr"/>
       <c r="C536" s="8" t="inlineStr">
         <is>
-          <t>excel-003</t>
+          <t>excel-004</t>
         </is>
       </c>
       <c r="D536" s="8" t="inlineStr">
@@ -23996,29 +24008,32 @@
       <c r="E536" s="8" t="n"/>
       <c r="F536" s="8" t="inlineStr">
         <is>
-          <t>验证Excel缺少必填列的错误提示</t>
+          <t>验证Excel中用户ID不存在时部分成功处理</t>
         </is>
       </c>
       <c r="G536" s="8" t="inlineStr">
         <is>
-          <t>准备Excel文件，缺少"佣金金额"列</t>
+          <t>准备Excel：5条数据，其中2条的用户ID在系统中不存在</t>
         </is>
       </c>
       <c r="H536" s="8" t="inlineStr">
         <is>
-          <t>1. 上传缺列Excel文件。
-2. 点击导入</t>
+          <t>1. 上传Excel。
+2. 点击导入。
+3. 检查导入结果</t>
         </is>
       </c>
       <c r="I536" s="8" t="inlineStr">
         <is>
-          <t>1. 提示"缺少必要字段：佣金金额"。
-2. 不产生任何导入记录</t>
+          <t>1. 提示"成功3条，失败2条"。
+2. 存在的3个用户佣金正确入库。
+3. 不存在的2条标记失败并显示原因。
+4. 可下载失败记录明细</t>
         </is>
       </c>
       <c r="J536" s="8" t="inlineStr">
         <is>
-          <t>模板校验</t>
+          <t>部分成功部分失败的处理</t>
         </is>
       </c>
     </row>
@@ -24027,7 +24042,7 @@
       <c r="B537" s="8" t="inlineStr"/>
       <c r="C537" s="8" t="inlineStr">
         <is>
-          <t>excel-004</t>
+          <t>excel-005</t>
         </is>
       </c>
       <c r="D537" s="8" t="inlineStr">
@@ -24038,32 +24053,32 @@
       <c r="E537" s="8" t="n"/>
       <c r="F537" s="8" t="inlineStr">
         <is>
-          <t>验证Excel中用户ID不存在时部分成功处理</t>
+          <t>验证Excel佣金为负数/0/超大值的校验</t>
         </is>
       </c>
       <c r="G537" s="8" t="inlineStr">
         <is>
-          <t>准备Excel：5条数据，其中2条的用户ID在系统中不存在</t>
+          <t>准备Excel：佣金分别为-10、0、999999999</t>
         </is>
       </c>
       <c r="H537" s="8" t="inlineStr">
         <is>
-          <t>1. 上传Excel。
+          <t>1. 上传含异常佣金的Excel。
 2. 点击导入。
-3. 检查导入结果</t>
+3. 检查各行结果</t>
         </is>
       </c>
       <c r="I537" s="8" t="inlineStr">
         <is>
-          <t>1. 提示"成功3条，失败2条"。
-2. 存在的3个用户佣金正确入库。
-3. 不存在的2条标记失败并显示原因。
-4. 可下载失败记录明细</t>
+          <t>1. 佣金为负数：该行标记失败"佣金不能为负数"。
+2. 佣金为0：待确认是否允许。
+3. 佣金超大值：该行标记失败或有上限提示。
+4. 正常行不受影响</t>
         </is>
       </c>
       <c r="J537" s="8" t="inlineStr">
         <is>
-          <t>部分成功部分失败的处理</t>
+          <t>佣金数据的边界校验</t>
         </is>
       </c>
     </row>
@@ -24072,7 +24087,7 @@
       <c r="B538" s="8" t="inlineStr"/>
       <c r="C538" s="8" t="inlineStr">
         <is>
-          <t>excel-005</t>
+          <t>excel-006</t>
         </is>
       </c>
       <c r="D538" s="8" t="inlineStr">
@@ -24083,32 +24098,31 @@
       <c r="E538" s="8" t="n"/>
       <c r="F538" s="8" t="inlineStr">
         <is>
-          <t>验证Excel佣金为负数/0/超大值的校验</t>
+          <t>验证非Excel格式文件上传的拦截</t>
         </is>
       </c>
       <c r="G538" s="8" t="inlineStr">
         <is>
-          <t>准备Excel：佣金分别为-10、0、999999999</t>
+          <t>准备.txt文件和.pdf文件</t>
         </is>
       </c>
       <c r="H538" s="8" t="inlineStr">
         <is>
-          <t>1. 上传含异常佣金的Excel。
-2. 点击导入。
-3. 检查各行结果</t>
+          <t>1. 尝试上传.txt文件。
+2. 尝试上传.pdf文件。
+3. 尝试上传.csv文件</t>
         </is>
       </c>
       <c r="I538" s="8" t="inlineStr">
         <is>
-          <t>1. 佣金为负数：该行标记失败"佣金不能为负数"。
-2. 佣金为0：待确认是否允许。
-3. 佣金超大值：该行标记失败或有上限提示。
-4. 正常行不受影响</t>
+          <t>1. .txt文件：提示"请上传Excel格式文件（.xlsx/.xls）"。
+2. .pdf文件：同上提示。
+3. .csv文件：待确认是否支持</t>
         </is>
       </c>
       <c r="J538" s="8" t="inlineStr">
         <is>
-          <t>佣金数据的边界校验</t>
+          <t>文件格式校验</t>
         </is>
       </c>
     </row>
@@ -24117,7 +24131,7 @@
       <c r="B539" s="8" t="inlineStr"/>
       <c r="C539" s="8" t="inlineStr">
         <is>
-          <t>excel-006</t>
+          <t>excel-007</t>
         </is>
       </c>
       <c r="D539" s="8" t="inlineStr">
@@ -24128,67 +24142,23 @@
       <c r="E539" s="8" t="n"/>
       <c r="F539" s="8" t="inlineStr">
         <is>
-          <t>验证非Excel格式文件上传的拦截</t>
+          <t>验证重复导入同一Excel的处理</t>
         </is>
       </c>
       <c r="G539" s="8" t="inlineStr">
-        <is>
-          <t>准备.txt文件和.pdf文件</t>
-        </is>
-      </c>
-      <c r="H539" s="8" t="inlineStr">
-        <is>
-          <t>1. 尝试上传.txt文件。
-2. 尝试上传.pdf文件。
-3. 尝试上传.csv文件</t>
-        </is>
-      </c>
-      <c r="I539" s="8" t="inlineStr">
-        <is>
-          <t>1. .txt文件：提示"请上传Excel格式文件（.xlsx/.xls）"。
-2. .pdf文件：同上提示。
-3. .csv文件：待确认是否支持</t>
-        </is>
-      </c>
-      <c r="J539" s="8" t="inlineStr">
-        <is>
-          <t>文件格式校验</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" s="8" t="inlineStr"/>
-      <c r="B540" s="8" t="inlineStr"/>
-      <c r="C540" s="8" t="inlineStr">
-        <is>
-          <t>excel-007</t>
-        </is>
-      </c>
-      <c r="D540" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E540" s="8" t="n"/>
-      <c r="F540" s="8" t="inlineStr">
-        <is>
-          <t>验证重复导入同一Excel的处理</t>
-        </is>
-      </c>
-      <c r="G540" s="8" t="inlineStr">
         <is>
           <t>1. 已成功导入一份Excel
 2. 再次上传同一份Excel</t>
         </is>
       </c>
-      <c r="H540" s="8" t="inlineStr">
+      <c r="H539" s="8" t="inlineStr">
         <is>
           <t>1. 第一次导入成功。
 2. 再次上传同一份Excel。
 3. 点击导入</t>
         </is>
       </c>
-      <c r="I540" s="8" t="inlineStr">
+      <c r="I539" s="8" t="inlineStr">
         <is>
           <t>1. 提示"以下数据已存在"。
 2. 提供选项：覆盖/跳过/取消。
@@ -24196,51 +24166,51 @@
 4. 选择覆盖：更新已存在的数据</t>
         </is>
       </c>
-      <c r="J540" s="8" t="inlineStr">
+      <c r="J539" s="8" t="inlineStr">
         <is>
           <t>防止重复导入</t>
         </is>
       </c>
     </row>
-    <row r="541">
-      <c r="A541" s="9" t="inlineStr">
+    <row r="540">
+      <c r="A540" s="9" t="inlineStr">
         <is>
           <t>管理后台</t>
         </is>
       </c>
-      <c r="B541" s="9" t="inlineStr">
+      <c r="B540" s="9" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="C541" s="9" t="inlineStr">
+      <c r="C540" s="9" t="inlineStr">
         <is>
           <t>bf-001</t>
         </is>
       </c>
-      <c r="D541" s="9" t="inlineStr">
+      <c r="D540" s="9" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E541" s="9" t="inlineStr">
+      <c r="E540" s="9" t="inlineStr">
         <is>
           <t>并发场景
 增强测试</t>
         </is>
       </c>
-      <c r="F541" s="9" t="inlineStr">
+      <c r="F540" s="9" t="inlineStr">
         <is>
           <t>验证多运营并发审核同一人工辅助订单</t>
         </is>
       </c>
-      <c r="G541" s="9" t="inlineStr">
+      <c r="G540" s="9" t="inlineStr">
         <is>
           <t>1. 2个运营管理员账号同时在线
 2. 1笔待审核的人工辅助订单</t>
         </is>
       </c>
-      <c r="H541" s="9" t="inlineStr">
+      <c r="H540" s="9" t="inlineStr">
         <is>
           <t>1. 运营A打开该订单审核页面。
 2. 运营B也打开同一订单审核页面。
@@ -24249,7 +24219,7 @@
 5. 检查结果</t>
         </is>
       </c>
-      <c r="I541" s="9" t="inlineStr">
+      <c r="I540" s="9" t="inlineStr">
         <is>
           <t>1. 运营A操作成功。
 2. 运营B提示"该订单已被审核"或操作失败。
@@ -24257,9 +24227,55 @@
 4. 不出现重复验证码</t>
         </is>
       </c>
-      <c r="J541" s="9" t="inlineStr">
+      <c r="J540" s="9" t="inlineStr">
         <is>
           <t>并发审核是常见业务场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="8" t="inlineStr"/>
+      <c r="B541" s="8" t="inlineStr"/>
+      <c r="C541" s="8" t="inlineStr">
+        <is>
+          <t>bf-002</t>
+        </is>
+      </c>
+      <c r="D541" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E541" s="8" t="n"/>
+      <c r="F541" s="8" t="inlineStr">
+        <is>
+          <t>验证FAIL状态下重试发货和退款的互斥性</t>
+        </is>
+      </c>
+      <c r="G541" s="8" t="inlineStr">
+        <is>
+          <t>1. 一笔通用券订单处于FAIL状态
+2. 2个运营在线</t>
+        </is>
+      </c>
+      <c r="H541" s="8" t="inlineStr">
+        <is>
+          <t>1. 运营A点击"重试发货"。
+2. 运营B几乎同时点击"退款"。
+3. 检查最终结果</t>
+        </is>
+      </c>
+      <c r="I541" s="8" t="inlineStr">
+        <is>
+          <t>1. 只有一个操作成功。
+2. 重试中退款按钮自动置灰（或反之）。
+3. 不出现"重试成功同时又退款"的矛盾状态。
+4. 最终订单状态唯一确定</t>
+        </is>
+      </c>
+      <c r="J541" s="8" t="inlineStr">
+        <is>
+          <t>互斥操作的并发控制</t>
         </is>
       </c>
     </row>
@@ -24268,44 +24284,43 @@
       <c r="B542" s="8" t="inlineStr"/>
       <c r="C542" s="8" t="inlineStr">
         <is>
-          <t>bf-002</t>
+          <t>bf-003</t>
         </is>
       </c>
       <c r="D542" s="8" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E542" s="8" t="n"/>
       <c r="F542" s="8" t="inlineStr">
         <is>
-          <t>验证FAIL状态下重试发货和退款的互斥性</t>
+          <t>验证高并发轮询模式下渠道分配均匀性</t>
         </is>
       </c>
       <c r="G542" s="8" t="inlineStr">
         <is>
-          <t>1. 一笔通用券订单处于FAIL状态
-2. 2个运营在线</t>
+          <t>1. 外卖红包配置为轮询模式
+2. 3个渠道（美赚/聚推客/凡点）</t>
         </is>
       </c>
       <c r="H542" s="8" t="inlineStr">
         <is>
-          <t>1. 运营A点击"重试发货"。
-2. 运营B几乎同时点击"退款"。
-3. 检查最终结果</t>
+          <t>1. 模拟100次并发请求外卖红包跳转。
+2. 统计各渠道被分配的次数。
+3. 验证均匀性</t>
         </is>
       </c>
       <c r="I542" s="8" t="inlineStr">
         <is>
-          <t>1. 只有一个操作成功。
-2. 重试中退款按钮自动置灰（或反之）。
-3. 不出现"重试成功同时又退款"的矛盾状态。
-4. 最终订单状态唯一确定</t>
+          <t>1. 100次请求中：美赚约33次、聚推客约34次、凡点约33次。
+2. 偏差不超过±3。
+3. 无请求失败</t>
         </is>
       </c>
       <c r="J542" s="8" t="inlineStr">
         <is>
-          <t>互斥操作的并发控制</t>
+          <t>使用JMeter或脚本模拟</t>
         </is>
       </c>
     </row>
@@ -24314,7 +24329,7 @@
       <c r="B543" s="8" t="inlineStr"/>
       <c r="C543" s="8" t="inlineStr">
         <is>
-          <t>bf-003</t>
+          <t>bf-004</t>
         </is>
       </c>
       <c r="D543" s="8" t="inlineStr">
@@ -24325,68 +24340,23 @@
       <c r="E543" s="8" t="n"/>
       <c r="F543" s="8" t="inlineStr">
         <is>
-          <t>验证高并发轮询模式下渠道分配均匀性</t>
+          <t>验证同一订单多处同时发起退款的处理</t>
         </is>
       </c>
       <c r="G543" s="8" t="inlineStr">
-        <is>
-          <t>1. 外卖红包配置为轮询模式
-2. 3个渠道（美赚/聚推客/凡点）</t>
-        </is>
-      </c>
-      <c r="H543" s="8" t="inlineStr">
-        <is>
-          <t>1. 模拟100次并发请求外卖红包跳转。
-2. 统计各渠道被分配的次数。
-3. 验证均匀性</t>
-        </is>
-      </c>
-      <c r="I543" s="8" t="inlineStr">
-        <is>
-          <t>1. 100次请求中：美赚约33次、聚推客约34次、凡点约33次。
-2. 偏差不超过±3。
-3. 无请求失败</t>
-        </is>
-      </c>
-      <c r="J543" s="8" t="inlineStr">
-        <is>
-          <t>使用JMeter或脚本模拟</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" s="8" t="inlineStr"/>
-      <c r="B544" s="8" t="inlineStr"/>
-      <c r="C544" s="8" t="inlineStr">
-        <is>
-          <t>bf-004</t>
-        </is>
-      </c>
-      <c r="D544" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E544" s="8" t="n"/>
-      <c r="F544" s="8" t="inlineStr">
-        <is>
-          <t>验证同一订单多处同时发起退款的处理</t>
-        </is>
-      </c>
-      <c r="G544" s="8" t="inlineStr">
         <is>
           <t>1. 一笔餐饮扫码已完成订单
 2. 用户端和商家端同时打开该订单</t>
         </is>
       </c>
-      <c r="H544" s="8" t="inlineStr">
+      <c r="H543" s="8" t="inlineStr">
         <is>
           <t>1. 用户在用户端发起退款申请。
 2. 商家几乎同时在商家端发起退款。
 3. 检查退款结果</t>
         </is>
       </c>
-      <c r="I544" s="8" t="inlineStr">
+      <c r="I543" s="8" t="inlineStr">
         <is>
           <t>1. 只有一方退款申请成功提交。
 2. 另一方提示"该订单已有退款申请"。
@@ -24394,151 +24364,151 @@
 4. 退款金额正确</t>
         </is>
       </c>
-      <c r="J544" s="8" t="inlineStr">
+      <c r="J543" s="8" t="inlineStr">
         <is>
           <t>多端同时操作的并发控制</t>
         </is>
       </c>
     </row>
-    <row r="545">
-      <c r="A545" s="9" t="inlineStr">
+    <row r="544">
+      <c r="A544" s="9" t="inlineStr">
         <is>
           <t>用户端</t>
         </is>
       </c>
-      <c r="B545" s="9" t="inlineStr">
+      <c r="B544" s="9" t="inlineStr">
         <is>
           <t>0.5h</t>
         </is>
       </c>
-      <c r="C545" s="9" t="inlineStr">
+      <c r="C544" s="9" t="inlineStr">
         <is>
           <t>jycz-006</t>
         </is>
       </c>
-      <c r="D545" s="9" t="inlineStr">
+      <c r="D544" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E545" s="9" t="inlineStr">
+      <c r="E544" s="9" t="inlineStr">
         <is>
           <t>加油/充电
 (环境异常补充)</t>
         </is>
       </c>
-      <c r="F545" s="9" t="inlineStr">
+      <c r="F544" s="9" t="inlineStr">
         <is>
           <t>验证加油/充电模块GPS关闭时的处理</t>
         </is>
       </c>
-      <c r="G545" s="9" t="inlineStr">
+      <c r="G544" s="9" t="inlineStr">
         <is>
           <t>1. 用户设备GPS已关闭</t>
         </is>
       </c>
-      <c r="H545" s="9" t="inlineStr">
+      <c r="H544" s="9" t="inlineStr">
         <is>
           <t>1. 点击"加油/充电"入口。
 2. 系统请求位置权限。
 3. 用户拒绝授权或GPS关闭</t>
         </is>
       </c>
-      <c r="I545" s="9" t="inlineStr">
+      <c r="I544" s="9" t="inlineStr">
         <is>
           <t>1. 提示"需要获取位置权限，请在设置中开启"。
 2. 提供跳转设置的按钮。
 3. 不出现白屏或崩溃</t>
         </is>
       </c>
-      <c r="J545" s="9" t="inlineStr">
+      <c r="J544" s="9" t="inlineStr">
         <is>
           <t>与打车模块类似的定位场景</t>
         </is>
       </c>
     </row>
-    <row r="546">
-      <c r="A546" s="8" t="inlineStr"/>
-      <c r="B546" s="8" t="inlineStr"/>
-      <c r="C546" s="8" t="inlineStr">
+    <row r="545">
+      <c r="A545" s="8" t="inlineStr"/>
+      <c r="B545" s="8" t="inlineStr"/>
+      <c r="C545" s="8" t="inlineStr">
         <is>
           <t>jycz-007</t>
         </is>
       </c>
-      <c r="D546" s="8" t="inlineStr">
+      <c r="D545" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E546" s="8" t="n"/>
-      <c r="F546" s="8" t="inlineStr">
+      <c r="E545" s="8" t="n"/>
+      <c r="F545" s="8" t="inlineStr">
         <is>
           <t>验证加油/充电列表在弱网下的加载表现</t>
         </is>
       </c>
-      <c r="G546" s="8" t="inlineStr">
+      <c r="G545" s="8" t="inlineStr">
         <is>
           <t>弱网环境（3G模拟）</t>
         </is>
       </c>
-      <c r="H546" s="8" t="inlineStr">
+      <c r="H545" s="8" t="inlineStr">
         <is>
           <t>1. 在弱网下进入加油/充电列表。
 2. 观察加载过程。
 3. 下拉刷新</t>
         </is>
       </c>
-      <c r="I546" s="8" t="inlineStr">
+      <c r="I545" s="8" t="inlineStr">
         <is>
           <t>1. 有loading提示。
 2. 5秒内加载完成或有超时提示。
 3. 不白屏</t>
         </is>
       </c>
-      <c r="J546" s="8" t="inlineStr">
+      <c r="J545" s="8" t="inlineStr">
         <is>
           <t>弱网场景覆盖</t>
         </is>
       </c>
     </row>
-    <row r="547">
-      <c r="A547" s="9" t="inlineStr">
+    <row r="546">
+      <c r="A546" s="9" t="inlineStr">
         <is>
           <t>用户端</t>
         </is>
       </c>
-      <c r="B547" s="9" t="inlineStr">
+      <c r="B546" s="9" t="inlineStr">
         <is>
           <t>0.5h</t>
         </is>
       </c>
-      <c r="C547" s="9" t="inlineStr">
+      <c r="C546" s="9" t="inlineStr">
         <is>
           <t>gwfl-026</t>
         </is>
       </c>
-      <c r="D547" s="9" t="inlineStr">
+      <c r="D546" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E547" s="9" t="inlineStr">
+      <c r="E546" s="9" t="inlineStr">
         <is>
           <t>购物返利
 (环境异常补充)</t>
         </is>
       </c>
-      <c r="F547" s="9" t="inlineStr">
+      <c r="F546" s="9" t="inlineStr">
         <is>
           <t>验证粘贴商品链接在不同手机系统的剪贴板兼容性</t>
         </is>
       </c>
-      <c r="G547" s="9" t="inlineStr">
+      <c r="G546" s="9" t="inlineStr">
         <is>
           <t>1. 分别在iOS和Android设备上操作</t>
         </is>
       </c>
-      <c r="H547" s="9" t="inlineStr">
+      <c r="H546" s="9" t="inlineStr">
         <is>
           <t>1. 在淘宝App复制商品链接。
 2. 切换到快乐羊毛小程序。
@@ -24546,102 +24516,102 @@
 4. 检查是否正确识别</t>
         </is>
       </c>
-      <c r="I547" s="9" t="inlineStr">
+      <c r="I546" s="9" t="inlineStr">
         <is>
           <t>1. iOS：剪贴板内容正确粘贴并识别。
 2. Android：剪贴板内容正确粘贴并识别。
 3. 链接解析正确，生成专属推广链接</t>
         </is>
       </c>
-      <c r="J547" s="9" t="inlineStr">
+      <c r="J546" s="9" t="inlineStr">
         <is>
           <t>iOS和Android剪贴板机制有差异</t>
         </is>
       </c>
     </row>
-    <row r="548">
-      <c r="A548" s="8" t="inlineStr"/>
-      <c r="B548" s="8" t="inlineStr"/>
-      <c r="C548" s="8" t="inlineStr">
+    <row r="547">
+      <c r="A547" s="8" t="inlineStr"/>
+      <c r="B547" s="8" t="inlineStr"/>
+      <c r="C547" s="8" t="inlineStr">
         <is>
           <t>gwfl-027</t>
         </is>
       </c>
-      <c r="D548" s="8" t="inlineStr">
+      <c r="D547" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E548" s="8" t="n"/>
-      <c r="F548" s="8" t="inlineStr">
+      <c r="E547" s="8" t="n"/>
+      <c r="F547" s="8" t="inlineStr">
         <is>
           <t>验证购物返利授权绑定流程在不同系统的表现</t>
         </is>
       </c>
-      <c r="G548" s="8" t="inlineStr">
+      <c r="G547" s="8" t="inlineStr">
         <is>
           <t>1. 首次使用购物返利功能
 2. 需要授权绑定淘宝/京东账号</t>
         </is>
       </c>
-      <c r="H548" s="8" t="inlineStr">
+      <c r="H547" s="8" t="inlineStr">
         <is>
           <t>1. 点击购物返利，触发授权绑定。
 2. 在iOS上完成淘宝账号授权。
 3. 在Android上完成京东账号授权</t>
         </is>
       </c>
-      <c r="I548" s="8" t="inlineStr">
+      <c r="I547" s="8" t="inlineStr">
         <is>
           <t>1. 授权弹窗正常显示。
 2. 授权流程正常完成。
 3. 绑定成功后返回小程序，状态正确</t>
         </is>
       </c>
-      <c r="J548" s="8" t="inlineStr">
+      <c r="J547" s="8" t="inlineStr">
         <is>
           <t>第三方授权在不同系统的兼容性</t>
         </is>
       </c>
     </row>
-    <row r="549">
-      <c r="A549" s="9" t="inlineStr">
+    <row r="548">
+      <c r="A548" s="9" t="inlineStr">
         <is>
           <t>用户端</t>
         </is>
       </c>
-      <c r="B549" s="9" t="inlineStr">
+      <c r="B548" s="9" t="inlineStr">
         <is>
           <t>0.5h</t>
         </is>
       </c>
-      <c r="C549" s="9" t="inlineStr">
+      <c r="C548" s="9" t="inlineStr">
         <is>
           <t>xxtz-013</t>
         </is>
       </c>
-      <c r="D549" s="9" t="inlineStr">
+      <c r="D548" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E549" s="9" t="inlineStr">
+      <c r="E548" s="9" t="inlineStr">
         <is>
           <t>消息通知
 (环境异常补充)</t>
         </is>
       </c>
-      <c r="F549" s="9" t="inlineStr">
+      <c r="F548" s="9" t="inlineStr">
         <is>
           <t>验证用户未授权订阅消息时不影响正常业务流程</t>
         </is>
       </c>
-      <c r="G549" s="9" t="inlineStr">
+      <c r="G548" s="9" t="inlineStr">
         <is>
           <t>1. 用户已拒绝小程序订阅消息授权</t>
         </is>
       </c>
-      <c r="H549" s="9" t="inlineStr">
+      <c r="H548" s="9" t="inlineStr">
         <is>
           <t>1. 完成一笔通用券购买。
 2. 检查订单状态是否正常。
@@ -24649,7 +24619,7 @@
 4. 检查短信是否作为备选发送</t>
         </is>
       </c>
-      <c r="I549" s="9" t="inlineStr">
+      <c r="I548" s="9" t="inlineStr">
         <is>
           <t>1. 订单正常完成，不因消息发送失败而阻塞。
 2. 降级为短信通知。
@@ -24657,37 +24627,37 @@
 4. 用户可在订单详情页查看信息</t>
         </is>
       </c>
-      <c r="J549" s="9" t="inlineStr">
+      <c r="J548" s="9" t="inlineStr">
         <is>
           <t>消息通知不能阻塞核心业务</t>
         </is>
       </c>
     </row>
-    <row r="550">
-      <c r="A550" s="8" t="inlineStr"/>
-      <c r="B550" s="8" t="inlineStr"/>
-      <c r="C550" s="8" t="inlineStr">
+    <row r="549">
+      <c r="A549" s="8" t="inlineStr"/>
+      <c r="B549" s="8" t="inlineStr"/>
+      <c r="C549" s="8" t="inlineStr">
         <is>
           <t>xxtz-014</t>
         </is>
       </c>
-      <c r="D550" s="8" t="inlineStr">
+      <c r="D549" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E550" s="8" t="n"/>
-      <c r="F550" s="8" t="inlineStr">
+      <c r="E549" s="8" t="n"/>
+      <c r="F549" s="8" t="inlineStr">
         <is>
           <t>验证消息通知内容在iOS和Android上的展示一致性</t>
         </is>
       </c>
-      <c r="G550" s="8" t="inlineStr">
+      <c r="G549" s="8" t="inlineStr">
         <is>
           <t>1. 分别在iOS和Android设备上接收消息通知</t>
         </is>
       </c>
-      <c r="H550" s="8" t="inlineStr">
+      <c r="H549" s="8" t="inlineStr">
         <is>
           <t>1. 触发一笔订单完成通知。
 2. 在iOS上查看订阅消息内容。
@@ -24695,74 +24665,66 @@
 4. 对比两端内容</t>
         </is>
       </c>
-      <c r="I550" s="8" t="inlineStr">
+      <c r="I549" s="8" t="inlineStr">
         <is>
           <t>1. 两端消息内容一致。
 2. 金额、订单号等字段完整。
 3. 不出现截断或乱码</t>
         </is>
       </c>
-      <c r="J550" s="8" t="inlineStr">
+      <c r="J549" s="8" t="inlineStr">
         <is>
           <t>跨平台消息内容一致性</t>
         </is>
       </c>
     </row>
+    <row r="550"/>
+    <row r="551">
+      <c r="A551" s="13" t="inlineStr">
+        <is>
+          <t>═══ 微信小程序环境专项测试 ═══ 生命周期 / 授权 / 转发分享 / 版本更新 / 缓存 / 前后台切换 ═══</t>
+        </is>
+      </c>
+    </row>
     <row r="552">
-      <c r="A552" s="13" t="inlineStr">
-        <is>
-          <t>═══ 微信小程序环境专项测试 ═══ 生命周期 / 授权 / 转发分享 / 版本更新 / 缓存 / 前后台切换 ═══</t>
-        </is>
-      </c>
-      <c r="B552" s="14" t="n"/>
-      <c r="C552" s="14" t="n"/>
-      <c r="D552" s="14" t="n"/>
-      <c r="E552" s="14" t="n"/>
-      <c r="F552" s="14" t="n"/>
-      <c r="G552" s="14" t="n"/>
-      <c r="H552" s="14" t="n"/>
-      <c r="I552" s="14" t="n"/>
-      <c r="J552" s="14" t="n"/>
-    </row>
-    <row r="553">
-      <c r="A553" s="9" t="inlineStr">
+      <c r="A552" s="9" t="inlineStr">
         <is>
           <t>用户端</t>
         </is>
       </c>
-      <c r="B553" s="9" t="inlineStr">
+      <c r="B552" s="9" t="inlineStr">
         <is>
           <t>1.5h</t>
         </is>
       </c>
-      <c r="C553" s="9" t="inlineStr">
+      <c r="C552" s="9" t="inlineStr">
         <is>
           <t>xcx-sm-001</t>
         </is>
       </c>
-      <c r="D553" s="9" t="inlineStr">
+      <c r="D552" s="9" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E553" s="9" t="inlineStr">
+      <c r="E552" s="9" t="inlineStr">
         <is>
           <t>小程序环境
 (生命周期/启动)</t>
         </is>
       </c>
-      <c r="F553" s="9" t="inlineStr">
+      <c r="F552" s="9" t="inlineStr">
         <is>
           <t>验证小程序冷启动正常加载</t>
         </is>
       </c>
-      <c r="G553" s="9" t="inlineStr">
+      <c r="G552" s="9" t="inlineStr">
         <is>
           <t>1. 小程序未在微信后台运行
 2. 用户已有微信登录态</t>
         </is>
       </c>
-      <c r="H553" s="9" t="inlineStr">
+      <c r="H552" s="9" t="inlineStr">
         <is>
           <t>1. 在微信中搜索或扫码打开快乐羊毛小程序。
 2. 观察启动过程（闪屏/loading）。
@@ -24770,7 +24732,7 @@
 4. 检查首页数据是否完整加载</t>
         </is>
       </c>
-      <c r="I553" s="9" t="inlineStr">
+      <c r="I552" s="9" t="inlineStr">
         <is>
           <t>1. 启动过程有品牌闪屏（如有配置）。
 2. 首屏渲染&lt;2秒（WiFi）/&lt;5秒（4G）。
@@ -24778,38 +24740,38 @@
 4. 用户登录态自动恢复（微信静默登录）</t>
         </is>
       </c>
-      <c r="J553" s="9" t="inlineStr">
+      <c r="J552" s="9" t="inlineStr">
         <is>
           <t>冷启动是用户最常遇到的入口场景</t>
         </is>
       </c>
     </row>
-    <row r="554">
-      <c r="A554" s="8" t="inlineStr"/>
-      <c r="B554" s="8" t="inlineStr"/>
-      <c r="C554" s="8" t="inlineStr">
+    <row r="553">
+      <c r="A553" s="8" t="inlineStr"/>
+      <c r="B553" s="8" t="inlineStr"/>
+      <c r="C553" s="8" t="inlineStr">
         <is>
           <t>xcx-sm-002</t>
         </is>
       </c>
-      <c r="D554" s="8" t="inlineStr">
+      <c r="D553" s="8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E554" s="8" t="n"/>
-      <c r="F554" s="8" t="inlineStr">
+      <c r="E553" s="8" t="n"/>
+      <c r="F553" s="8" t="inlineStr">
         <is>
           <t>验证小程序热启动（从后台恢复）数据状态保持</t>
         </is>
       </c>
-      <c r="G554" s="8" t="inlineStr">
+      <c r="G553" s="8" t="inlineStr">
         <is>
           <t>1. 小程序已打开且在某个页面（如订单列表页）
 2. 用户按Home键将小程序切到后台</t>
         </is>
       </c>
-      <c r="H554" s="8" t="inlineStr">
+      <c r="H553" s="8" t="inlineStr">
         <is>
           <t>1. 在订单列表页按Home键切换到微信聊天。
 2. 在微信中浏览其他内容1分钟。
@@ -24817,7 +24779,7 @@
 4. 检查页面状态</t>
         </is>
       </c>
-      <c r="I554" s="8" t="inlineStr">
+      <c r="I553" s="8" t="inlineStr">
         <is>
           <t>1. 小程序从后台恢复，不重新加载（热启动）。
 2. 页面保持在订单列表页。
@@ -24826,9 +24788,56 @@
 5. 如有实时数据可下拉刷新更新</t>
         </is>
       </c>
+      <c r="J553" s="8" t="inlineStr">
+        <is>
+          <t>热启动应保持页面状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="8" t="inlineStr"/>
+      <c r="B554" s="8" t="inlineStr"/>
+      <c r="C554" s="8" t="inlineStr">
+        <is>
+          <t>xcx-sm-003</t>
+        </is>
+      </c>
+      <c r="D554" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E554" s="8" t="n"/>
+      <c r="F554" s="8" t="inlineStr">
+        <is>
+          <t>验证小程序被微信回收后再次打开的恢复</t>
+        </is>
+      </c>
+      <c r="G554" s="8" t="inlineStr">
+        <is>
+          <t>1. 小程序已打开
+2. 模拟内存不足被微信回收（打开多个其他小程序挤占内存）</t>
+        </is>
+      </c>
+      <c r="H554" s="8" t="inlineStr">
+        <is>
+          <t>1. 打开快乐羊毛小程序，停在订单页。
+2. 连续打开5-10个其他小程序，消耗内存。
+3. 回到快乐羊毛小程序。
+4. 观察启动行为</t>
+        </is>
+      </c>
+      <c r="I554" s="8" t="inlineStr">
+        <is>
+          <t>1. 小程序重新加载（冷启动行为）。
+2. 用户登录态自动恢复。
+3. 不出现报错或白屏。
+4. 数据重新加载完整</t>
+        </is>
+      </c>
       <c r="J554" s="8" t="inlineStr">
         <is>
-          <t>热启动应保持页面状态</t>
+          <t>内存回收后小程序会被销毁，需重启</t>
         </is>
       </c>
     </row>
@@ -24837,7 +24846,7 @@
       <c r="B555" s="8" t="inlineStr"/>
       <c r="C555" s="8" t="inlineStr">
         <is>
-          <t>xcx-sm-003</t>
+          <t>xcx-sm-004</t>
         </is>
       </c>
       <c r="D555" s="8" t="inlineStr">
@@ -24848,34 +24857,34 @@
       <c r="E555" s="8" t="n"/>
       <c r="F555" s="8" t="inlineStr">
         <is>
-          <t>验证小程序被微信回收后再次打开的恢复</t>
+          <t>验证小程序前后台切换期间定时器/倒计时的准确性</t>
         </is>
       </c>
       <c r="G555" s="8" t="inlineStr">
         <is>
-          <t>1. 小程序已打开
-2. 模拟内存不足被微信回收（打开多个其他小程序挤占内存）</t>
+          <t>1. 商家端生成了一个收款二维码
+2. 二维码有15分钟超时倒计时</t>
         </is>
       </c>
       <c r="H555" s="8" t="inlineStr">
         <is>
-          <t>1. 打开快乐羊毛小程序，停在订单页。
-2. 连续打开5-10个其他小程序，消耗内存。
-3. 回到快乐羊毛小程序。
-4. 观察启动行为</t>
+          <t>1. 生成二维码，开始15分钟倒计时。
+2. 将小程序切到后台5分钟。
+3. 切回小程序。
+4. 检查倒计时是否正确（应显示约10分钟）</t>
         </is>
       </c>
       <c r="I555" s="8" t="inlineStr">
         <is>
-          <t>1. 小程序重新加载（冷启动行为）。
-2. 用户登录态自动恢复。
-3. 不出现报错或白屏。
-4. 数据重新加载完整</t>
+          <t>1. 切回后倒计时正确更新（显示约10分钟）。
+2. 不因后台运行暂停而显示错误时间。
+3. 到期后正确触发超时逻辑。
+4. 如小程序被回收重启，倒计时从服务端获取</t>
         </is>
       </c>
       <c r="J555" s="8" t="inlineStr">
         <is>
-          <t>内存回收后小程序会被销毁，需重启</t>
+          <t>后台运行时JS定时器可能暂停</t>
         </is>
       </c>
     </row>
@@ -24884,73 +24893,26 @@
       <c r="B556" s="8" t="inlineStr"/>
       <c r="C556" s="8" t="inlineStr">
         <is>
-          <t>xcx-sm-004</t>
+          <t>xcx-sm-005</t>
         </is>
       </c>
       <c r="D556" s="8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E556" s="8" t="n"/>
       <c r="F556" s="8" t="inlineStr">
         <is>
-          <t>验证小程序前后台切换期间定时器/倒计时的准确性</t>
+          <t>验证小程序从不同入口启动的页面路由正确</t>
         </is>
       </c>
       <c r="G556" s="8" t="inlineStr">
         <is>
-          <t>1. 商家端生成了一个收款二维码
-2. 二维码有15分钟超时倒计时</t>
+          <t>微信不同入口</t>
         </is>
       </c>
       <c r="H556" s="8" t="inlineStr">
-        <is>
-          <t>1. 生成二维码，开始15分钟倒计时。
-2. 将小程序切到后台5分钟。
-3. 切回小程序。
-4. 检查倒计时是否正确（应显示约10分钟）</t>
-        </is>
-      </c>
-      <c r="I556" s="8" t="inlineStr">
-        <is>
-          <t>1. 切回后倒计时正确更新（显示约10分钟）。
-2. 不因后台运行暂停而显示错误时间。
-3. 到期后正确触发超时逻辑。
-4. 如小程序被回收重启，倒计时从服务端获取</t>
-        </is>
-      </c>
-      <c r="J556" s="8" t="inlineStr">
-        <is>
-          <t>后台运行时JS定时器可能暂停</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" s="8" t="inlineStr"/>
-      <c r="B557" s="8" t="inlineStr"/>
-      <c r="C557" s="8" t="inlineStr">
-        <is>
-          <t>xcx-sm-005</t>
-        </is>
-      </c>
-      <c r="D557" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E557" s="8" t="n"/>
-      <c r="F557" s="8" t="inlineStr">
-        <is>
-          <t>验证小程序从不同入口启动的页面路由正确</t>
-        </is>
-      </c>
-      <c r="G557" s="8" t="inlineStr">
-        <is>
-          <t>微信不同入口</t>
-        </is>
-      </c>
-      <c r="H557" s="8" t="inlineStr">
         <is>
           <t>1. 从微信"发现-小程序"入口进入 → 首页。
 2. 从微信聊天分享卡片进入 → 分享的目标页面。
@@ -24959,7 +24921,7 @@
 5. 从微信搜索进入 → 首页</t>
         </is>
       </c>
-      <c r="I557" s="8" t="inlineStr">
+      <c r="I556" s="8" t="inlineStr">
         <is>
           <t>1. 各入口均能正常启动小程序。
 2. 从分享卡片进入直达分享页面，不回到首页。
@@ -24968,51 +24930,51 @@
 5. 搜索进入首页</t>
         </is>
       </c>
-      <c r="J557" s="8" t="inlineStr">
+      <c r="J556" s="8" t="inlineStr">
         <is>
           <t>小程序多入口场景是常见的</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="A558" s="9" t="inlineStr">
+    <row r="557">
+      <c r="A557" s="9" t="inlineStr">
         <is>
           <t>用户端</t>
         </is>
       </c>
-      <c r="B558" s="9" t="inlineStr">
+      <c r="B557" s="9" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="C558" s="9" t="inlineStr">
+      <c r="C557" s="9" t="inlineStr">
         <is>
           <t>xcx-sq-001</t>
         </is>
       </c>
-      <c r="D558" s="9" t="inlineStr">
+      <c r="D557" s="9" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E558" s="9" t="inlineStr">
+      <c r="E557" s="9" t="inlineStr">
         <is>
           <t>小程序环境
 (微信授权/登录)</t>
         </is>
       </c>
-      <c r="F558" s="9" t="inlineStr">
+      <c r="F557" s="9" t="inlineStr">
         <is>
           <t>验证微信一键登录（获取手机号）首次授权流程</t>
         </is>
       </c>
-      <c r="G558" s="9" t="inlineStr">
+      <c r="G557" s="9" t="inlineStr">
         <is>
           <t>1. 用户首次打开小程序
 2. 未注册过账号</t>
         </is>
       </c>
-      <c r="H558" s="9" t="inlineStr">
+      <c r="H557" s="9" t="inlineStr">
         <is>
           <t>1. 打开小程序，触发登录流程。
 2. 弹出"获取手机号"授权弹窗。
@@ -25020,7 +24982,7 @@
 4. 检查注册结果</t>
         </is>
       </c>
-      <c r="I558" s="9" t="inlineStr">
+      <c r="I557" s="9" t="inlineStr">
         <is>
           <t>1. 授权弹窗正常显示（微信原生弹窗）。
 2. 点击允许后获取手机号成功。
@@ -25028,9 +24990,55 @@
 4. 个人中心显示脱敏手机号</t>
         </is>
       </c>
-      <c r="J558" s="9" t="inlineStr">
+      <c r="J557" s="9" t="inlineStr">
         <is>
           <t>微信授权是小程序特有的登录方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="8" t="inlineStr"/>
+      <c r="B558" s="8" t="inlineStr"/>
+      <c r="C558" s="8" t="inlineStr">
+        <is>
+          <t>xcx-sq-003</t>
+        </is>
+      </c>
+      <c r="D558" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E558" s="8" t="n"/>
+      <c r="F558" s="8" t="inlineStr">
+        <is>
+          <t>验证微信session_key过期后静默刷新</t>
+        </is>
+      </c>
+      <c r="G558" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户已登录
+2. session_key已过期（模拟或长时间不使用）</t>
+        </is>
+      </c>
+      <c r="H558" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户长时间未使用小程序（&gt;30分钟）后重新打开。
+2. 尝试执行需要登录的操作（如下单）。
+3. 观察是否需要重新授权</t>
+        </is>
+      </c>
+      <c r="I558" s="8" t="inlineStr">
+        <is>
+          <t>1. 系统自动调用wx.checkSession()检测session状态。
+2. session过期时自动调用wx.login()静默刷新。
+3. 用户无感知，不弹出授权弹窗。
+4. 操作正常继续</t>
+        </is>
+      </c>
+      <c r="J558" s="8" t="inlineStr">
+        <is>
+          <t>微信小程序session管理的特殊性</t>
         </is>
       </c>
     </row>
@@ -25039,119 +25047,26 @@
       <c r="B559" s="8" t="inlineStr"/>
       <c r="C559" s="8" t="inlineStr">
         <is>
-          <t>xcx-sq-002</t>
+          <t>xcx-sq-004</t>
         </is>
       </c>
       <c r="D559" s="8" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E559" s="8" t="n"/>
       <c r="F559" s="8" t="inlineStr">
         <is>
-          <t>验证用户拒绝手机号授权后的处理</t>
+          <t>验证微信位置授权流程（打车/加油模块）</t>
         </is>
       </c>
       <c r="G559" s="8" t="inlineStr">
         <is>
-          <t>1. 用户首次打开小程序
-2. 准备拒绝授权</t>
+          <t>1. 用户首次使用打车或加油/充电功能</t>
         </is>
       </c>
       <c r="H559" s="8" t="inlineStr">
-        <is>
-          <t>1. 触发登录流程。
-2. 弹出手机号授权弹窗。
-3. 点击"拒绝"。
-4. 观察后续处理</t>
-        </is>
-      </c>
-      <c r="I559" s="8" t="inlineStr">
-        <is>
-          <t>1. 提示"需要授权手机号才能使用完整功能"。
-2. 提供重新授权入口/按钮。
-3. 不出现白屏或崩溃。
-4. 部分功能可浏览（如免费资料区），下单等核心功能需登录</t>
-        </is>
-      </c>
-      <c r="J559" s="8" t="inlineStr">
-        <is>
-          <t>必须有优雅的拒绝授权降级方案</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" s="8" t="inlineStr"/>
-      <c r="B560" s="8" t="inlineStr"/>
-      <c r="C560" s="8" t="inlineStr">
-        <is>
-          <t>xcx-sq-003</t>
-        </is>
-      </c>
-      <c r="D560" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E560" s="8" t="n"/>
-      <c r="F560" s="8" t="inlineStr">
-        <is>
-          <t>验证微信session_key过期后静默刷新</t>
-        </is>
-      </c>
-      <c r="G560" s="8" t="inlineStr">
-        <is>
-          <t>1. 用户已登录
-2. session_key已过期（模拟或长时间不使用）</t>
-        </is>
-      </c>
-      <c r="H560" s="8" t="inlineStr">
-        <is>
-          <t>1. 用户长时间未使用小程序（&gt;30分钟）后重新打开。
-2. 尝试执行需要登录的操作（如下单）。
-3. 观察是否需要重新授权</t>
-        </is>
-      </c>
-      <c r="I560" s="8" t="inlineStr">
-        <is>
-          <t>1. 系统自动调用wx.checkSession()检测session状态。
-2. session过期时自动调用wx.login()静默刷新。
-3. 用户无感知，不弹出授权弹窗。
-4. 操作正常继续</t>
-        </is>
-      </c>
-      <c r="J560" s="8" t="inlineStr">
-        <is>
-          <t>微信小程序session管理的特殊性</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" s="8" t="inlineStr"/>
-      <c r="B561" s="8" t="inlineStr"/>
-      <c r="C561" s="8" t="inlineStr">
-        <is>
-          <t>xcx-sq-004</t>
-        </is>
-      </c>
-      <c r="D561" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E561" s="8" t="n"/>
-      <c r="F561" s="8" t="inlineStr">
-        <is>
-          <t>验证微信位置授权流程（打车/加油模块）</t>
-        </is>
-      </c>
-      <c r="G561" s="8" t="inlineStr">
-        <is>
-          <t>1. 用户首次使用打车或加油/充电功能</t>
-        </is>
-      </c>
-      <c r="H561" s="8" t="inlineStr">
         <is>
           <t>1. 点击"打车服务"。
 2. 弹出微信位置授权弹窗。
@@ -25160,7 +25075,7 @@
 5. 拒绝授权后的处理</t>
         </is>
       </c>
-      <c r="I561" s="8" t="inlineStr">
+      <c r="I559" s="8" t="inlineStr">
         <is>
           <t>1. 允许授权后正确获取当前位置。
 2. 拒绝授权后提示需要位置权限+跳转设置引导。
@@ -25168,45 +25083,45 @@
 4. 不因授权拒绝导致页面异常</t>
         </is>
       </c>
-      <c r="J561" s="8" t="inlineStr">
+      <c r="J559" s="8" t="inlineStr">
         <is>
           <t>位置授权是微信小程序的特殊权限</t>
         </is>
       </c>
     </row>
-    <row r="562">
-      <c r="A562" s="8" t="inlineStr"/>
-      <c r="B562" s="8" t="inlineStr"/>
-      <c r="C562" s="8" t="inlineStr">
+    <row r="560">
+      <c r="A560" s="8" t="inlineStr"/>
+      <c r="B560" s="8" t="inlineStr"/>
+      <c r="C560" s="8" t="inlineStr">
         <is>
           <t>xcx-sq-005</t>
         </is>
       </c>
-      <c r="D562" s="8" t="inlineStr">
+      <c r="D560" s="8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E562" s="8" t="n"/>
-      <c r="F562" s="8" t="inlineStr">
+      <c r="E560" s="8" t="n"/>
+      <c r="F560" s="8" t="inlineStr">
         <is>
           <t>验证用户在微信设置中取消小程序授权后的处理</t>
         </is>
       </c>
-      <c r="G562" s="8" t="inlineStr">
+      <c r="G560" s="8" t="inlineStr">
         <is>
           <t>1. 用户已授权手机号和位置
 2. 在微信"设置-隐私-授权管理"中取消快乐羊毛小程序的授权</t>
         </is>
       </c>
-      <c r="H562" s="8" t="inlineStr">
+      <c r="H560" s="8" t="inlineStr">
         <is>
           <t>1. 取消手机号授权。
 2. 重新打开小程序。
 3. 尝试下单等需要登录的操作</t>
         </is>
       </c>
-      <c r="I562" s="8" t="inlineStr">
+      <c r="I560" s="8" t="inlineStr">
         <is>
           <t>1. 检测到授权被撤销。
 2. 重新弹出授权请求。
@@ -25214,51 +25129,51 @@
 4. 不出现"已登录但无法获取用户信息"的矛盾状态</t>
         </is>
       </c>
-      <c r="J562" s="8" t="inlineStr">
+      <c r="J560" s="8" t="inlineStr">
         <is>
           <t>用户可随时撤销授权——小程序必须处理</t>
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" s="9" t="inlineStr">
+    <row r="561">
+      <c r="A561" s="9" t="inlineStr">
         <is>
           <t>用户端</t>
         </is>
       </c>
-      <c r="B563" s="9" t="inlineStr">
+      <c r="B561" s="9" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="C563" s="9" t="inlineStr">
+      <c r="C561" s="9" t="inlineStr">
         <is>
           <t>xcx-fx-001</t>
         </is>
       </c>
-      <c r="D563" s="9" t="inlineStr">
+      <c r="D561" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E563" s="9" t="inlineStr">
+      <c r="E561" s="9" t="inlineStr">
         <is>
           <t>小程序环境
 (转发/分享)</t>
         </is>
       </c>
-      <c r="F563" s="9" t="inlineStr">
+      <c r="F561" s="9" t="inlineStr">
         <is>
           <t>验证小程序转发分享卡片到微信好友</t>
         </is>
       </c>
-      <c r="G563" s="9" t="inlineStr">
+      <c r="G561" s="9" t="inlineStr">
         <is>
           <t>1. 用户已打开小程序
 2. 在某个可分享的页面</t>
         </is>
       </c>
-      <c r="H563" s="9" t="inlineStr">
+      <c r="H561" s="9" t="inlineStr">
         <is>
           <t>1. 点击小程序右上角"..."菜单。
 2. 选择"转发"。
@@ -25267,7 +25182,7 @@
 5. 检查进入的页面</t>
         </is>
       </c>
-      <c r="I563" s="9" t="inlineStr">
+      <c r="I561" s="9" t="inlineStr">
         <is>
           <t>1. 分享卡片正常显示（标题/描述/封面图）。
 2. 卡片发送成功。
@@ -25275,38 +25190,38 @@
 4. 页面数据正确加载</t>
         </is>
       </c>
-      <c r="J563" s="9" t="inlineStr">
+      <c r="J561" s="9" t="inlineStr">
         <is>
           <t>分享是小程序获客核心渠道</t>
         </is>
       </c>
     </row>
-    <row r="564">
-      <c r="A564" s="8" t="inlineStr"/>
-      <c r="B564" s="8" t="inlineStr"/>
-      <c r="C564" s="8" t="inlineStr">
+    <row r="562">
+      <c r="A562" s="8" t="inlineStr"/>
+      <c r="B562" s="8" t="inlineStr"/>
+      <c r="C562" s="8" t="inlineStr">
         <is>
           <t>xcx-fx-002</t>
         </is>
       </c>
-      <c r="D564" s="8" t="inlineStr">
+      <c r="D562" s="8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E564" s="8" t="n"/>
-      <c r="F564" s="8" t="inlineStr">
+      <c r="E562" s="8" t="n"/>
+      <c r="F562" s="8" t="inlineStr">
         <is>
           <t>验证推广海报保存到相册（需相册授权）</t>
         </is>
       </c>
-      <c r="G564" s="8" t="inlineStr">
+      <c r="G562" s="8" t="inlineStr">
         <is>
           <t>1. 用户在推广中心
 2. 已生成推广海报</t>
         </is>
       </c>
-      <c r="H564" s="8" t="inlineStr">
+      <c r="H562" s="8" t="inlineStr">
         <is>
           <t>1. 点击"保存到相册"。
 2. 首次弹出相册写入授权弹窗。
@@ -25314,7 +25229,7 @@
 4. 检查相册中是否有海报图片</t>
         </is>
       </c>
-      <c r="I564" s="8" t="inlineStr">
+      <c r="I562" s="8" t="inlineStr">
         <is>
           <t>1. 授权弹窗正常显示。
 2. 允许后海报成功保存到相册。
@@ -25323,38 +25238,38 @@
 5. 拒绝授权时提示引导</t>
         </is>
       </c>
-      <c r="J564" s="8" t="inlineStr">
+      <c r="J562" s="8" t="inlineStr">
         <is>
           <t>小程序保存图片需要相册权限</t>
         </is>
       </c>
     </row>
-    <row r="565">
-      <c r="A565" s="8" t="inlineStr"/>
-      <c r="B565" s="8" t="inlineStr"/>
-      <c r="C565" s="8" t="inlineStr">
+    <row r="563">
+      <c r="A563" s="8" t="inlineStr"/>
+      <c r="B563" s="8" t="inlineStr"/>
+      <c r="C563" s="8" t="inlineStr">
         <is>
           <t>xcx-fx-003</t>
         </is>
       </c>
-      <c r="D565" s="8" t="inlineStr">
+      <c r="D563" s="8" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E565" s="8" t="n"/>
-      <c r="F565" s="8" t="inlineStr">
+      <c r="E563" s="8" t="n"/>
+      <c r="F563" s="8" t="inlineStr">
         <is>
           <t>验证分享带参二维码（推广追踪）</t>
         </is>
       </c>
-      <c r="G565" s="8" t="inlineStr">
+      <c r="G563" s="8" t="inlineStr">
         <is>
           <t>1. 分销员A生成推广海报
 2. 海报包含个人专属二维码</t>
         </is>
       </c>
-      <c r="H565" s="8" t="inlineStr">
+      <c r="H563" s="8" t="inlineStr">
         <is>
           <t>1. 分销员A将推广海报分享给潜在用户B。
 2. 用户B长按海报中的二维码识别进入小程序。
@@ -25362,7 +25277,7 @@
 4. 检查分销员A的推广记录</t>
         </is>
       </c>
-      <c r="I565" s="8" t="inlineStr">
+      <c r="I563" s="8" t="inlineStr">
         <is>
           <t>1. 用户B扫码后正确进入小程序。
 2. 用户B的注册绑定到分销员A名下。
@@ -25370,37 +25285,37 @@
 4. 用户B的订单产生的佣金正确归属分销员A</t>
         </is>
       </c>
-      <c r="J565" s="8" t="inlineStr">
+      <c r="J563" s="8" t="inlineStr">
         <is>
           <t>分销推广的核心链路——参数追踪</t>
         </is>
       </c>
     </row>
-    <row r="566">
-      <c r="A566" s="8" t="inlineStr"/>
-      <c r="B566" s="8" t="inlineStr"/>
-      <c r="C566" s="8" t="inlineStr">
+    <row r="564">
+      <c r="A564" s="8" t="inlineStr"/>
+      <c r="B564" s="8" t="inlineStr"/>
+      <c r="C564" s="8" t="inlineStr">
         <is>
           <t>xcx-fx-004</t>
         </is>
       </c>
-      <c r="D566" s="8" t="inlineStr">
+      <c r="D564" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E566" s="8" t="n"/>
-      <c r="F566" s="8" t="inlineStr">
+      <c r="E564" s="8" t="n"/>
+      <c r="F564" s="8" t="inlineStr">
         <is>
           <t>验证小程序分享到朋友圈（如有配置）</t>
         </is>
       </c>
-      <c r="G566" s="8" t="inlineStr">
+      <c r="G564" s="8" t="inlineStr">
         <is>
           <t>用户在小程序中</t>
         </is>
       </c>
-      <c r="H566" s="8" t="inlineStr">
+      <c r="H564" s="8" t="inlineStr">
         <is>
           <t>1. 点击右上角"..."。
 2. 查看是否有"分享到朋友圈"选项。
@@ -25408,7 +25323,7 @@
 4. 他人从朋友圈进入</t>
         </is>
       </c>
-      <c r="I566" s="8" t="inlineStr">
+      <c r="I564" s="8" t="inlineStr">
         <is>
           <t>1. 分享到朋友圈功能正常（如已启用）。
 2. 朋友圈展示正确（标题/封面）。
@@ -25416,51 +25331,51 @@
 4. 单页模式下核心信息可见</t>
         </is>
       </c>
-      <c r="J566" s="8" t="inlineStr">
+      <c r="J564" s="8" t="inlineStr">
         <is>
           <t>朋友圈分享是小程序的"单页模式"，功能受限</t>
         </is>
       </c>
     </row>
-    <row r="567">
-      <c r="A567" s="9" t="inlineStr">
+    <row r="565">
+      <c r="A565" s="9" t="inlineStr">
         <is>
           <t>用户端</t>
         </is>
       </c>
-      <c r="B567" s="9" t="inlineStr">
+      <c r="B565" s="9" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="C567" s="9" t="inlineStr">
+      <c r="C565" s="9" t="inlineStr">
         <is>
           <t>xcx-zf-001</t>
         </is>
       </c>
-      <c r="D567" s="9" t="inlineStr">
+      <c r="D565" s="9" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E567" s="9" t="inlineStr">
+      <c r="E565" s="9" t="inlineStr">
         <is>
           <t>小程序环境
 (微信支付专项)</t>
         </is>
       </c>
-      <c r="F567" s="9" t="inlineStr">
+      <c r="F565" s="9" t="inlineStr">
         <is>
           <t>验证微信支付弹窗正常唤起与完成</t>
         </is>
       </c>
-      <c r="G567" s="9" t="inlineStr">
+      <c r="G565" s="9" t="inlineStr">
         <is>
           <t>1. 用户已确认订单（通用券）
 2. 微信有足够余额/已绑定银行卡</t>
         </is>
       </c>
-      <c r="H567" s="9" t="inlineStr">
+      <c r="H565" s="9" t="inlineStr">
         <is>
           <t>1. 点击"确认支付"。
 2. 微信支付弹窗唤起。
@@ -25468,7 +25383,7 @@
 4. 支付完成</t>
         </is>
       </c>
-      <c r="I567" s="9" t="inlineStr">
+      <c r="I565" s="9" t="inlineStr">
         <is>
           <t>1. 支付弹窗在1秒内唤起。
 2. 显示正确的支付金额。
@@ -25477,9 +25392,101 @@
 5. 展示支付成功结果</t>
         </is>
       </c>
-      <c r="J567" s="9" t="inlineStr">
+      <c r="J565" s="9" t="inlineStr">
         <is>
           <t>微信支付是小程序核心能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="8" t="inlineStr"/>
+      <c r="B566" s="8" t="inlineStr"/>
+      <c r="C566" s="8" t="inlineStr">
+        <is>
+          <t>xcx-zf-002</t>
+        </is>
+      </c>
+      <c r="D566" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E566" s="8" t="n"/>
+      <c r="F566" s="8" t="inlineStr">
+        <is>
+          <t>验证微信支付密码输错后的处理</t>
+        </is>
+      </c>
+      <c r="G566" s="8" t="inlineStr">
+        <is>
+          <t>1. 支付弹窗已唤起</t>
+        </is>
+      </c>
+      <c r="H566" s="8" t="inlineStr">
+        <is>
+          <t>1. 输入错误的支付密码。
+2. 微信提示密码错误。
+3. 重新输入正确密码。
+4. 完成支付</t>
+        </is>
+      </c>
+      <c r="I566" s="8" t="inlineStr">
+        <is>
+          <t>1. 微信提示"支付密码错误"。
+2. 可以重新输入密码。
+3. 重新输入正确密码后支付成功。
+4. 不影响订单状态（仍为"待支付"直到成功）</t>
+        </is>
+      </c>
+      <c r="J566" s="8" t="inlineStr">
+        <is>
+          <t>密码输错是常见场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="8" t="inlineStr"/>
+      <c r="B567" s="8" t="inlineStr"/>
+      <c r="C567" s="8" t="inlineStr">
+        <is>
+          <t>xcx-zf-003</t>
+        </is>
+      </c>
+      <c r="D567" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E567" s="8" t="n"/>
+      <c r="F567" s="8" t="inlineStr">
+        <is>
+          <t>验证微信支付弹窗取消后的处理</t>
+        </is>
+      </c>
+      <c r="G567" s="8" t="inlineStr">
+        <is>
+          <t>1. 支付弹窗已唤起</t>
+        </is>
+      </c>
+      <c r="H567" s="8" t="inlineStr">
+        <is>
+          <t>1. 点击支付弹窗的"取消"或点击空白区域关闭。
+2. 回到小程序。
+3. 检查订单状态。
+4. 尝试重新支付</t>
+        </is>
+      </c>
+      <c r="I567" s="8" t="inlineStr">
+        <is>
+          <t>1. 返回小程序后订单状态为"待支付"。
+2. 可重新点击支付按钮再次唤起支付。
+3. 不产生重复订单。
+4. 超时前可多次尝试支付</t>
+        </is>
+      </c>
+      <c r="J567" s="8" t="inlineStr">
+        <is>
+          <t>用户可能多次取消后再支付</t>
         </is>
       </c>
     </row>
@@ -25488,90 +25495,103 @@
       <c r="B568" s="8" t="inlineStr"/>
       <c r="C568" s="8" t="inlineStr">
         <is>
-          <t>xcx-zf-002</t>
+          <t>xcx-zf-004</t>
         </is>
       </c>
       <c r="D568" s="8" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E568" s="8" t="n"/>
       <c r="F568" s="8" t="inlineStr">
         <is>
-          <t>验证微信支付密码输错后的处理</t>
+          <t>验证微信未绑定银行卡时的支付处理</t>
         </is>
       </c>
       <c r="G568" s="8" t="inlineStr">
         <is>
-          <t>1. 支付弹窗已唤起</t>
+          <t>1. 测试微信号未绑定银行卡且余额不足</t>
         </is>
       </c>
       <c r="H568" s="8" t="inlineStr">
         <is>
-          <t>1. 输入错误的支付密码。
-2. 微信提示密码错误。
-3. 重新输入正确密码。
-4. 完成支付</t>
+          <t>1. 发起支付。
+2. 微信支付弹窗提示"余额不足"。
+3. 观察小程序行为</t>
         </is>
       </c>
       <c r="I568" s="8" t="inlineStr">
         <is>
-          <t>1. 微信提示"支付密码错误"。
-2. 可以重新输入密码。
-3. 重新输入正确密码后支付成功。
-4. 不影响订单状态（仍为"待支付"直到成功）</t>
+          <t>1. 微信提示绑定银行卡或充值。
+2. 用户选择取消后返回小程序。
+3. 订单状态"待支付"。
+4. 可在绑卡后重新支付</t>
         </is>
       </c>
       <c r="J568" s="8" t="inlineStr">
         <is>
-          <t>密码输错是常见场景</t>
+          <t>新用户可能未绑定银行卡</t>
         </is>
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="8" t="inlineStr"/>
-      <c r="B569" s="8" t="inlineStr"/>
-      <c r="C569" s="8" t="inlineStr">
-        <is>
-          <t>xcx-zf-003</t>
-        </is>
-      </c>
-      <c r="D569" s="8" t="inlineStr">
+      <c r="A569" s="9" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B569" s="9" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C569" s="9" t="inlineStr">
+        <is>
+          <t>xcx-hc-001</t>
+        </is>
+      </c>
+      <c r="D569" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E569" s="8" t="n"/>
-      <c r="F569" s="8" t="inlineStr">
-        <is>
-          <t>验证微信支付弹窗取消后的处理</t>
-        </is>
-      </c>
-      <c r="G569" s="8" t="inlineStr">
-        <is>
-          <t>1. 支付弹窗已唤起</t>
-        </is>
-      </c>
-      <c r="H569" s="8" t="inlineStr">
-        <is>
-          <t>1. 点击支付弹窗的"取消"或点击空白区域关闭。
-2. 回到小程序。
-3. 检查订单状态。
-4. 尝试重新支付</t>
-        </is>
-      </c>
-      <c r="I569" s="8" t="inlineStr">
-        <is>
-          <t>1. 返回小程序后订单状态为"待支付"。
-2. 可重新点击支付按钮再次唤起支付。
-3. 不产生重复订单。
-4. 超时前可多次尝试支付</t>
-        </is>
-      </c>
-      <c r="J569" s="8" t="inlineStr">
-        <is>
-          <t>用户可能多次取消后再支付</t>
+      <c r="E569" s="9" t="inlineStr">
+        <is>
+          <t>小程序环境
+(缓存/存储)</t>
+        </is>
+      </c>
+      <c r="F569" s="9" t="inlineStr">
+        <is>
+          <t>验证小程序本地缓存超限时的处理</t>
+        </is>
+      </c>
+      <c r="G569" s="9" t="inlineStr">
+        <is>
+          <t>1. 小程序已使用一段时间
+2. 微信小程序本地存储上限10MB</t>
+        </is>
+      </c>
+      <c r="H569" s="9" t="inlineStr">
+        <is>
+          <t>1. 模拟大量数据缓存（多次浏览/搜索/加载图片）。
+2. 当本地存储接近10MB时。
+3. 尝试新操作（如搜索、缓存新数据）。
+4. 检查是否有清理机制</t>
+        </is>
+      </c>
+      <c r="I569" s="9" t="inlineStr">
+        <is>
+          <t>1. 不因缓存满而崩溃。
+2. 有自动清理旧缓存的机制（LRU）。
+3. 核心数据（登录态/用户信息）优先保留。
+4. 即使缓存被清理，功能正常（从网络重新获取）</t>
+        </is>
+      </c>
+      <c r="J569" s="9" t="inlineStr">
+        <is>
+          <t>微信小程序本地存储限制10MB</t>
         </is>
       </c>
     </row>
@@ -25580,7 +25600,7 @@
       <c r="B570" s="8" t="inlineStr"/>
       <c r="C570" s="8" t="inlineStr">
         <is>
-          <t>xcx-zf-004</t>
+          <t>xcx-hc-002</t>
         </is>
       </c>
       <c r="D570" s="8" t="inlineStr">
@@ -25591,32 +25611,33 @@
       <c r="E570" s="8" t="n"/>
       <c r="F570" s="8" t="inlineStr">
         <is>
-          <t>验证微信未绑定银行卡时的支付处理</t>
+          <t>验证用户清除小程序数据后的恢复</t>
         </is>
       </c>
       <c r="G570" s="8" t="inlineStr">
         <is>
-          <t>1. 测试微信号未绑定银行卡且余额不足</t>
+          <t>1. 用户在微信设置中找到快乐羊毛小程序</t>
         </is>
       </c>
       <c r="H570" s="8" t="inlineStr">
         <is>
-          <t>1. 发起支付。
-2. 微信支付弹窗提示"余额不足"。
-3. 观察小程序行为</t>
+          <t>1. 在微信"发现-小程序"列表中长按快乐羊毛。
+2. 选择"删除"小程序。
+3. 重新搜索并打开快乐羊毛小程序。
+4. 检查数据状态</t>
         </is>
       </c>
       <c r="I570" s="8" t="inlineStr">
         <is>
-          <t>1. 微信提示绑定银行卡或充值。
-2. 用户选择取消后返回小程序。
-3. 订单状态"待支付"。
-4. 可在绑卡后重新支付</t>
+          <t>1. 删除后所有本地缓存被清空。
+2. 重新打开为冷启动。
+3. 需要重新授权登录。
+4. 登录后服务端数据完整（订单/佣金等不丢失）</t>
         </is>
       </c>
       <c r="J570" s="8" t="inlineStr">
         <is>
-          <t>新用户可能未绑定银行卡</t>
+          <t>删除小程序≠注销账号，服务端数据不丢</t>
         </is>
       </c>
     </row>
@@ -25633,7 +25654,7 @@
       </c>
       <c r="C571" s="9" t="inlineStr">
         <is>
-          <t>xcx-hc-001</t>
+          <t>xcx-gx-001</t>
         </is>
       </c>
       <c r="D571" s="9" t="inlineStr">
@@ -25644,39 +25665,38 @@
       <c r="E571" s="9" t="inlineStr">
         <is>
           <t>小程序环境
-(缓存/存储)</t>
+(版本更新)</t>
         </is>
       </c>
       <c r="F571" s="9" t="inlineStr">
         <is>
-          <t>验证小程序本地缓存超限时的处理</t>
+          <t>验证小程序版本更新提示与强制更新</t>
         </is>
       </c>
       <c r="G571" s="9" t="inlineStr">
         <is>
-          <t>1. 小程序已使用一段时间
-2. 微信小程序本地存储上限10MB</t>
+          <t>1. 当前小程序有新版本可用</t>
         </is>
       </c>
       <c r="H571" s="9" t="inlineStr">
         <is>
-          <t>1. 模拟大量数据缓存（多次浏览/搜索/加载图片）。
-2. 当本地存储接近10MB时。
-3. 尝试新操作（如搜索、缓存新数据）。
-4. 检查是否有清理机制</t>
+          <t>1. 打开小程序。
+2. 系统检测到新版本。
+3. 观察更新提示。
+4. 执行更新</t>
         </is>
       </c>
       <c r="I571" s="9" t="inlineStr">
         <is>
-          <t>1. 不因缓存满而崩溃。
-2. 有自动清理旧缓存的机制（LRU）。
-3. 核心数据（登录态/用户信息）优先保留。
-4. 即使缓存被清理，功能正常（从网络重新获取）</t>
+          <t>1. 弹出更新提示"发现新版本，是否重启更新？"。
+2. 点击"立即更新"后小程序重启。
+3. 重启后为最新版本。
+4. 如为强制更新，不可取消</t>
         </is>
       </c>
       <c r="J571" s="9" t="inlineStr">
         <is>
-          <t>微信小程序本地存储限制10MB</t>
+          <t>微信小程序热更新机制</t>
         </is>
       </c>
     </row>
@@ -25685,44 +25705,44 @@
       <c r="B572" s="8" t="inlineStr"/>
       <c r="C572" s="8" t="inlineStr">
         <is>
-          <t>xcx-hc-002</t>
+          <t>xcx-gx-002</t>
         </is>
       </c>
       <c r="D572" s="8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E572" s="8" t="n"/>
       <c r="F572" s="8" t="inlineStr">
         <is>
-          <t>验证用户清除小程序数据后的恢复</t>
+          <t>验证小程序开发版/体验版/正式版的环境隔离</t>
         </is>
       </c>
       <c r="G572" s="8" t="inlineStr">
         <is>
-          <t>1. 用户在微信设置中找到快乐羊毛小程序</t>
+          <t>1. 小程序有开发版、体验版、正式版三个版本</t>
         </is>
       </c>
       <c r="H572" s="8" t="inlineStr">
         <is>
-          <t>1. 在微信"发现-小程序"列表中长按快乐羊毛。
-2. 选择"删除"小程序。
-3. 重新搜索并打开快乐羊毛小程序。
-4. 检查数据状态</t>
+          <t>1. 分别打开开发版、体验版、正式版。
+2. 检查各版本指向的后端环境。
+3. 在开发版创建测试数据。
+4. 检查正式版是否受影响</t>
         </is>
       </c>
       <c r="I572" s="8" t="inlineStr">
         <is>
-          <t>1. 删除后所有本地缓存被清空。
-2. 重新打开为冷启动。
-3. 需要重新授权登录。
-4. 登录后服务端数据完整（订单/佣金等不丢失）</t>
+          <t>1. 开发版指向测试环境。
+2. 体验版指向预发布环境。
+3. 正式版指向生产环境。
+4. 各版本数据隔离，互不影响</t>
         </is>
       </c>
       <c r="J572" s="8" t="inlineStr">
         <is>
-          <t>删除小程序≠注销账号，服务端数据不丢</t>
+          <t>确保测试不污染生产数据</t>
         </is>
       </c>
     </row>
@@ -25739,7 +25759,7 @@
       </c>
       <c r="C573" s="9" t="inlineStr">
         <is>
-          <t>xcx-gx-001</t>
+          <t>xcx-wl-001</t>
         </is>
       </c>
       <c r="D573" s="9" t="inlineStr">
@@ -25750,38 +25770,38 @@
       <c r="E573" s="9" t="inlineStr">
         <is>
           <t>小程序环境
-(版本更新)</t>
+(网络请求)</t>
         </is>
       </c>
       <c r="F573" s="9" t="inlineStr">
         <is>
-          <t>验证小程序版本更新提示与强制更新</t>
+          <t>验证小程序HTTPS请求证书有效性</t>
         </is>
       </c>
       <c r="G573" s="9" t="inlineStr">
         <is>
-          <t>1. 当前小程序有新版本可用</t>
+          <t>1. 小程序所有请求必须为HTTPS</t>
         </is>
       </c>
       <c r="H573" s="9" t="inlineStr">
         <is>
-          <t>1. 打开小程序。
-2. 系统检测到新版本。
-3. 观察更新提示。
-4. 执行更新</t>
+          <t>1. 使用Charles/Fiddler抓包，检查所有API请求。
+2. 确认全部为HTTPS。
+3. 检查证书是否有效。
+4. 检查是否有HTTP请求（不合规）</t>
         </is>
       </c>
       <c r="I573" s="9" t="inlineStr">
         <is>
-          <t>1. 弹出更新提示"发现新版本，是否重启更新？"。
-2. 点击"立即更新"后小程序重启。
-3. 重启后为最新版本。
-4. 如为强制更新，不可取消</t>
+          <t>1. 所有API请求均为HTTPS。
+2. SSL证书有效且未过期。
+3. 无HTTP明文请求。
+4. 无mixed content问题</t>
         </is>
       </c>
       <c r="J573" s="9" t="inlineStr">
         <is>
-          <t>微信小程序热更新机制</t>
+          <t>微信小程序强制要求HTTPS</t>
         </is>
       </c>
     </row>
@@ -25790,51 +25810,51 @@
       <c r="B574" s="8" t="inlineStr"/>
       <c r="C574" s="8" t="inlineStr">
         <is>
-          <t>xcx-gx-002</t>
+          <t>xcx-wl-002</t>
         </is>
       </c>
       <c r="D574" s="8" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E574" s="8" t="n"/>
       <c r="F574" s="8" t="inlineStr">
         <is>
-          <t>验证小程序开发版/体验版/正式版的环境隔离</t>
+          <t>验证小程序域名白名单配置正确</t>
         </is>
       </c>
       <c r="G574" s="8" t="inlineStr">
         <is>
-          <t>1. 小程序有开发版、体验版、正式版三个版本</t>
+          <t>1. 微信小程序后台已配置合法域名</t>
         </is>
       </c>
       <c r="H574" s="8" t="inlineStr">
         <is>
-          <t>1. 分别打开开发版、体验版、正式版。
-2. 检查各版本指向的后端环境。
-3. 在开发版创建测试数据。
-4. 检查正式版是否受影响</t>
+          <t>1. 检查所有API请求域名。
+2. 检查所有图片资源域名（OSS等）。
+3. 检查WebView（H5跳转）域名。
+4. 确认均在微信后台域名白名单中</t>
         </is>
       </c>
       <c r="I574" s="8" t="inlineStr">
         <is>
-          <t>1. 开发版指向测试环境。
-2. 体验版指向预发布环境。
-3. 正式版指向生产环境。
-4. 各版本数据隔离，互不影响</t>
+          <t>1. 所有请求域名在白名单中。
+2. 无因域名不合法导致的请求失败。
+3. OSS图片正常加载。
+4. H5页面正常打开</t>
         </is>
       </c>
       <c r="J574" s="8" t="inlineStr">
         <is>
-          <t>确保测试不污染生产数据</t>
+          <t>未配置域名会导致请求被微信拦截</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="9" t="inlineStr">
         <is>
-          <t>用户端</t>
+          <t>商家端</t>
         </is>
       </c>
       <c r="B575" s="9" t="inlineStr">
@@ -25844,7 +25864,7 @@
       </c>
       <c r="C575" s="9" t="inlineStr">
         <is>
-          <t>xcx-wl-001</t>
+          <t>xcx-sj-001</t>
         </is>
       </c>
       <c r="D575" s="9" t="inlineStr">
@@ -25854,39 +25874,39 @@
       </c>
       <c r="E575" s="9" t="inlineStr">
         <is>
-          <t>小程序环境
-(网络请求)</t>
+          <t>商家端小程序
+环境专项</t>
         </is>
       </c>
       <c r="F575" s="9" t="inlineStr">
         <is>
-          <t>验证小程序HTTPS请求证书有效性</t>
+          <t>验证商家端小程序扫码核销的摄像头授权</t>
         </is>
       </c>
       <c r="G575" s="9" t="inlineStr">
         <is>
-          <t>1. 小程序所有请求必须为HTTPS</t>
+          <t>1. 商家端小程序首次使用扫码功能</t>
         </is>
       </c>
       <c r="H575" s="9" t="inlineStr">
         <is>
-          <t>1. 使用Charles/Fiddler抓包，检查所有API请求。
-2. 确认全部为HTTPS。
-3. 检查证书是否有效。
-4. 检查是否有HTTP请求（不合规）</t>
+          <t>1. 在商家端点击"扫码核销"。
+2. 弹出摄像头授权弹窗。
+3. 允许授权。
+4. 扫描用户的验证码</t>
         </is>
       </c>
       <c r="I575" s="9" t="inlineStr">
         <is>
-          <t>1. 所有API请求均为HTTPS。
-2. SSL证书有效且未过期。
-3. 无HTTP明文请求。
-4. 无mixed content问题</t>
+          <t>1. 摄像头授权弹窗正常显示。
+2. 允许后摄像头正常开启。
+3. 扫码/输入验证码功能正常。
+4. 拒绝授权时提示需要摄像头权限</t>
         </is>
       </c>
       <c r="J575" s="9" t="inlineStr">
         <is>
-          <t>微信小程序强制要求HTTPS</t>
+          <t>小程序扫码需要摄像头权限</t>
         </is>
       </c>
     </row>
@@ -25895,7 +25915,7 @@
       <c r="B576" s="8" t="inlineStr"/>
       <c r="C576" s="8" t="inlineStr">
         <is>
-          <t>xcx-wl-002</t>
+          <t>xcx-sj-002</t>
         </is>
       </c>
       <c r="D576" s="8" t="inlineStr">
@@ -25906,121 +25926,16 @@
       <c r="E576" s="8" t="n"/>
       <c r="F576" s="8" t="inlineStr">
         <is>
-          <t>验证小程序域名白名单配置正确</t>
+          <t>验证商家端小程序收银台键盘交互</t>
         </is>
       </c>
       <c r="G576" s="8" t="inlineStr">
-        <is>
-          <t>1. 微信小程序后台已配置合法域名</t>
-        </is>
-      </c>
-      <c r="H576" s="8" t="inlineStr">
-        <is>
-          <t>1. 检查所有API请求域名。
-2. 检查所有图片资源域名（OSS等）。
-3. 检查WebView（H5跳转）域名。
-4. 确认均在微信后台域名白名单中</t>
-        </is>
-      </c>
-      <c r="I576" s="8" t="inlineStr">
-        <is>
-          <t>1. 所有请求域名在白名单中。
-2. 无因域名不合法导致的请求失败。
-3. OSS图片正常加载。
-4. H5页面正常打开</t>
-        </is>
-      </c>
-      <c r="J576" s="8" t="inlineStr">
-        <is>
-          <t>未配置域名会导致请求被微信拦截</t>
-        </is>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" s="9" t="inlineStr">
-        <is>
-          <t>商家端</t>
-        </is>
-      </c>
-      <c r="B577" s="9" t="inlineStr">
-        <is>
-          <t>0.5h</t>
-        </is>
-      </c>
-      <c r="C577" s="9" t="inlineStr">
-        <is>
-          <t>xcx-sj-001</t>
-        </is>
-      </c>
-      <c r="D577" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E577" s="9" t="inlineStr">
-        <is>
-          <t>商家端小程序
-环境专项</t>
-        </is>
-      </c>
-      <c r="F577" s="9" t="inlineStr">
-        <is>
-          <t>验证商家端小程序扫码核销的摄像头授权</t>
-        </is>
-      </c>
-      <c r="G577" s="9" t="inlineStr">
-        <is>
-          <t>1. 商家端小程序首次使用扫码功能</t>
-        </is>
-      </c>
-      <c r="H577" s="9" t="inlineStr">
-        <is>
-          <t>1. 在商家端点击"扫码核销"。
-2. 弹出摄像头授权弹窗。
-3. 允许授权。
-4. 扫描用户的验证码</t>
-        </is>
-      </c>
-      <c r="I577" s="9" t="inlineStr">
-        <is>
-          <t>1. 摄像头授权弹窗正常显示。
-2. 允许后摄像头正常开启。
-3. 扫码/输入验证码功能正常。
-4. 拒绝授权时提示需要摄像头权限</t>
-        </is>
-      </c>
-      <c r="J577" s="9" t="inlineStr">
-        <is>
-          <t>小程序扫码需要摄像头权限</t>
-        </is>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" s="8" t="inlineStr"/>
-      <c r="B578" s="8" t="inlineStr"/>
-      <c r="C578" s="8" t="inlineStr">
-        <is>
-          <t>xcx-sj-002</t>
-        </is>
-      </c>
-      <c r="D578" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E578" s="8" t="n"/>
-      <c r="F578" s="8" t="inlineStr">
-        <is>
-          <t>验证商家端小程序收银台键盘交互</t>
-        </is>
-      </c>
-      <c r="G578" s="8" t="inlineStr">
         <is>
           <t>1. 商家端小程序已登录
 2. 进入收银台页面</t>
         </is>
       </c>
-      <c r="H578" s="8" t="inlineStr">
+      <c r="H576" s="8" t="inlineStr">
         <is>
           <t>1. 点击金额输入框。
 2. 检查唤起的键盘类型。
@@ -26029,7 +25944,7 @@
 5. 检查输入值</t>
         </is>
       </c>
-      <c r="I578" s="8" t="inlineStr">
+      <c r="I576" s="8" t="inlineStr">
         <is>
           <t>1. 唤起数字键盘（带小数点）。
 2. 键盘不遮挡金额显示区域。
@@ -26038,9 +25953,116 @@
 5. 折扣自动计算并展示</t>
         </is>
       </c>
-      <c r="J578" s="8" t="inlineStr">
+      <c r="J576" s="8" t="inlineStr">
         <is>
           <t>小程序键盘交互与原生App不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="8" t="inlineStr"/>
+      <c r="B577" s="8" t="inlineStr"/>
+      <c r="C577" s="8" t="inlineStr">
+        <is>
+          <t>xcx-sj-003</t>
+        </is>
+      </c>
+      <c r="D577" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E577" s="8" t="n"/>
+      <c r="F577" s="8" t="inlineStr">
+        <is>
+          <t>验证商家端小程序后台持续运行收银台</t>
+        </is>
+      </c>
+      <c r="G577" s="8" t="inlineStr">
+        <is>
+          <t>1. 商家端小程序收银台正在使用
+2. 已生成一个收款二维码</t>
+        </is>
+      </c>
+      <c r="H577" s="8" t="inlineStr">
+        <is>
+          <t>1. 保持收银台页面，锁屏。
+2. 10分钟后解锁。
+3. 检查收银台状态和二维码倒计时。
+4. 用户尝试扫码支付</t>
+        </is>
+      </c>
+      <c r="I577" s="8" t="inlineStr">
+        <is>
+          <t>1. 解锁后收银台页面正常显示。
+2. 二维码倒计时正确更新。
+3. 如未超时，扫码支付正常。
+4. 如已超时，提示重新生成</t>
+        </is>
+      </c>
+      <c r="J577" s="8" t="inlineStr">
+        <is>
+          <t>商家长期使用收银台的真实场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="9" t="inlineStr">
+        <is>
+          <t>管理后台</t>
+        </is>
+      </c>
+      <c r="B578" s="9" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C578" s="9" t="inlineStr">
+        <is>
+          <t>xcx-ht-001</t>
+        </is>
+      </c>
+      <c r="D578" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E578" s="9" t="inlineStr">
+        <is>
+          <t>管理后台
+PC浏览器环境</t>
+        </is>
+      </c>
+      <c r="F578" s="9" t="inlineStr">
+        <is>
+          <t>验证管理后台在不同分辨率下的响应式布局</t>
+        </is>
+      </c>
+      <c r="G578" s="9" t="inlineStr">
+        <is>
+          <t>1. Chrome浏览器
+2. 后台已登录</t>
+        </is>
+      </c>
+      <c r="H578" s="9" t="inlineStr">
+        <is>
+          <t>1. 在1920x1080分辨率下查看后台。
+2. 缩小浏览器窗口至1366x768。
+3. 缩小至1024x768。
+4. 检查各页面布局</t>
+        </is>
+      </c>
+      <c r="I578" s="9" t="inlineStr">
+        <is>
+          <t>1. 1920x1080：全功能正常展示。
+2. 1366x768：布局自适应，功能正常。
+3. 1024x768：关键功能可用，可能出现滚动条。
+4. 不出现元素重叠或功能不可用</t>
+        </is>
+      </c>
+      <c r="J578" s="9" t="inlineStr">
+        <is>
+          <t>运营人员可能使用不同分辨率显示器</t>
         </is>
       </c>
     </row>
@@ -26049,134 +26071,27 @@
       <c r="B579" s="8" t="inlineStr"/>
       <c r="C579" s="8" t="inlineStr">
         <is>
-          <t>xcx-sj-003</t>
+          <t>xcx-ht-002</t>
         </is>
       </c>
       <c r="D579" s="8" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E579" s="8" t="n"/>
       <c r="F579" s="8" t="inlineStr">
         <is>
-          <t>验证商家端小程序后台持续运行收银台</t>
+          <t>验证管理后台文件下载功能（Excel导出）</t>
         </is>
       </c>
       <c r="G579" s="8" t="inlineStr">
-        <is>
-          <t>1. 商家端小程序收银台正在使用
-2. 已生成一个收款二维码</t>
-        </is>
-      </c>
-      <c r="H579" s="8" t="inlineStr">
-        <is>
-          <t>1. 保持收银台页面，锁屏。
-2. 10分钟后解锁。
-3. 检查收银台状态和二维码倒计时。
-4. 用户尝试扫码支付</t>
-        </is>
-      </c>
-      <c r="I579" s="8" t="inlineStr">
-        <is>
-          <t>1. 解锁后收银台页面正常显示。
-2. 二维码倒计时正确更新。
-3. 如未超时，扫码支付正常。
-4. 如已超时，提示重新生成</t>
-        </is>
-      </c>
-      <c r="J579" s="8" t="inlineStr">
-        <is>
-          <t>商家长期使用收银台的真实场景</t>
-        </is>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" s="9" t="inlineStr">
-        <is>
-          <t>管理后台</t>
-        </is>
-      </c>
-      <c r="B580" s="9" t="inlineStr">
-        <is>
-          <t>0.5h</t>
-        </is>
-      </c>
-      <c r="C580" s="9" t="inlineStr">
-        <is>
-          <t>xcx-ht-001</t>
-        </is>
-      </c>
-      <c r="D580" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E580" s="9" t="inlineStr">
-        <is>
-          <t>管理后台
-PC浏览器环境</t>
-        </is>
-      </c>
-      <c r="F580" s="9" t="inlineStr">
-        <is>
-          <t>验证管理后台在不同分辨率下的响应式布局</t>
-        </is>
-      </c>
-      <c r="G580" s="9" t="inlineStr">
-        <is>
-          <t>1. Chrome浏览器
-2. 后台已登录</t>
-        </is>
-      </c>
-      <c r="H580" s="9" t="inlineStr">
-        <is>
-          <t>1. 在1920x1080分辨率下查看后台。
-2. 缩小浏览器窗口至1366x768。
-3. 缩小至1024x768。
-4. 检查各页面布局</t>
-        </is>
-      </c>
-      <c r="I580" s="9" t="inlineStr">
-        <is>
-          <t>1. 1920x1080：全功能正常展示。
-2. 1366x768：布局自适应，功能正常。
-3. 1024x768：关键功能可用，可能出现滚动条。
-4. 不出现元素重叠或功能不可用</t>
-        </is>
-      </c>
-      <c r="J580" s="9" t="inlineStr">
-        <is>
-          <t>运营人员可能使用不同分辨率显示器</t>
-        </is>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" s="8" t="inlineStr"/>
-      <c r="B581" s="8" t="inlineStr"/>
-      <c r="C581" s="8" t="inlineStr">
-        <is>
-          <t>xcx-ht-002</t>
-        </is>
-      </c>
-      <c r="D581" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E581" s="8" t="n"/>
-      <c r="F581" s="8" t="inlineStr">
-        <is>
-          <t>验证管理后台文件下载功能（Excel导出）</t>
-        </is>
-      </c>
-      <c r="G581" s="8" t="inlineStr">
         <is>
           <t>1. Chrome浏览器
 2. 后台有订单数据</t>
         </is>
       </c>
-      <c r="H581" s="8" t="inlineStr">
+      <c r="H579" s="8" t="inlineStr">
         <is>
           <t>1. 在订单管理页点击"导出"。
 2. 检查浏览器下载行为。
@@ -26184,7 +26099,7 @@
 4. 验证数据完整性</t>
         </is>
       </c>
-      <c r="I581" s="8" t="inlineStr">
+      <c r="I579" s="8" t="inlineStr">
         <is>
           <t>1. 导出文件正常下载。
 2. 文件名包含日期标识。
@@ -26192,37 +26107,37 @@
 4. 中文不乱码</t>
         </is>
       </c>
-      <c r="J581" s="8" t="inlineStr">
+      <c r="J579" s="8" t="inlineStr">
         <is>
           <t>导出功能在不同浏览器行为可能不同</t>
         </is>
       </c>
     </row>
-    <row r="582">
-      <c r="A582" s="8" t="inlineStr"/>
-      <c r="B582" s="8" t="inlineStr"/>
-      <c r="C582" s="8" t="inlineStr">
+    <row r="580">
+      <c r="A580" s="8" t="inlineStr"/>
+      <c r="B580" s="8" t="inlineStr"/>
+      <c r="C580" s="8" t="inlineStr">
         <is>
           <t>xcx-ht-003</t>
         </is>
       </c>
-      <c r="D582" s="8" t="inlineStr">
+      <c r="D580" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E582" s="8" t="n"/>
-      <c r="F582" s="8" t="inlineStr">
+      <c r="E580" s="8" t="n"/>
+      <c r="F580" s="8" t="inlineStr">
         <is>
           <t>验证管理后台多标签页打开的数据独立性</t>
         </is>
       </c>
-      <c r="G582" s="8" t="inlineStr">
+      <c r="G580" s="8" t="inlineStr">
         <is>
           <t>1. Chrome浏览器已登录后台</t>
         </is>
       </c>
-      <c r="H582" s="8" t="inlineStr">
+      <c r="H580" s="8" t="inlineStr">
         <is>
           <t>1. 打开标签页A，查看订单列表第1页。
 2. 打开标签页B，查看订单列表第5页。
@@ -26230,7 +26145,7 @@
 4. 切回标签页B检查数据</t>
         </is>
       </c>
-      <c r="I582" s="8" t="inlineStr">
+      <c r="I580" s="8" t="inlineStr">
         <is>
           <t>1. 两个标签页独立操作，不互相影响。
 2. 标签页A的筛选不影响标签页B。
@@ -26238,7 +26153,7 @@
 4. 不出现数据混乱</t>
         </is>
       </c>
-      <c r="J582" s="8" t="inlineStr">
+      <c r="J580" s="8" t="inlineStr">
         <is>
           <t>运营可能同时打开多个标签页工作</t>
         </is>

--- a/快乐羊毛系统/功能测试需要的文件2026.03.17/最终版测试用例/快乐羊毛系统完整测试用例2026.03.17（付仕菊）-V3.0完善版v2.xlsx
+++ b/快乐羊毛系统/功能测试需要的文件2026.03.17/最终版测试用例/快乐羊毛系统完整测试用例2026.03.17（付仕菊）-V3.0完善版v2.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -219,8 +219,14 @@
       <color rgb="00C00000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="000D47A1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -431,8 +437,20 @@
         <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D47A1"/>
+        <bgColor rgb="000D47A1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -566,6 +584,50 @@
       <bottom style="thin">
         <color rgb="00D9D9D9"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
@@ -715,7 +777,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -750,6 +812,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1199,7 +1270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J580"/>
+  <dimension ref="A1:J627"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="6.5" customWidth="1" style="3" min="1" max="3"/>
@@ -20057,7 +20128,6 @@
       </c>
       <c r="J453" s="4" t="inlineStr"/>
     </row>
-    <row r="454"/>
     <row r="455">
       <c r="A455" s="7" t="inlineStr">
         <is>
@@ -24678,7 +24748,6 @@
         </is>
       </c>
     </row>
-    <row r="550"/>
     <row r="551">
       <c r="A551" s="13" t="inlineStr">
         <is>
@@ -24692,59 +24761,15 @@
           <t>用户端</t>
         </is>
       </c>
-      <c r="B552" s="9" t="inlineStr">
-        <is>
-          <t>1.5h</t>
-        </is>
-      </c>
-      <c r="C552" s="9" t="inlineStr">
-        <is>
-          <t>xcx-sm-001</t>
-        </is>
-      </c>
-      <c r="D552" s="9" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E552" s="9" t="inlineStr">
-        <is>
-          <t>小程序环境
-(生命周期/启动)</t>
-        </is>
-      </c>
-      <c r="F552" s="9" t="inlineStr">
-        <is>
-          <t>验证小程序冷启动正常加载</t>
-        </is>
-      </c>
-      <c r="G552" s="9" t="inlineStr">
-        <is>
-          <t>1. 小程序未在微信后台运行
-2. 用户已有微信登录态</t>
-        </is>
-      </c>
-      <c r="H552" s="9" t="inlineStr">
-        <is>
-          <t>1. 在微信中搜索或扫码打开快乐羊毛小程序。
-2. 观察启动过程（闪屏/loading）。
-3. 记录从点击到首页完全渲染的时间。
-4. 检查首页数据是否完整加载</t>
-        </is>
-      </c>
-      <c r="I552" s="9" t="inlineStr">
-        <is>
-          <t>1. 启动过程有品牌闪屏（如有配置）。
-2. 首屏渲染&lt;2秒（WiFi）/&lt;5秒（4G）。
-3. 首页数据完整加载，不出现白屏。
-4. 用户登录态自动恢复（微信静默登录）</t>
-        </is>
-      </c>
-      <c r="J552" s="9" t="inlineStr">
-        <is>
-          <t>冷启动是用户最常遇到的入口场景</t>
-        </is>
-      </c>
+      <c r="B552" s="16" t="n"/>
+      <c r="C552" s="16" t="n"/>
+      <c r="D552" s="16" t="n"/>
+      <c r="E552" s="16" t="n"/>
+      <c r="F552" s="16" t="n"/>
+      <c r="G552" s="16" t="n"/>
+      <c r="H552" s="16" t="n"/>
+      <c r="I552" s="16" t="n"/>
+      <c r="J552" s="17" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="8" t="inlineStr"/>
@@ -26159,13 +26184,2378 @@
         </is>
       </c>
     </row>
+    <row r="582">
+      <c r="A582" s="18" t="inlineStr">
+        <is>
+          <t>═══ 各功能模块 · 小程序环境专项用例 ═══ 每个模块在微信小程序中的具体操作行为、交互、异常 ═══</t>
+        </is>
+      </c>
+      <c r="B582" s="19" t="n"/>
+      <c r="C582" s="19" t="n"/>
+      <c r="D582" s="19" t="n"/>
+      <c r="E582" s="19" t="n"/>
+      <c r="F582" s="19" t="n"/>
+      <c r="G582" s="19" t="n"/>
+      <c r="H582" s="19" t="n"/>
+      <c r="I582" s="19" t="n"/>
+      <c r="J582" s="19" t="n"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="20" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B583" s="20" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C583" s="20" t="inlineStr">
+        <is>
+          <t>mfzl-xcx-001</t>
+        </is>
+      </c>
+      <c r="D583" s="20" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E583" s="20" t="inlineStr">
+        <is>
+          <t>免费资料区
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F583" s="20" t="inlineStr">
+        <is>
+          <t>验证小程序内复制链接调用剪贴板后的微信原生Toast提示</t>
+        </is>
+      </c>
+      <c r="G583" s="20" t="inlineStr">
+        <is>
+          <t>1. 用户已进入免费资料区详情页
+2. 详情页有可复制链接</t>
+        </is>
+      </c>
+      <c r="H583" s="20" t="inlineStr">
+        <is>
+          <t>1. 点击"复制链接"按钮。
+2. 观察弹出的Toast提示样式。
+3. 长按微信聊天输入框粘贴，验证剪贴板内容正确。
+4. 等待Toast消失（约2秒）</t>
+        </is>
+      </c>
+      <c r="I583" s="20" t="inlineStr">
+        <is>
+          <t>1. 点击后弹出"复制成功"Toast（微信原生样式，非自定义弹窗）。
+2. Toast约2秒后自动消失。
+3. 粘贴内容为完整链接URL。
+4. 不弹出微信"是否允许读取剪贴板"授权提示（写入不需要）</t>
+        </is>
+      </c>
+      <c r="J583" s="20" t="inlineStr">
+        <is>
+          <t>小程序调用wx.setClipboardData会弹微信原生Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="8" t="inlineStr"/>
+      <c r="B584" s="8" t="inlineStr"/>
+      <c r="C584" s="8" t="inlineStr">
+        <is>
+          <t>mfzl-xcx-002</t>
+        </is>
+      </c>
+      <c r="D584" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E584" s="8" t="n"/>
+      <c r="F584" s="8" t="inlineStr">
+        <is>
+          <t>验证资料列表页小程序下拉刷新和触底加载交互</t>
+        </is>
+      </c>
+      <c r="G584" s="8" t="inlineStr">
+        <is>
+          <t>1. 免费资料区已有20+条数据
+2. 小程序已开启enablePullDownRefresh</t>
+        </is>
+      </c>
+      <c r="H584" s="8" t="inlineStr">
+        <is>
+          <t>1. 在列表页顶部下拉。
+2. 观察下拉刷新动画（微信原生三个点）。
+3. 松手后数据刷新。
+4. 滚动到列表底部。
+5. 观察触底加载更多行为</t>
+        </is>
+      </c>
+      <c r="I584" s="8" t="inlineStr">
+        <is>
+          <t>1. 下拉显示微信原生刷新动画（绿色三个点）。
+2. 松手后触发onPullDownRefresh，数据刷新，动画结束。
+3. 触底自动触发onReachBottom加载下一页。
+4. 加载中显示"加载中..."。
+5. 最后一页显示"没有更多了"</t>
+        </is>
+      </c>
+      <c r="J584" s="8" t="inlineStr">
+        <is>
+          <t>小程序下拉刷新是原生Page事件，非自定义组件</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="8" t="inlineStr"/>
+      <c r="B585" s="8" t="inlineStr"/>
+      <c r="C585" s="8" t="inlineStr">
+        <is>
+          <t>mfzl-xcx-003</t>
+        </is>
+      </c>
+      <c r="D585" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E585" s="8" t="n"/>
+      <c r="F585" s="8" t="inlineStr">
+        <is>
+          <t>验证详情页返回列表时页面栈保持和滚动位置恢复</t>
+        </is>
+      </c>
+      <c r="G585" s="8" t="inlineStr">
+        <is>
+          <t>1. 列表已滚动到第15条数据位置
+2. 准备点击某条进入详情</t>
+        </is>
+      </c>
+      <c r="H585" s="8" t="inlineStr">
+        <is>
+          <t>1. 记录当前滚动位置（约第15条）。
+2. 点击某条资料进入详情页（navigateTo压栈）。
+3. 点击左上角返回按钮（navigateBack出栈）。
+4. 检查列表页状态</t>
+        </is>
+      </c>
+      <c r="I585" s="8" t="inlineStr">
+        <is>
+          <t>1. 进入详情页时列表页保留在页面栈中。
+2. 返回后列表恢复到第15条位置，不回到顶部。
+3. 已加载的数据不丢失、不重复请求。
+4. 页面栈深度不超过10层（小程序限制）</t>
+        </is>
+      </c>
+      <c r="J585" s="8" t="inlineStr">
+        <is>
+          <t>小程序navigateTo最大10层页面栈</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="8" t="inlineStr"/>
+      <c r="B586" s="8" t="inlineStr"/>
+      <c r="C586" s="8" t="inlineStr">
+        <is>
+          <t>mfzl-xcx-004</t>
+        </is>
+      </c>
+      <c r="D586" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E586" s="8" t="n"/>
+      <c r="F586" s="8" t="inlineStr">
+        <is>
+          <t>验证资料区转发分享给好友后对方能正确打开</t>
+        </is>
+      </c>
+      <c r="G586" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户在免费资料详情页</t>
+        </is>
+      </c>
+      <c r="H586" s="8" t="inlineStr">
+        <is>
+          <t>1. 点击右上角"..."胶囊按钮。
+2. 选择"转发"。
+3. 选择好友发送。
+4. 好友在聊天中点击分享卡片</t>
+        </is>
+      </c>
+      <c r="I586" s="8" t="inlineStr">
+        <is>
+          <t>1. 分享卡片显示资料标题和描述。
+2. 好友点击后直接进入该资料详情页（非首页）。
+3. 详情页数据正确加载。
+4. 好友可正常返回首页浏览其他内容</t>
+        </is>
+      </c>
+      <c r="J586" s="8" t="inlineStr">
+        <is>
+          <t>小程序分享需配置onShareAppMessage</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="20" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B587" s="20" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C587" s="20" t="inlineStr">
+        <is>
+          <t>wamhb-xcx-001</t>
+        </is>
+      </c>
+      <c r="D587" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E587" s="20" t="inlineStr">
+        <is>
+          <t>外卖区-红包
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F587" s="20" t="inlineStr">
+        <is>
+          <t>验证小程序内跳转外部App（美团/饿了么）的行为</t>
+        </is>
+      </c>
+      <c r="G587" s="20" t="inlineStr">
+        <is>
+          <t>1. 用户在外卖红包页面
+2. 手机已安装美团App</t>
+        </is>
+      </c>
+      <c r="H587" s="20" t="inlineStr">
+        <is>
+          <t>1. 点击美团红包Icon。
+2. 中间页加载完成。
+3. 观察跳转行为（小程序→App）。
+4. 从美团App返回小程序</t>
+        </is>
+      </c>
+      <c r="I587" s="20" t="inlineStr">
+        <is>
+          <t>1. 小程序通过scheme/universal link唤起美团App。
+2. 跳转时微信可能弹出"即将打开外部应用"确认框。
+3. 确认后成功打开美团对应页面。
+4. 从美团App返回微信后，小程序热启动恢复到红包页面</t>
+        </is>
+      </c>
+      <c r="J587" s="20" t="inlineStr">
+        <is>
+          <t>小程序跳转外部App需要配置URL Scheme白名单</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="8" t="inlineStr"/>
+      <c r="B588" s="8" t="inlineStr"/>
+      <c r="C588" s="8" t="inlineStr">
+        <is>
+          <t>wamhb-xcx-002</t>
+        </is>
+      </c>
+      <c r="D588" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E588" s="8" t="n"/>
+      <c r="F588" s="8" t="inlineStr">
+        <is>
+          <t>验证手机未安装目标App时小程序降级为H5内嵌打开</t>
+        </is>
+      </c>
+      <c r="G588" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户手机未安装饿了么App</t>
+        </is>
+      </c>
+      <c r="H588" s="8" t="inlineStr">
+        <is>
+          <t>1. 点击饿了么红包Icon。
+2. 观察跳转行为</t>
+        </is>
+      </c>
+      <c r="I588" s="8" t="inlineStr">
+        <is>
+          <t>1. 检测到未安装App，不尝试唤起。
+2. 在小程序内嵌web-view中打开H5页面。
+3. 或弹出提示"未安装饿了么App，是否下载？"。
+4. H5页面正常显示领券内容</t>
+        </is>
+      </c>
+      <c r="J588" s="8" t="inlineStr">
+        <is>
+          <t>小程序需判断canLaunch再决定跳转方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="8" t="inlineStr"/>
+      <c r="B589" s="8" t="inlineStr"/>
+      <c r="C589" s="8" t="inlineStr">
+        <is>
+          <t>wamhb-xcx-003</t>
+        </is>
+      </c>
+      <c r="D589" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E589" s="8" t="n"/>
+      <c r="F589" s="8" t="inlineStr">
+        <is>
+          <t>验证外卖红包页面小程序分享卡片内容正确</t>
+        </is>
+      </c>
+      <c r="G589" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户在外卖红包页面</t>
+        </is>
+      </c>
+      <c r="H589" s="8" t="inlineStr">
+        <is>
+          <t>1. 点击右上角"..."。
+2. 选择"转发"给好友。
+3. 好友收到后点击分享卡片</t>
+        </is>
+      </c>
+      <c r="I589" s="8" t="inlineStr">
+        <is>
+          <t>1. 分享卡片标题如"快乐羊毛·外卖红包"。
+2. 卡片封面图正确。
+3. 好友点击后进入外卖红包页面（含推广参数）。
+4. 推广关系正确绑定</t>
+        </is>
+      </c>
+      <c r="J589" s="8" t="inlineStr">
+        <is>
+          <t>分享卡片是用户裂变的核心渠道</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="20" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B590" s="20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="C590" s="20" t="inlineStr">
+        <is>
+          <t>wamtyj-xcx-001</t>
+        </is>
+      </c>
+      <c r="D590" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E590" s="20" t="inlineStr">
+        <is>
+          <t>外卖区-通用券
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F590" s="20" t="inlineStr">
+        <is>
+          <t>验证通用券购买全流程在小程序中的微信支付交互</t>
+        </is>
+      </c>
+      <c r="G590" s="20" t="inlineStr">
+        <is>
+          <t>1. 用户已选择10元面额通用券
+2. 确认订单页已展示</t>
+        </is>
+      </c>
+      <c r="H590" s="20" t="inlineStr">
+        <is>
+          <t>1. 确认红色"支付后不退款"提示文案可见。
+2. 勾选"已阅读并同意"协议复选框。
+3. 点击"确认支付"。
+4. 微信支付弹窗从底部弹出。
+5. 确认弹窗显示金额（如¥9.50）和收款方。
+6. 输入6位支付密码。
+7. 支付完成后观察页面跳转</t>
+        </is>
+      </c>
+      <c r="I590" s="20" t="inlineStr">
+        <is>
+          <t>1. 微信支付弹窗正常唤起（wx.requestPayment）。
+2. 弹窗显示正确金额和"快乐羊毛"收款方。
+3. 输入密码后弹窗消失，返回小程序。
+4. 自动跳转到订单结果页展示卡密。
+5. 整个过程不超过3秒</t>
+        </is>
+      </c>
+      <c r="J590" s="20" t="inlineStr">
+        <is>
+          <t>小程序支付通过wx.requestPayment调起</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="8" t="inlineStr"/>
+      <c r="B591" s="8" t="inlineStr"/>
+      <c r="C591" s="8" t="inlineStr">
+        <is>
+          <t>wamtyj-xcx-002</t>
+        </is>
+      </c>
+      <c r="D591" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E591" s="8" t="n"/>
+      <c r="F591" s="8" t="inlineStr">
+        <is>
+          <t>验证小程序支付弹窗取消后可重新发起支付</t>
+        </is>
+      </c>
+      <c r="G591" s="8" t="inlineStr">
+        <is>
+          <t>1. 支付弹窗已唤起</t>
+        </is>
+      </c>
+      <c r="H591" s="8" t="inlineStr">
+        <is>
+          <t>1. 在支付弹窗上点击右上角"×"关闭。
+2. 返回到订单确认页。
+3. 检查页面状态和按钮可用性。
+4. 再次点击"确认支付"</t>
+        </is>
+      </c>
+      <c r="I591" s="8" t="inlineStr">
+        <is>
+          <t>1. 关闭弹窗后小程序收到fail回调（errMsg: requestPayment:fail cancel）。
+2. 订单状态保持"待支付"。
+3. 支付按钮恢复可点击。
+4. 再次点击正常唤起支付弹窗。
+5. 不产生重复订单</t>
+        </is>
+      </c>
+      <c r="J591" s="8" t="inlineStr">
+        <is>
+          <t>用户可能反复取消再支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="8" t="inlineStr"/>
+      <c r="B592" s="8" t="inlineStr"/>
+      <c r="C592" s="8" t="inlineStr">
+        <is>
+          <t>wamtyj-xcx-003</t>
+        </is>
+      </c>
+      <c r="D592" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E592" s="8" t="n"/>
+      <c r="F592" s="8" t="inlineStr">
+        <is>
+          <t>验证卡密复制按钮在小程序中的剪贴板行为</t>
+        </is>
+      </c>
+      <c r="G592" s="8" t="inlineStr">
+        <is>
+          <t>1. 通用券购买成功
+2. 订单详情展示卡密信息</t>
+        </is>
+      </c>
+      <c r="H592" s="8" t="inlineStr">
+        <is>
+          <t>1. 点击"复制卡密"按钮。
+2. 观察提示。
+3. 切换到微信聊天窗口粘贴验证。
+4. 返回小程序点击"复制券码"</t>
+        </is>
+      </c>
+      <c r="I592" s="8" t="inlineStr">
+        <is>
+          <t>1. 点击后微信弹出原生"内容已复制"Toast。
+2. 粘贴内容为完整卡密号。
+3. 切换回小程序页面不丢失数据。
+4. 券码复制同样正常</t>
+        </is>
+      </c>
+      <c r="J592" s="8" t="inlineStr">
+        <is>
+          <t>小程序复制后自动弹微信系统Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="8" t="inlineStr"/>
+      <c r="B593" s="8" t="inlineStr"/>
+      <c r="C593" s="8" t="inlineStr">
+        <is>
+          <t>wamtyj-xcx-004</t>
+        </is>
+      </c>
+      <c r="D593" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E593" s="8" t="n"/>
+      <c r="F593" s="8" t="inlineStr">
+        <is>
+          <t>验证通用券下单确认页"不退款"协议勾选框的小程序交互</t>
+        </is>
+      </c>
+      <c r="G593" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户已选择面额，进入确认页</t>
+        </is>
+      </c>
+      <c r="H593" s="8" t="inlineStr">
+        <is>
+          <t>1. 不勾选协议，直接点击"确认支付"。
+2. 观察按钮状态和提示。
+3. 勾选协议复选框。
+4. 再次点击"确认支付"</t>
+        </is>
+      </c>
+      <c r="I593" s="8" t="inlineStr">
+        <is>
+          <t>1. 未勾选时：支付按钮为灰色不可点击，或点击后提示"请先勾选协议"。
+2. 勾选后：支付按钮变为可点击状态（颜色变化）。
+3. 点击后正常唤起微信支付弹窗</t>
+        </is>
+      </c>
+      <c r="J593" s="8" t="inlineStr">
+        <is>
+          <t>此勾选框是合规要求，必须拦截未勾选</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="20" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B594" s="20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="C594" s="20" t="inlineStr">
+        <is>
+          <t>cyzkxtzl-xcx-001</t>
+        </is>
+      </c>
+      <c r="D594" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E594" s="20" t="inlineStr">
+        <is>
+          <t>餐饮折扣-系统直连
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F594" s="20" t="inlineStr">
+        <is>
+          <t>验证小程序扫码支付全流程（wx.scanCode → 支付）</t>
+        </is>
+      </c>
+      <c r="G594" s="20" t="inlineStr">
+        <is>
+          <t>1. 商家已在小程序端生成收款二维码
+2. 用户打开快乐羊毛小程序</t>
+        </is>
+      </c>
+      <c r="H594" s="20" t="inlineStr">
+        <is>
+          <t>1. 用户在小程序内点击"扫码支付"。
+2. 小程序调起摄像头（首次弹授权）。
+3. 对准商家二维码扫描。
+4. 扫码成功，跳转到支付确认页。
+5. 确认原价/优惠/实付金额。
+6. 点击支付，微信支付弹窗弹出。
+7. 输入密码完成支付</t>
+        </is>
+      </c>
+      <c r="I594" s="20" t="inlineStr">
+        <is>
+          <t>1. 扫码功能正常调起（wx.scanCode）。
+2. 首次使用弹出摄像头授权，允许后正常扫描。
+3. 扫码解析二维码内容并跳转正确页面。
+4. 支付确认页展示正确的金额（如原价100/优惠20/实付80）。
+5. 微信支付正常完成。
+6. 支付成功后跳转结果页，三端数据同步</t>
+        </is>
+      </c>
+      <c r="J594" s="20" t="inlineStr">
+        <is>
+          <t>扫码→解析→支付是小程序核心链路</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="8" t="inlineStr"/>
+      <c r="B595" s="8" t="inlineStr"/>
+      <c r="C595" s="8" t="inlineStr">
+        <is>
+          <t>cyzkxtzl-xcx-002</t>
+        </is>
+      </c>
+      <c r="D595" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E595" s="8" t="n"/>
+      <c r="F595" s="8" t="inlineStr">
+        <is>
+          <t>验证用户通过微信"扫一扫"扫商家码进入小程序支付</t>
+        </is>
+      </c>
+      <c r="G595" s="8" t="inlineStr">
+        <is>
+          <t>1. 商家已生成收款二维码
+2. 用户在微信首页</t>
+        </is>
+      </c>
+      <c r="H595" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户在微信首页点击右上角"+"→"扫一扫"。
+2. 扫描商家收款二维码。
+3. 微信识别为小程序码后自动打开快乐羊毛小程序。
+4. 小程序直接跳转到支付确认页。
+5. 完成支付</t>
+        </is>
+      </c>
+      <c r="I595" s="8" t="inlineStr">
+        <is>
+          <t>1. 微信扫一扫正确识别二维码。
+2. 自动打开快乐羊毛小程序（冷启动或热启动）。
+3. 通过scene参数直接跳转到支付页面，不经过首页。
+4. 支付确认页展示正确金额。
+5. 支付流程正常完成</t>
+        </is>
+      </c>
+      <c r="J595" s="8" t="inlineStr">
+        <is>
+          <t>用户可能直接从微信扫一扫进入，不是从小程序内部扫码</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="8" t="inlineStr"/>
+      <c r="B596" s="8" t="inlineStr"/>
+      <c r="C596" s="8" t="inlineStr">
+        <is>
+          <t>cyzkxtzl-xcx-003</t>
+        </is>
+      </c>
+      <c r="D596" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E596" s="8" t="n"/>
+      <c r="F596" s="8" t="inlineStr">
+        <is>
+          <t>验证二维码生成后的小程序前后台切换不影响有效性</t>
+        </is>
+      </c>
+      <c r="G596" s="8" t="inlineStr">
+        <is>
+          <t>1. 商家端小程序已生成收款二维码
+2. 二维码有15分钟倒计时</t>
+        </is>
+      </c>
+      <c r="H596" s="8" t="inlineStr">
+        <is>
+          <t>1. 商家生成二维码后按Home键将小程序切到后台。
+2. 等待3分钟。
+3. 回到小程序前台。
+4. 检查二维码和倒计时状态。
+5. 让用户扫码支付</t>
+        </is>
+      </c>
+      <c r="I596" s="8" t="inlineStr">
+        <is>
+          <t>1. 切回前台后二维码仍然显示。
+2. 倒计时正确更新（从服务端同步时间而非本地计时）。
+3. 用户扫码支付正常完成。
+4. 如小程序被系统回收重启，重新加载收银台页面</t>
+        </is>
+      </c>
+      <c r="J596" s="8" t="inlineStr">
+        <is>
+          <t>商家经常切后台聊天再回来——二维码不能丢</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="8" t="inlineStr"/>
+      <c r="B597" s="8" t="inlineStr"/>
+      <c r="C597" s="8" t="inlineStr">
+        <is>
+          <t>cyzkxtzl-xcx-004</t>
+        </is>
+      </c>
+      <c r="D597" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E597" s="8" t="n"/>
+      <c r="F597" s="8" t="inlineStr">
+        <is>
+          <t>验证餐饮折扣收银台小程序数字键盘输入金额</t>
+        </is>
+      </c>
+      <c r="G597" s="8" t="inlineStr">
+        <is>
+          <t>1. 商家端小程序已打开收银台页面</t>
+        </is>
+      </c>
+      <c r="H597" s="8" t="inlineStr">
+        <is>
+          <t>1. 点击金额输入框。
+2. 观察弹出的键盘类型。
+3. 输入金额"99.50"。
+4. 点击输入框外收起键盘。
+5. 检查折扣自动计算</t>
+        </is>
+      </c>
+      <c r="I597" s="8" t="inlineStr">
+        <is>
+          <t>1. 弹出小程序数字键盘（type="digit"带小数点）。
+2. 键盘不遮挡金额和折扣展示区域（页面自动上推）。
+3. 输入99.50后实时计算折扣（如8折=79.60）。
+4. 收起键盘后金额保持。
+5. 计算结果正确显示</t>
+        </is>
+      </c>
+      <c r="J597" s="8" t="inlineStr">
+        <is>
+          <t>小程序input的type="digit"唤起带小数点的数字键盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="20" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B598" s="20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="C598" s="20" t="inlineStr">
+        <is>
+          <t>cyzkrg-xcx-001</t>
+        </is>
+      </c>
+      <c r="D598" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E598" s="20" t="inlineStr">
+        <is>
+          <t>餐饮折扣-人工辅助
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F598" s="20" t="inlineStr">
+        <is>
+          <t>验证小程序内拍照/相册选择上传凭证（wx.chooseImage）</t>
+        </is>
+      </c>
+      <c r="G598" s="20" t="inlineStr">
+        <is>
+          <t>1. 用户在人工辅助模式下单页
+2. 已输入消费金额</t>
+        </is>
+      </c>
+      <c r="H598" s="20" t="inlineStr">
+        <is>
+          <t>1. 点击"上传凭证"按钮。
+2. 小程序弹出ActionSheet："拍照"/"从相册选择"。
+3. 选择"拍照"，摄像头打开。
+4. 拍照后确认使用该照片。
+5. 再次点击上传，选择"从相册选择"。
+6. 从相册选择一张图片</t>
+        </is>
+      </c>
+      <c r="I598" s="20" t="inlineStr">
+        <is>
+          <t>1. ActionSheet正常弹出（wx.chooseMedia/wx.chooseImage）。
+2. 选择拍照后摄像头授权弹窗正常。
+3. 拍照后图片压缩上传，缩略图正确展示。
+4. 从相册选择后图片正常上传。
+5. 支持多次选择上传多张（最多5张）</t>
+        </is>
+      </c>
+      <c r="J598" s="20" t="inlineStr">
+        <is>
+          <t>小程序图片选择API在iOS和Android行为不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="8" t="inlineStr"/>
+      <c r="B599" s="8" t="inlineStr"/>
+      <c r="C599" s="8" t="inlineStr">
+        <is>
+          <t>cyzkrg-xcx-002</t>
+        </is>
+      </c>
+      <c r="D599" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E599" s="8" t="n"/>
+      <c r="F599" s="8" t="inlineStr">
+        <is>
+          <t>验证凭证图片预览大图（wx.previewImage）</t>
+        </is>
+      </c>
+      <c r="G599" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户已上传2张凭证图片</t>
+        </is>
+      </c>
+      <c r="H599" s="8" t="inlineStr">
+        <is>
+          <t>1. 点击第1张缩略图。
+2. 观察预览行为。
+3. 在预览中左右滑动。
+4. 点击返回关闭预览</t>
+        </is>
+      </c>
+      <c r="I599" s="8" t="inlineStr">
+        <is>
+          <t>1. 调用wx.previewImage打开微信原生图片预览。
+2. 图片全屏展示，支持双指缩放。
+3. 左右滑动可查看其他已上传图片。
+4. 点击返回回到上传页面，数据不丢失</t>
+        </is>
+      </c>
+      <c r="J599" s="8" t="inlineStr">
+        <is>
+          <t>小程序图片预览是微信原生全屏预览体验</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="8" t="inlineStr"/>
+      <c r="B600" s="8" t="inlineStr"/>
+      <c r="C600" s="8" t="inlineStr">
+        <is>
+          <t>cyzkrg-xcx-003</t>
+        </is>
+      </c>
+      <c r="D600" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E600" s="8" t="n"/>
+      <c r="F600" s="8" t="inlineStr">
+        <is>
+          <t>验证用户收到验证码的小程序订阅消息推送</t>
+        </is>
+      </c>
+      <c r="G600" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户已授权订阅消息
+2. 运营已审核通过并输入验证码</t>
+        </is>
+      </c>
+      <c r="H600" s="8" t="inlineStr">
+        <is>
+          <t>1. 运营在后台点击"确认下发"验证码。
+2. 用户手机检查微信消息通知。
+3. 点击订阅消息卡片。
+4. 查看消息详情</t>
+        </is>
+      </c>
+      <c r="I600" s="8" t="inlineStr">
+        <is>
+          <t>1. 微信"服务通知"出现新消息（&lt;1分钟内）。
+2. 消息卡片显示：快乐羊毛发来服务通知。
+3. 点击卡片进入小程序订单详情页。
+4. 详情页展示验证码+商家名称+消费金额。
+5. 验证码可复制或展示给商家</t>
+        </is>
+      </c>
+      <c r="J600" s="8" t="inlineStr">
+        <is>
+          <t>订阅消息需要用户在小程序内主动授权触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="8" t="inlineStr"/>
+      <c r="B601" s="8" t="inlineStr"/>
+      <c r="C601" s="8" t="inlineStr">
+        <is>
+          <t>cyzkrg-xcx-004</t>
+        </is>
+      </c>
+      <c r="D601" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E601" s="8" t="n"/>
+      <c r="F601" s="8" t="inlineStr">
+        <is>
+          <t>验证用户未授权订阅消息时验证码的降级通知</t>
+        </is>
+      </c>
+      <c r="G601" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户拒绝了订阅消息授权
+2. 运营已下发验证码</t>
+        </is>
+      </c>
+      <c r="H601" s="8" t="inlineStr">
+        <is>
+          <t>1. 运营下发验证码。
+2. 系统检测到用户未授权订阅消息。
+3. 自动降级发送短信通知。
+4. 用户查看短信</t>
+        </is>
+      </c>
+      <c r="I601" s="8" t="inlineStr">
+        <is>
+          <t>1. 小程序订阅消息发送失败（用户未授权）。
+2. 系统自动降级为短信推送。
+3. 用户手机收到短信（含验证码/商家名/金额）。
+4. 同时，用户在小程序"我的订单"详情页也能查看验证码。
+5. 不因推送失败阻塞业务流程</t>
+        </is>
+      </c>
+      <c r="J601" s="8" t="inlineStr">
+        <is>
+          <t>三级降级：订阅消息→短信→订单详情页查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="8" t="inlineStr"/>
+      <c r="B602" s="8" t="inlineStr"/>
+      <c r="C602" s="8" t="inlineStr">
+        <is>
+          <t>cyzkrg-xcx-005</t>
+        </is>
+      </c>
+      <c r="D602" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E602" s="8" t="n"/>
+      <c r="F602" s="8" t="inlineStr">
+        <is>
+          <t>验证商家端小程序核销验证码的输入与确认交互</t>
+        </is>
+      </c>
+      <c r="G602" s="8" t="inlineStr">
+        <is>
+          <t>1. 商家端小程序已登录
+2. 用户到店出示验证码</t>
+        </is>
+      </c>
+      <c r="H602" s="8" t="inlineStr">
+        <is>
+          <t>1. 商家在小程序订单详情页点击"核销"。
+2. 弹出验证码输入弹窗/页面。
+3. 输入用户告知的验证码。
+4. 点击"确认核销"。
+5. 核销成功</t>
+        </is>
+      </c>
+      <c r="I602" s="8" t="inlineStr">
+        <is>
+          <t>1. 输入框获取焦点后弹出数字键盘。
+2. 输入验证码后按钮变为可点击。
+3. 点击核销后loading状态（防重复点击）。
+4. 核销成功弹出"核销成功"Toast。
+5. 订单状态实时更新为"已完成"</t>
+        </is>
+      </c>
+      <c r="J602" s="8" t="inlineStr">
+        <is>
+          <t>商家操作场景——简洁快速</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="20" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B603" s="20" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C603" s="20" t="inlineStr">
+        <is>
+          <t>dcfw-xcx-001</t>
+        </is>
+      </c>
+      <c r="D603" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E603" s="20" t="inlineStr">
+        <is>
+          <t>打车服务
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F603" s="20" t="inlineStr">
+        <is>
+          <t>验证小程序获取位置权限（wx.getLocation）及定位</t>
+        </is>
+      </c>
+      <c r="G603" s="20" t="inlineStr">
+        <is>
+          <t>1. 用户首次使用打车服务
+2. 手机GPS已开启</t>
+        </is>
+      </c>
+      <c r="H603" s="20" t="inlineStr">
+        <is>
+          <t>1. 点击"打车服务"入口。
+2. 小程序弹出位置授权弹窗。
+3. 点击"允许"。
+4. 观察定位结果</t>
+        </is>
+      </c>
+      <c r="I603" s="20" t="inlineStr">
+        <is>
+          <t>1. 微信原生授权弹窗："快乐羊毛申请获取你的地理位置"。
+2. 允许后获取当前GPS坐标。
+3. 页面展示当前位置地址（逆地理编码）。
+4. 定位精度在可接受范围内（偏差&lt;100米）</t>
+        </is>
+      </c>
+      <c r="J603" s="20" t="inlineStr">
+        <is>
+          <t>小程序wx.getLocation需要在app.json配置permission</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="8" t="inlineStr"/>
+      <c r="B604" s="8" t="inlineStr"/>
+      <c r="C604" s="8" t="inlineStr">
+        <is>
+          <t>dcfw-xcx-002</t>
+        </is>
+      </c>
+      <c r="D604" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E604" s="8" t="n"/>
+      <c r="F604" s="8" t="inlineStr">
+        <is>
+          <t>验证拒绝位置授权后的引导重新授权流程</t>
+        </is>
+      </c>
+      <c r="G604" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户已拒绝位置授权</t>
+        </is>
+      </c>
+      <c r="H604" s="8" t="inlineStr">
+        <is>
+          <t>1. 进入打车页面，检测到无位置权限。
+2. 页面显示"需要位置权限"提示。
+3. 点击"去设置"按钮。
+4. 跳转到微信小程序设置页（wx.openSetting）。
+5. 用户手动开启位置权限。
+6. 返回小程序</t>
+        </is>
+      </c>
+      <c r="I604" s="8" t="inlineStr">
+        <is>
+          <t>1. 页面正确识别无权限状态。
+2. 点击"去设置"打开小程序权限设置页。
+3. 设置页列出"位置信息"开关。
+4. 开启后返回小程序，自动重新获取位置。
+5. 定位成功，页面正常展示</t>
+        </is>
+      </c>
+      <c r="J604" s="8" t="inlineStr">
+        <is>
+          <t>小程序拒绝授权后不能再次弹窗，只能引导去设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="8" t="inlineStr"/>
+      <c r="B605" s="8" t="inlineStr"/>
+      <c r="C605" s="8" t="inlineStr">
+        <is>
+          <t>dcfw-xcx-003</t>
+        </is>
+      </c>
+      <c r="D605" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E605" s="8" t="n"/>
+      <c r="F605" s="8" t="inlineStr">
+        <is>
+          <t>验证打车跳转第三方小程序（滴滴/高德）</t>
+        </is>
+      </c>
+      <c r="G605" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户已选择目的地
+2. 准备跳转第三方打车</t>
+        </is>
+      </c>
+      <c r="H605" s="8" t="inlineStr">
+        <is>
+          <t>1. 选择"滴滴出行"打车。
+2. 点击"呼叫快车"。
+3. 观察跳转行为</t>
+        </is>
+      </c>
+      <c r="I605" s="8" t="inlineStr">
+        <is>
+          <t>1. 调用wx.navigateToMiniProgram跳转至滴滴小程序。
+2. 微信弹出"即将打开滴滴出行小程序"确认框。
+3. 确认后跳转成功，携带起点/终点参数。
+4. 取消则留在当前小程序。
+5. 从滴滴小程序返回时回到打车页面</t>
+        </is>
+      </c>
+      <c r="J605" s="8" t="inlineStr">
+        <is>
+          <t>跳转其他小程序需用户确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="20" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B606" s="20" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C606" s="20" t="inlineStr">
+        <is>
+          <t>dypw-xcx-001</t>
+        </is>
+      </c>
+      <c r="D606" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E606" s="20" t="inlineStr">
+        <is>
+          <t>电影票务
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F606" s="20" t="inlineStr">
+        <is>
+          <t>验证电影选座界面在小程序中的触控交互（缩放/拖动）</t>
+        </is>
+      </c>
+      <c r="G606" s="20" t="inlineStr">
+        <is>
+          <t>1. 用户已选择影片和场次
+2. 进入选座页面</t>
+        </is>
+      </c>
+      <c r="H606" s="20" t="inlineStr">
+        <is>
+          <t>1. 查看座位图展示。
+2. 双指捏合缩小座位图。
+3. 双指张开放大座位图。
+4. 单指拖动查看不同区域。
+5. 点击绿色可选座位。
+6. 已选座位高亮标记</t>
+        </is>
+      </c>
+      <c r="I606" s="20" t="inlineStr">
+        <is>
+          <t>1. 座位图在小程序canvas或movable-view中正常渲染。
+2. 双指缩放流畅，无卡顿。
+3. 拖动时不触发页面下拉刷新（需禁止冒泡）。
+4. 点击座位响应准确（不会误触相邻座位）。
+5. 最多选4座，选第5座提示限制。
+6. 已售灰色座位点击无反应</t>
+        </is>
+      </c>
+      <c r="J606" s="20" t="inlineStr">
+        <is>
+          <t>小程序触控事件处理与原生App不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="8" t="inlineStr"/>
+      <c r="B607" s="8" t="inlineStr"/>
+      <c r="C607" s="8" t="inlineStr">
+        <is>
+          <t>dypw-xcx-002</t>
+        </is>
+      </c>
+      <c r="D607" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E607" s="8" t="n"/>
+      <c r="F607" s="8" t="inlineStr">
+        <is>
+          <t>验证电影出票后取票码在小程序内展示和保存</t>
+        </is>
+      </c>
+      <c r="G607" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户已购票成功
+2. 出票完成</t>
+        </is>
+      </c>
+      <c r="H607" s="8" t="inlineStr">
+        <is>
+          <t>1. 查看订单详情页的取票码/二维码。
+2. 调整手机亮度查看二维码清晰度。
+3. 长按二维码图片。
+4. 点击"保存到手机"（如有该功能）</t>
+        </is>
+      </c>
+      <c r="I607" s="8" t="inlineStr">
+        <is>
+          <t>1. 取票码数字清晰显示，字体大小合适。
+2. 二维码清晰可扫（影院扫码机能识别）。
+3. 小程序可调用wx.setScreenBrightness提高亮度。
+4. 长按二维码弹出保存选项（需相册授权）。
+5. 同时展示短信取票码文本</t>
+        </is>
+      </c>
+      <c r="J607" s="8" t="inlineStr">
+        <is>
+          <t>到影院后需要在小程序内展示取票码给机器扫</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="8" t="inlineStr"/>
+      <c r="B608" s="8" t="inlineStr"/>
+      <c r="C608" s="8" t="inlineStr">
+        <is>
+          <t>dypw-xcx-003</t>
+        </is>
+      </c>
+      <c r="D608" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E608" s="8" t="n"/>
+      <c r="F608" s="8" t="inlineStr">
+        <is>
+          <t>验证选座页面在小程序中实时更新已售座位</t>
+        </is>
+      </c>
+      <c r="G608" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户A和用户B同时浏览同一场次</t>
+        </is>
+      </c>
+      <c r="H608" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户A在选座页面看到某座位可选。
+2. 用户B购买了该座位。
+3. 用户A的页面是否实时更新。
+4. 用户A点击该座位</t>
+        </is>
+      </c>
+      <c r="I608" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户A页面通过WebSocket或轮询检测更新。
+2. 被购买的座位自动变为灰色。
+3. 如用户A选中后提交时座位已被占，提示"该座位已被他人选择，请重新选座"。
+4. 不产生重复出票</t>
+        </is>
+      </c>
+      <c r="J608" s="8" t="inlineStr">
+        <is>
+          <t>小程序可使用wx.connectSocket做实时通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="20" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B609" s="20" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C609" s="20" t="inlineStr">
+        <is>
+          <t>hycz-xcx-001</t>
+        </is>
+      </c>
+      <c r="D609" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E609" s="20" t="inlineStr">
+        <is>
+          <t>会员充值
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F609" s="20" t="inlineStr">
+        <is>
+          <t>验证小程序内手机号输入键盘和运营商自动识别</t>
+        </is>
+      </c>
+      <c r="G609" s="20" t="inlineStr">
+        <is>
+          <t>1. 用户选择"话费充值"分类
+2. 选择50元面额</t>
+        </is>
+      </c>
+      <c r="H609" s="20" t="inlineStr">
+        <is>
+          <t>1. 点击手机号输入框。
+2. 观察弹出键盘类型。
+3. 输入手机号"13800138000"。
+4. 观察运营商自动识别。
+5. 输入完成后收起键盘</t>
+        </is>
+      </c>
+      <c r="I609" s="20" t="inlineStr">
+        <is>
+          <t>1. 弹出纯数字键盘（type="number"）。
+2. 输入11位后自动收起键盘或限制继续输入。
+3. 输入过程中自动识别运营商："中国移动"。
+4. 运营商标识Icon正确展示。
+5. 键盘收起后页面恢复正常布局</t>
+        </is>
+      </c>
+      <c r="J609" s="20" t="inlineStr">
+        <is>
+          <t>小程序input type="number"不带小数点的纯数字键盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="8" t="inlineStr"/>
+      <c r="B610" s="8" t="inlineStr"/>
+      <c r="C610" s="8" t="inlineStr">
+        <is>
+          <t>hycz-xcx-002</t>
+        </is>
+      </c>
+      <c r="D610" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E610" s="8" t="n"/>
+      <c r="F610" s="8" t="inlineStr">
+        <is>
+          <t>验证充值成功后订阅消息通知推送</t>
+        </is>
+      </c>
+      <c r="G610" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户已授权订阅消息
+2. 话费充值成功</t>
+        </is>
+      </c>
+      <c r="H610" s="8" t="inlineStr">
+        <is>
+          <t>1. 充值完成后等待通知。
+2. 检查微信"服务通知"。
+3. 点击通知卡片</t>
+        </is>
+      </c>
+      <c r="I610" s="8" t="inlineStr">
+        <is>
+          <t>1. 微信"服务通知"收到充值成功通知（&lt;1分钟）。
+2. 通知内容：充值金额/充值账号/充值状态。
+3. 点击卡片跳转到小程序对应订单详情页。
+4. 详情页展示"充值成功"状态</t>
+        </is>
+      </c>
+      <c r="J610" s="8" t="inlineStr">
+        <is>
+          <t>充值结果通过订阅消息推送给用户</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="20" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B611" s="20" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C611" s="20" t="inlineStr">
+        <is>
+          <t>jdgw-xcx-001</t>
+        </is>
+      </c>
+      <c r="D611" s="20" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E611" s="20" t="inlineStr">
+        <is>
+          <t>家电购物
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F611" s="20" t="inlineStr">
+        <is>
+          <t>验证小程序跳转京东App/京东小程序完成购买</t>
+        </is>
+      </c>
+      <c r="G611" s="20" t="inlineStr">
+        <is>
+          <t>1. 用户在家电购物列表
+2. 手机已安装京东App</t>
+        </is>
+      </c>
+      <c r="H611" s="20" t="inlineStr">
+        <is>
+          <t>1. 点击某家电商品。
+2. 查看商品详情和"预计返利XX元"。
+3. 点击"去购买"。
+4. 观察跳转行为</t>
+        </is>
+      </c>
+      <c r="I611" s="20" t="inlineStr">
+        <is>
+          <t>1. 跳转时携带CPS推广参数（辛贝渠道标识）。
+2. 优先跳转京东App（通过scheme）。
+3. 未安装京东App时跳转京东小程序或H5。
+4. 跳转链接中推广参数正确（用于佣金追踪）。
+5. 返回快乐羊毛小程序时页面恢复</t>
+        </is>
+      </c>
+      <c r="J611" s="20" t="inlineStr">
+        <is>
+          <t>确保CPS推广参数不丢失</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="8" t="inlineStr"/>
+      <c r="B612" s="8" t="inlineStr"/>
+      <c r="C612" s="8" t="inlineStr">
+        <is>
+          <t>jdgw-xcx-002</t>
+        </is>
+      </c>
+      <c r="D612" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E612" s="8" t="n"/>
+      <c r="F612" s="8" t="inlineStr">
+        <is>
+          <t>验证家电商品图片在小程序中的懒加载</t>
+        </is>
+      </c>
+      <c r="G612" s="8" t="inlineStr">
+        <is>
+          <t>1. 家电列表有20+商品，每个有主图</t>
+        </is>
+      </c>
+      <c r="H612" s="8" t="inlineStr">
+        <is>
+          <t>1. 进入家电购物列表。
+2. 观察首屏图片加载。
+3. 快速向下滚动。
+4. 观察屏幕外图片加载行为</t>
+        </is>
+      </c>
+      <c r="I612" s="8" t="inlineStr">
+        <is>
+          <t>1. 首屏内图片优先加载。
+2. 屏幕外图片不立即加载（lazy-load）。
+3. 滚动到视口内时自动加载。
+4. 图片未加载时显示占位图。
+5. 列表滚动流畅不卡顿</t>
+        </is>
+      </c>
+      <c r="J612" s="8" t="inlineStr">
+        <is>
+          <t>小程序image组件支持lazy-load属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="20" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B613" s="20" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C613" s="20" t="inlineStr">
+        <is>
+          <t>gwfl-xcx-001</t>
+        </is>
+      </c>
+      <c r="D613" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E613" s="20" t="inlineStr">
+        <is>
+          <t>购物返利
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F613" s="20" t="inlineStr">
+        <is>
+          <t>验证小程序内粘贴商品链接的剪贴板读取行为</t>
+        </is>
+      </c>
+      <c r="G613" s="20" t="inlineStr">
+        <is>
+          <t>1. 用户已在淘宝/京东App复制了商品链接
+2. 切换到快乐羊毛小程序</t>
+        </is>
+      </c>
+      <c r="H613" s="20" t="inlineStr">
+        <is>
+          <t>1. 切换到快乐羊毛小程序。
+2. 进入购物返利页面。
+3. 点击搜索框/粘贴区域。
+4. 长按粘贴或直接触发自动识别。
+5. 检查链接解析</t>
+        </is>
+      </c>
+      <c r="I613" s="20" t="inlineStr">
+        <is>
+          <t>1. 小程序可通过wx.getClipboardData读取剪贴板。
+2. 微信可能弹出"快乐羊毛要读取你的剪贴板"提示（iOS 14+）。
+3. 用户允许后粘贴内容正确。
+4. 系统解析商品链接，展示商品信息和预计返利。
+5. 生成专属推广链接</t>
+        </is>
+      </c>
+      <c r="J613" s="20" t="inlineStr">
+        <is>
+          <t>iOS 14+有剪贴板读取隐私提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="8" t="inlineStr"/>
+      <c r="B614" s="8" t="inlineStr"/>
+      <c r="C614" s="8" t="inlineStr">
+        <is>
+          <t>gwfl-xcx-002</t>
+        </is>
+      </c>
+      <c r="D614" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E614" s="8" t="n"/>
+      <c r="F614" s="8" t="inlineStr">
+        <is>
+          <t>验证购物返利授权绑定淘宝/京东账号流程</t>
+        </is>
+      </c>
+      <c r="G614" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户首次使用购物返利
+2. 未绑定淘宝/京东账号</t>
+        </is>
+      </c>
+      <c r="H614" s="8" t="inlineStr">
+        <is>
+          <t>1. 进入购物返利功能。
+2. 提示需要绑定平台账号。
+3. 点击"绑定淘宝账号"。
+4. 跳转淘宝授权页面（web-view）。
+5. 完成授权后返回小程序</t>
+        </is>
+      </c>
+      <c r="I614" s="8" t="inlineStr">
+        <is>
+          <t>1. 绑定提示清晰告知用途。
+2. 通过web-view打开淘宝联盟授权页。
+3. 用户在web-view中完成淘宝登录授权。
+4. 授权回调返回小程序，绑定成功。
+5. 显示已绑定状态</t>
+        </is>
+      </c>
+      <c r="J614" s="8" t="inlineStr">
+        <is>
+          <t>第三方授权在小程序中通过web-view实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="20" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B615" s="20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="C615" s="20" t="inlineStr">
+        <is>
+          <t>grzx-xcx-001</t>
+        </is>
+      </c>
+      <c r="D615" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E615" s="20" t="inlineStr">
+        <is>
+          <t>个人中心
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F615" s="20" t="inlineStr">
+        <is>
+          <t>验证微信一键登录获取手机号的完整流程</t>
+        </is>
+      </c>
+      <c r="G615" s="20" t="inlineStr">
+        <is>
+          <t>1. 用户首次打开小程序
+2. 未注册过</t>
+        </is>
+      </c>
+      <c r="H615" s="20" t="inlineStr">
+        <is>
+          <t>1. 进入小程序，显示登录页。
+2. 点击"微信一键登录"按钮（button open-type="getPhoneNumber"）。
+3. 微信弹出手机号授权弹窗。
+4. 点击"允许"。
+5. 登录成功跳转首页</t>
+        </is>
+      </c>
+      <c r="I615" s="20" t="inlineStr">
+        <is>
+          <t>1. 登录按钮使用小程序原生&lt;button&gt;组件。
+2. 微信弹出"快乐羊毛申请获取你的手机号"授权框。
+3. 允许后获取加密手机号数据（encryptedData+iv）。
+4. 后端解密得到手机号，自动注册新用户。
+5. 登录成功，个人中心显示脱敏手机号（138****8000）</t>
+        </is>
+      </c>
+      <c r="J615" s="20" t="inlineStr">
+        <is>
+          <t>小程序获取手机号必须用&lt;button&gt;组件，不能js直接调用</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="8" t="inlineStr"/>
+      <c r="B616" s="8" t="inlineStr"/>
+      <c r="C616" s="8" t="inlineStr">
+        <is>
+          <t>grzx-xcx-002</t>
+        </is>
+      </c>
+      <c r="D616" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E616" s="8" t="n"/>
+      <c r="F616" s="8" t="inlineStr">
+        <is>
+          <t>验证推广海报生成并保存到相册（wx.saveImageToPhotosAlbum）</t>
+        </is>
+      </c>
+      <c r="G616" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户已登录
+2. 进入推广中心页面</t>
+        </is>
+      </c>
+      <c r="H616" s="8" t="inlineStr">
+        <is>
+          <t>1. 点击"生成推广海报"。
+2. 等待海报生成（canvas绘制）。
+3. 海报展示个人专属二维码。
+4. 点击"保存到相册"。
+5. 首次弹出相册写入授权</t>
+        </is>
+      </c>
+      <c r="I616" s="8" t="inlineStr">
+        <is>
+          <t>1. 海报通过canvas绘制完成。
+2. 海报包含个人专属二维码（唯一、可识别）。
+3. 点击保存弹出微信授权"保存到相册"。
+4. 允许后保存成功，提示"已保存到相册"。
+5. 拒绝授权时提示"请在设置中开启相册权限"</t>
+        </is>
+      </c>
+      <c r="J616" s="8" t="inlineStr">
+        <is>
+          <t>小程序saveImage需要scope.writePhotosAlbum授权</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="8" t="inlineStr"/>
+      <c r="B617" s="8" t="inlineStr"/>
+      <c r="C617" s="8" t="inlineStr">
+        <is>
+          <t>grzx-xcx-003</t>
+        </is>
+      </c>
+      <c r="D617" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E617" s="8" t="n"/>
+      <c r="F617" s="8" t="inlineStr">
+        <is>
+          <t>验证订单列表下拉刷新和分页加载交互</t>
+        </is>
+      </c>
+      <c r="G617" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户有10+笔订单
+2. 在"我的订单"页面</t>
+        </is>
+      </c>
+      <c r="H617" s="8" t="inlineStr">
+        <is>
+          <t>1. 下拉刷新订单列表。
+2. 观察刷新动画。
+3. 滚动到底部加载更多。
+4. 按状态Tab切换筛选。
+5. 按订单类型筛选</t>
+        </is>
+      </c>
+      <c r="I617" s="8" t="inlineStr">
+        <is>
+          <t>1. 下拉显示微信原生刷新动画。
+2. 刷新后列表更新为最新数据。
+3. 触底自动加载下一页。
+4. 切换状态Tab筛选正确（待支付/已完成/已退款等）。
+5. 按业务线筛选正确（外卖券/充值/餐饮等）</t>
+        </is>
+      </c>
+      <c r="J617" s="8" t="inlineStr">
+        <is>
+          <t>订单列表是高频访问页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="8" t="inlineStr"/>
+      <c r="B618" s="8" t="inlineStr"/>
+      <c r="C618" s="8" t="inlineStr">
+        <is>
+          <t>grzx-xcx-004</t>
+        </is>
+      </c>
+      <c r="D618" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E618" s="8" t="n"/>
+      <c r="F618" s="8" t="inlineStr">
+        <is>
+          <t>验证小程序分享推广海报/推广链接到微信好友</t>
+        </is>
+      </c>
+      <c r="G618" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户在推广中心
+2. 已生成推广二维码</t>
+        </is>
+      </c>
+      <c r="H618" s="8" t="inlineStr">
+        <is>
+          <t>1. 点击"分享给好友"按钮。
+2. 选择好友发送分享卡片。
+3. 好友点击卡片进入小程序。
+4. 好友注册后检查推广关系</t>
+        </is>
+      </c>
+      <c r="I618" s="8" t="inlineStr">
+        <is>
+          <t>1. 分享卡片标题和描述正确（如"快来快乐羊毛省钱"）。
+2. 卡片携带推广者ID参数。
+3. 好友点击后进入小程序并绑定推广关系。
+4. 推广中心"我的团队"新增该好友。
+5. 好友消费后推广者可获得佣金</t>
+        </is>
+      </c>
+      <c r="J618" s="8" t="inlineStr">
+        <is>
+          <t>分享裂变是获客核心——参数传递不能丢</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="8" t="inlineStr"/>
+      <c r="B619" s="8" t="inlineStr"/>
+      <c r="C619" s="8" t="inlineStr">
+        <is>
+          <t>grzx-xcx-005</t>
+        </is>
+      </c>
+      <c r="D619" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E619" s="8" t="n"/>
+      <c r="F619" s="8" t="inlineStr">
+        <is>
+          <t>验证佣金/余额数据在小程序端实时更新</t>
+        </is>
+      </c>
+      <c r="G619" s="8" t="inlineStr">
+        <is>
+          <t>1. 用户是代理商
+2. 有佣金记录</t>
+        </is>
+      </c>
+      <c r="H619" s="8" t="inlineStr">
+        <is>
+          <t>1. 查看个人中心"预估收入"和"可提现余额"。
+2. 通过另一个账号完成一笔新订单。
+3. 下拉刷新个人中心。
+4. 检查佣金变化</t>
+        </is>
+      </c>
+      <c r="I619" s="8" t="inlineStr">
+        <is>
+          <t>1. "预估收入"和"可提现余额"正确展示。
+2. 新订单完成后下拉刷新。
+3. "预估收入"增加相应佣金金额。
+4. 数据与后台管理端完全一致。
+5. 金额精确到分（0.00格式）</t>
+        </is>
+      </c>
+      <c r="J619" s="8" t="inlineStr">
+        <is>
+          <t>佣金准确性直接影响用户信任</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="20" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B620" s="20" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C620" s="20" t="inlineStr">
+        <is>
+          <t>jycz-xcx-001</t>
+        </is>
+      </c>
+      <c r="D620" s="20" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E620" s="20" t="inlineStr">
+        <is>
+          <t>加油/充电
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F620" s="20" t="inlineStr">
+        <is>
+          <t>验证加油站/充电桩列表的位置排序（wx.getLocation）</t>
+        </is>
+      </c>
+      <c r="G620" s="20" t="inlineStr">
+        <is>
+          <t>1. 用户已授权位置权限
+2. 附近有加油站/充电桩数据</t>
+        </is>
+      </c>
+      <c r="H620" s="20" t="inlineStr">
+        <is>
+          <t>1. 进入加油/充电页面。
+2. 系统获取当前位置。
+3. 展示附近站点列表。
+4. 检查排序是否按距离</t>
+        </is>
+      </c>
+      <c r="I620" s="20" t="inlineStr">
+        <is>
+          <t>1. 位置获取成功。
+2. 列表按距离从近到远排序。
+3. 每项展示名称+距离（如"中石化加油站 1.2km"）。
+4. 点击某站点跳转第三方App/H5（携带CPS参数）</t>
+        </is>
+      </c>
+      <c r="J620" s="20" t="inlineStr">
+        <is>
+          <t>复用打车模块的位置授权</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="20" t="inlineStr">
+        <is>
+          <t>商家端</t>
+        </is>
+      </c>
+      <c r="B621" s="20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="C621" s="20" t="inlineStr">
+        <is>
+          <t>sjd-xcx-001</t>
+        </is>
+      </c>
+      <c r="D621" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E621" s="20" t="inlineStr">
+        <is>
+          <t>商家端收银台
+(小程序环境)</t>
+        </is>
+      </c>
+      <c r="F621" s="20" t="inlineStr">
+        <is>
+          <t>验证商家端小程序收银台生成二维码的完整交互</t>
+        </is>
+      </c>
+      <c r="G621" s="20" t="inlineStr">
+        <is>
+          <t>1. 商家品牌主账号/门店子账号已登录商家端小程序</t>
+        </is>
+      </c>
+      <c r="H621" s="20" t="inlineStr">
+        <is>
+          <t>1. 进入收银台页面。
+2. 点击金额输入框，弹出数字键盘。
+3. 输入消费金额100。
+4. 系统自动展示折扣计算（8折=实付80元）。
+5. 点击"生成收款码"按钮。
+6. 等待二维码生成。
+7. 展示二维码和15分钟倒计时</t>
+        </is>
+      </c>
+      <c r="I621" s="20" t="inlineStr">
+        <is>
+          <t>1. 数字键盘正常弹出（带小数点）。
+2. 输入金额后折扣实时计算并展示。
+3. 点击生成后按钮变为loading状态。
+4. 二维码生成成功，清晰可扫。
+5. 倒计时正确显示"14:59"并倒数。
+6. 页面布局适配不同手机屏幕</t>
+        </is>
+      </c>
+      <c r="J621" s="20" t="inlineStr">
+        <is>
+          <t>收银台是商家最高频使用的功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="8" t="inlineStr"/>
+      <c r="B622" s="8" t="inlineStr"/>
+      <c r="C622" s="8" t="inlineStr">
+        <is>
+          <t>sjd-xcx-002</t>
+        </is>
+      </c>
+      <c r="D622" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E622" s="8" t="n"/>
+      <c r="F622" s="8" t="inlineStr">
+        <is>
+          <t>验证商家端小程序验证码核销输入交互</t>
+        </is>
+      </c>
+      <c r="G622" s="8" t="inlineStr">
+        <is>
+          <t>1. 有一笔人工辅助订单已下发验证码
+2. 用户到店出示验证码</t>
+        </is>
+      </c>
+      <c r="H622" s="8" t="inlineStr">
+        <is>
+          <t>1. 商家在订单管理中找到该订单。
+2. 点击"核销"按钮。
+3. 输入用户出示的验证码。
+4. 点击"确认核销"。
+5. 等待结果</t>
+        </is>
+      </c>
+      <c r="I622" s="8" t="inlineStr">
+        <is>
+          <t>1. 弹出验证码输入框，自动获取焦点。
+2. 数字键盘弹出。
+3. 输入完成后"确认核销"按钮可点击。
+4. 点击后按钮loading防重复。
+5. 核销成功弹出Toast"核销成功"。
+6. 订单状态自动刷新为"已完成"</t>
+        </is>
+      </c>
+      <c r="J622" s="8" t="inlineStr">
+        <is>
+          <t>核销操作需要快速简洁</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="8" t="inlineStr"/>
+      <c r="B623" s="8" t="inlineStr"/>
+      <c r="C623" s="8" t="inlineStr">
+        <is>
+          <t>sjd-xcx-003</t>
+        </is>
+      </c>
+      <c r="D623" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E623" s="8" t="n"/>
+      <c r="F623" s="8" t="inlineStr">
+        <is>
+          <t>验证商家端小程序订单管理列表的筛选交互</t>
+        </is>
+      </c>
+      <c r="G623" s="8" t="inlineStr">
+        <is>
+          <t>1. 商家端小程序已登录
+2. 有多笔订单</t>
+        </is>
+      </c>
+      <c r="H623" s="8" t="inlineStr">
+        <is>
+          <t>1. 进入订单管理页面。
+2. 点击日期筛选，选择日期范围。
+3. 点击状态筛选（已支付/已退款等）。
+4. 下拉刷新列表。
+5. 滚动到底部加载更多</t>
+        </is>
+      </c>
+      <c r="I623" s="8" t="inlineStr">
+        <is>
+          <t>1. 日期选择器使用小程序picker组件（mode="date"）。
+2. 状态筛选正常工作。
+3. 下拉刷新显示微信原生动画。
+4. 触底加载分页数据。
+5. 只显示本门店数据</t>
+        </is>
+      </c>
+      <c r="J623" s="8" t="inlineStr">
+        <is>
+          <t>小程序picker的日期选择器交互</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="8" t="inlineStr"/>
+      <c r="B624" s="8" t="inlineStr"/>
+      <c r="C624" s="8" t="inlineStr">
+        <is>
+          <t>sjd-xcx-004</t>
+        </is>
+      </c>
+      <c r="D624" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E624" s="8" t="n"/>
+      <c r="F624" s="8" t="inlineStr">
+        <is>
+          <t>验证门店子账号登录商家端小程序的权限隔离</t>
+        </is>
+      </c>
+      <c r="G624" s="8" t="inlineStr">
+        <is>
+          <t>1. 品牌有门店A和门店B
+2. 使用门店A的子账号登录</t>
+        </is>
+      </c>
+      <c r="H624" s="8" t="inlineStr">
+        <is>
+          <t>1. 门店A子账号登录商家端小程序。
+2. 查看订单管理——只显示门店A订单。
+3. 查看数据统计——只显示门店A流水。
+4. 检查菜单——无"创建子账号"功能。
+5. 检查收银台——无"修正金额"按钮</t>
+        </is>
+      </c>
+      <c r="I624" s="8" t="inlineStr">
+        <is>
+          <t>1. 订单列表只展示门店A的数据。
+2. 数据统计只有门店A的流水和核销笔数。
+3. 菜单中无子账号管理入口。
+4. 收银台无手动修正金额功能。
+5. 通过修改API参数尝试查看门店B数据返回"无权限"</t>
+        </is>
+      </c>
+      <c r="J624" s="8" t="inlineStr">
+        <is>
+          <t>数据隔离在小程序端也必须严格执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="20" t="inlineStr">
+        <is>
+          <t>管理后台</t>
+        </is>
+      </c>
+      <c r="B625" s="20" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C625" s="20" t="inlineStr">
+        <is>
+          <t>htgl-pc-001</t>
+        </is>
+      </c>
+      <c r="D625" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E625" s="20" t="inlineStr">
+        <is>
+          <t>管理后台
+(PC浏览器环境)</t>
+        </is>
+      </c>
+      <c r="F625" s="20" t="inlineStr">
+        <is>
+          <t>验证管理后台登录和核心操作在Chrome浏览器正常运行</t>
+        </is>
+      </c>
+      <c r="G625" s="20" t="inlineStr">
+        <is>
+          <t>1. Chrome最新版浏览器
+2. 访问 https://red.jinyedaojia.com/</t>
+        </is>
+      </c>
+      <c r="H625" s="20" t="inlineStr">
+        <is>
+          <t>1. 输入admin/admin123登录。
+2. 查看订单列表并翻页。
+3. 执行分佣配置修改。
+4. 查看选品仓库。
+5. 查看退款审核列表</t>
+        </is>
+      </c>
+      <c r="I625" s="20" t="inlineStr">
+        <is>
+          <t>1. 登录成功进入后台首页。
+2. 订单列表分页正常（首屏加载&lt;3秒）。
+3. 分佣配置保存成功。
+4. 选品仓库列表正常。
+5. 退款列表可正常审核操作。
+6. 页面布局完整无错位</t>
+        </is>
+      </c>
+      <c r="J625" s="20" t="inlineStr">
+        <is>
+          <t>后台测试环境: https://red.jinyedaojia.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="8" t="inlineStr"/>
+      <c r="B626" s="8" t="inlineStr"/>
+      <c r="C626" s="8" t="inlineStr">
+        <is>
+          <t>htgl-pc-002</t>
+        </is>
+      </c>
+      <c r="D626" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E626" s="8" t="n"/>
+      <c r="F626" s="8" t="inlineStr">
+        <is>
+          <t>验证管理后台Excel文件上传/下载功能在浏览器中正常</t>
+        </is>
+      </c>
+      <c r="G626" s="8" t="inlineStr">
+        <is>
+          <t>1. Chrome浏览器已登录后台
+2. 准备测试Excel文件</t>
+        </is>
+      </c>
+      <c r="H626" s="8" t="inlineStr">
+        <is>
+          <t>1. 在佣金导入页面点击"选择文件"。
+2. 浏览器弹出文件选择框。
+3. 选择Excel文件上传。
+4. 在对账管理页面点击"导出"。
+5. 检查浏览器下载</t>
+        </is>
+      </c>
+      <c r="I626" s="8" t="inlineStr">
+        <is>
+          <t>1. 文件选择框正常弹出。
+2. 选择.xlsx文件后正常上传解析。
+3. 导出Excel正常下载到本地。
+4. 下载文件名含日期标识。
+5. 打开Excel数据完整，中文无乱码</t>
+        </is>
+      </c>
+      <c r="J626" s="8" t="inlineStr">
+        <is>
+          <t>上传/下载是后台常见操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="8" t="inlineStr"/>
+      <c r="B627" s="8" t="inlineStr"/>
+      <c r="C627" s="8" t="inlineStr">
+        <is>
+          <t>htgl-pc-003</t>
+        </is>
+      </c>
+      <c r="D627" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E627" s="8" t="n"/>
+      <c r="F627" s="8" t="inlineStr">
+        <is>
+          <t>验证管理后台在Edge浏览器的兼容性</t>
+        </is>
+      </c>
+      <c r="G627" s="8" t="inlineStr">
+        <is>
+          <t>1. Edge最新版浏览器
+2. 管理员账号</t>
+        </is>
+      </c>
+      <c r="H627" s="8" t="inlineStr">
+        <is>
+          <t>1. 在Edge中访问后台登录。
+2. 查看订单列表和数据报表。
+3. 执行退款审核操作。
+4. 查看选品仓库并执行一键同步。
+5. 上传Excel文件</t>
+        </is>
+      </c>
+      <c r="I627" s="8" t="inlineStr">
+        <is>
+          <t>1. 所有页面布局与Chrome一致。
+2. 表格渲染正常。
+3. 退款审核弹窗正常显示。
+4. 同步进度条正常。
+5. 文件上传正常</t>
+        </is>
+      </c>
+      <c r="J627" s="8" t="inlineStr">
+        <is>
+          <t>确保Chrome和Edge两个主流浏览器都兼容</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J453"/>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="E67:E90"/>
     <mergeCell ref="A552:J552"/>
     <mergeCell ref="E20:E37"/>
     <mergeCell ref="E38:E56"/>
+    <mergeCell ref="A582:J582"/>
     <mergeCell ref="A455:J455"/>
     <mergeCell ref="E2:E19"/>
     <mergeCell ref="E57:E65"/>
@@ -26180,7 +28570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="29.125" customWidth="1" style="3" min="2" max="4"/>
@@ -27123,6 +29513,248 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="B59" s="10">
+        <f>== 各模块·小程序环境专项用例 ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>免费资料区(小程序环境): 下拉刷新/页面栈/剪贴板/分享</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>外卖红包(小程序环境): App跳转/scheme/降级H5/分享卡片</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>通用券(小程序环境): 微信支付交互/取消重付/剪贴板/协议勾选</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>餐饮直连(小程序环境): 扫码/微信扫一扫/前后台切换/数字键盘</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>餐饮人工辅助(小程序环境): chooseImage/预览/订阅消息/降级/核销</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>打车服务(小程序环境): 位置授权/openSetting/跳转其他小程序</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>电影票务(小程序环境): 触控选座/取票码展示/实时座位</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>会员充值(小程序环境): 数字键盘/运营商识别/订阅消息</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>家电购物(小程序环境): 跳转京东/懒加载</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>购物返利(小程序环境): 剪贴板读取/web-view授权</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>个人中心(小程序环境): 手机号授权/海报canvas/保存相册/分享裂变</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>加油充电(小程序环境): 位置排序</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>商家端</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>商家端收银台(小程序环境): 二维码生成/核销输入/订单筛选/权限隔离</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>管理后台</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>管理后台(PC浏览器): Chrome/Edge兼容/上传下载</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>各模块小程序环境小计</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>★ 完善版v2 最终总计 ★</t>
+        </is>
+      </c>
+      <c r="C76" s="15">
+        <f>574+45-2</f>
+        <v/>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>原574 - 去重2 + 模块小程序环境45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/快乐羊毛系统/功能测试需要的文件2026.03.17/最终版测试用例/快乐羊毛系统完整测试用例2026.03.17（付仕菊）-V3.0完善版v2.xlsx
+++ b/快乐羊毛系统/功能测试需要的文件2026.03.17/最终版测试用例/快乐羊毛系统完整测试用例2026.03.17（付仕菊）-V3.0完善版v2.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -225,8 +225,14 @@
       <color rgb="000D47A1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00E65100"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="40">
     <fill>
       <patternFill/>
     </fill>
@@ -447,6 +453,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00BBDEFB"/>
         <bgColor rgb="00BBDEFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E65100"/>
+        <bgColor rgb="00E65100"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+        <bgColor rgb="00FFF3E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -777,7 +795,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -826,6 +844,13 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1276,7 +1301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J571"/>
+  <dimension ref="A1:J593"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="6.5" customWidth="1" style="3" min="1" max="3"/>
@@ -20170,50 +20195,15 @@
     </row>
     <row r="455">
       <c r="A455" s="8" t="inlineStr"/>
-      <c r="B455" s="8" t="inlineStr"/>
-      <c r="C455" s="8" t="inlineStr">
-        <is>
-          <t>wlyc-005</t>
-        </is>
-      </c>
-      <c r="D455" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E455" s="8" t="n"/>
-      <c r="F455" s="8" t="inlineStr">
-        <is>
-          <t>验证断网环境下凭证图片上传的处理</t>
-        </is>
-      </c>
-      <c r="G455" s="8" t="inlineStr">
-        <is>
-          <t>1. 用户在人工辅助模式下单页
-2. 已输入消费金额</t>
-        </is>
-      </c>
-      <c r="H455" s="8" t="inlineStr">
-        <is>
-          <t>1. 选择一张凭证图片开始上传。
-2. 上传过程中断开网络。
-3. 观察上传结果提示。
-4. 恢复网络后重新上传</t>
-        </is>
-      </c>
-      <c r="I455" s="8" t="inlineStr">
-        <is>
-          <t>1. 上传失败，提示"网络异常，上传失败"。
-2. 已上传成功的图片不受影响（如有多张）。
-3. 恢复网络后可重新选择上传。
-4. 不产生损坏的图片数据</t>
-        </is>
-      </c>
-      <c r="J455" s="8" t="inlineStr">
-        <is>
-          <t>验证图片上传的断点续传或失败回滚</t>
-        </is>
-      </c>
+      <c r="B455" s="16" t="n"/>
+      <c r="C455" s="16" t="n"/>
+      <c r="D455" s="16" t="n"/>
+      <c r="E455" s="16" t="n"/>
+      <c r="F455" s="16" t="n"/>
+      <c r="G455" s="16" t="n"/>
+      <c r="H455" s="16" t="n"/>
+      <c r="I455" s="16" t="n"/>
+      <c r="J455" s="17" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="8" t="inlineStr"/>
@@ -23717,7 +23707,6 @@
         </is>
       </c>
     </row>
-    <row r="526"/>
     <row r="527">
       <c r="A527" s="9" t="inlineStr">
         <is>
@@ -23734,7 +23723,6 @@
       <c r="I527" s="16" t="n"/>
       <c r="J527" s="17" t="n"/>
     </row>
-    <row r="528"/>
     <row r="529">
       <c r="A529" s="18" t="inlineStr">
         <is>
@@ -24891,51 +24879,15 @@
     </row>
     <row r="552">
       <c r="A552" s="8" t="inlineStr"/>
-      <c r="B552" s="8" t="inlineStr"/>
-      <c r="C552" s="8" t="inlineStr">
-        <is>
-          <t>dypw-xcx-002</t>
-        </is>
-      </c>
-      <c r="D552" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E552" s="8" t="n"/>
-      <c r="F552" s="8" t="inlineStr">
-        <is>
-          <t>验证电影出票后取票码在小程序内展示和保存</t>
-        </is>
-      </c>
-      <c r="G552" s="8" t="inlineStr">
-        <is>
-          <t>1. 用户已购票成功
-2. 出票完成</t>
-        </is>
-      </c>
-      <c r="H552" s="8" t="inlineStr">
-        <is>
-          <t>1. 查看订单详情页的取票码/二维码。
-2. 调整手机亮度查看二维码清晰度。
-3. 长按二维码图片。
-4. 点击"保存到手机"（如有该功能）</t>
-        </is>
-      </c>
-      <c r="I552" s="8" t="inlineStr">
-        <is>
-          <t>1. 取票码数字清晰显示，字体大小合适。
-2. 二维码清晰可扫（影院扫码机能识别）。
-3. 小程序可调用wx.setScreenBrightness提高亮度。
-4. 长按二维码弹出保存选项（需相册授权）。
-5. 同时展示短信取票码文本</t>
-        </is>
-      </c>
-      <c r="J552" s="8" t="inlineStr">
-        <is>
-          <t>到影院后需要在小程序内展示取票码给机器扫</t>
-        </is>
-      </c>
+      <c r="B552" s="16" t="n"/>
+      <c r="C552" s="16" t="n"/>
+      <c r="D552" s="16" t="n"/>
+      <c r="E552" s="16" t="n"/>
+      <c r="F552" s="16" t="n"/>
+      <c r="G552" s="16" t="n"/>
+      <c r="H552" s="16" t="n"/>
+      <c r="I552" s="16" t="n"/>
+      <c r="J552" s="17" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="8" t="inlineStr"/>
@@ -25952,11 +25904,519 @@
         </is>
       </c>
     </row>
+    <row r="582"/>
+    <row r="584">
+      <c r="A584" s="23" t="inlineStr">
+        <is>
+          <t>═══ 复盘补漏 · 需求文档/测试策略交叉比对发现的遗漏点 ═══</t>
+        </is>
+      </c>
+      <c r="B584" s="24" t="n"/>
+      <c r="C584" s="24" t="n"/>
+      <c r="D584" s="24" t="n"/>
+      <c r="E584" s="24" t="n"/>
+      <c r="F584" s="24" t="n"/>
+      <c r="G584" s="24" t="n"/>
+      <c r="H584" s="24" t="n"/>
+      <c r="I584" s="24" t="n"/>
+      <c r="J584" s="24" t="n"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="25" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B585" s="25" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C585" s="25" t="inlineStr">
+        <is>
+          <t>mfzl-bl-001</t>
+        </is>
+      </c>
+      <c r="D585" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E585" s="25" t="inlineStr">
+        <is>
+          <t>免费资料区
+(复盘补漏)</t>
+        </is>
+      </c>
+      <c r="F585" s="25" t="inlineStr">
+        <is>
+          <t>验证快速切换分类Tab时数据请求无竞态条件</t>
+        </is>
+      </c>
+      <c r="G585" s="25" t="inlineStr">
+        <is>
+          <t>1. 免费资料区已配置3个分类
+2. 每个分类各有数据</t>
+        </is>
+      </c>
+      <c r="H585" s="25" t="inlineStr">
+        <is>
+          <t>1. 快速连续点击"学习资料"→"工具模板"→"行业报告"→"全部"，每次间隔&lt;0.5秒。
+2. 最终停留在"全部"分类。
+3. 检查列表数据</t>
+        </is>
+      </c>
+      <c r="I585" s="25" t="inlineStr">
+        <is>
+          <t>1. 列表最终显示"全部"分类数据。
+2. 不出现"工具模板"分类的数据残留在"全部"列表中。
+3. 不出现数据闪烁或重叠。
+4. 无JS报错</t>
+        </is>
+      </c>
+      <c r="J585" s="25" t="inlineStr">
+        <is>
+          <t>需求2.1.4测试关注点：快速切换Tab竞态条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="25" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B586" s="25" t="inlineStr"/>
+      <c r="C586" s="25" t="inlineStr">
+        <is>
+          <t>wamtyj-bl-001</t>
+        </is>
+      </c>
+      <c r="D586" s="25" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E586" s="25" t="inlineStr">
+        <is>
+          <t>外卖区-通用券
+(复盘补漏)</t>
+        </is>
+      </c>
+      <c r="F586" s="25" t="inlineStr">
+        <is>
+          <t>验证订单详情页"再次购买"按钮功能</t>
+        </is>
+      </c>
+      <c r="G586" s="25" t="inlineStr">
+        <is>
+          <t>1. 用户已购买过10元通用券
+2. 进入该订单详情页</t>
+        </is>
+      </c>
+      <c r="H586" s="25" t="inlineStr">
+        <is>
+          <t>1. 查看订单详情页。
+2. 点击"再次购买"按钮。
+3. 检查跳转页面</t>
+        </is>
+      </c>
+      <c r="I586" s="25" t="inlineStr">
+        <is>
+          <t>1. "再次购买"按钮可见。
+2. 点击后跳转到该商品的购买页面。
+3. 面额默认选中上次购买的面额（10元）。
+4. 可正常发起新的购买</t>
+        </is>
+      </c>
+      <c r="J586" s="25" t="inlineStr">
+        <is>
+          <t>需求2.2.2：订单详情页操作按钮包含再次购买</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="25" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B587" s="25" t="inlineStr"/>
+      <c r="C587" s="25" t="inlineStr">
+        <is>
+          <t>cyzkrg-bl-001</t>
+        </is>
+      </c>
+      <c r="D587" s="25" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E587" s="25" t="inlineStr">
+        <is>
+          <t>餐饮折扣-人工辅助
+(复盘补漏)</t>
+        </is>
+      </c>
+      <c r="F587" s="25" t="inlineStr">
+        <is>
+          <t>验证同名商家是否允许重复录入</t>
+        </is>
+      </c>
+      <c r="G587" s="25" t="inlineStr">
+        <is>
+          <t>1. 已录入一个商家"张三烤肉店"</t>
+        </is>
+      </c>
+      <c r="H587" s="25" t="inlineStr">
+        <is>
+          <t>1. 再次录入一个同名商家"张三烤肉店"（不同地址）。
+2. 提交审核。
+3. 检查结果</t>
+        </is>
+      </c>
+      <c r="I587" s="25" t="inlineStr">
+        <is>
+          <t>1. 允许录入（不同门店可能同名）并提交成功。
+2. 或系统提示"已存在同名商家，是否继续？"。
+3. 列表中两个同名商家可通过地址区分</t>
+        </is>
+      </c>
+      <c r="J587" s="25" t="inlineStr">
+        <is>
+          <t>需求2.3.3测试关注点：同名商家重复录入</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="25" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B588" s="25" t="inlineStr"/>
+      <c r="C588" s="25" t="inlineStr">
+        <is>
+          <t>dcfw-bl-001</t>
+        </is>
+      </c>
+      <c r="D588" s="25" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E588" s="25" t="inlineStr">
+        <is>
+          <t>打车服务
+(复盘补漏)</t>
+        </is>
+      </c>
+      <c r="F588" s="25" t="inlineStr">
+        <is>
+          <t>验证定位不精确时支持手动修改起点地址</t>
+        </is>
+      </c>
+      <c r="G588" s="25" t="inlineStr">
+        <is>
+          <t>1. 用户已授权位置并完成定位
+2. 定位结果与实际位置有偏差</t>
+        </is>
+      </c>
+      <c r="H588" s="25" t="inlineStr">
+        <is>
+          <t>1. 查看当前定位地址。
+2. 点击起点地址栏进行修改。
+3. 输入正确地址或在地图上重新选点。
+4. 确认新起点</t>
+        </is>
+      </c>
+      <c r="I588" s="25" t="inlineStr">
+        <is>
+          <t>1. 起点地址栏可点击编辑。
+2. 支持输入文字搜索地址（联想补全）。
+3. 修改后起点更新为新地址。
+4. 跳转第三方打车时使用修改后的地址</t>
+        </is>
+      </c>
+      <c r="J588" s="25" t="inlineStr">
+        <is>
+          <t>需求2.4：定位不精确支持手动修改起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="25" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B589" s="25" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="C589" s="25" t="inlineStr">
+        <is>
+          <t>dypw-bl-001</t>
+        </is>
+      </c>
+      <c r="D589" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E589" s="25" t="inlineStr">
+        <is>
+          <t>电影票务
+(复盘补漏)</t>
+        </is>
+      </c>
+      <c r="F589" s="25" t="inlineStr">
+        <is>
+          <t>验证选座最多4座限制及取消已选座位</t>
+        </is>
+      </c>
+      <c r="G589" s="25" t="inlineStr">
+        <is>
+          <t>1. 用户在选座页面
+2. 有多个可选座位</t>
+        </is>
+      </c>
+      <c r="H589" s="25" t="inlineStr">
+        <is>
+          <t>1. 依次选择4个座位，每选一个观察已选列表。
+2. 尝试选第5个座位。
+3. 取消其中1个已选座位。
+4. 再选一个新座位</t>
+        </is>
+      </c>
+      <c r="I589" s="25" t="inlineStr">
+        <is>
+          <t>1. 选择4座后已选列表显示4个座位号。
+2. 选第5个时提示"最多可选4个座位"。
+3. 点击已选座位可取消（高亮恢复为绿色可选）。
+4. 取消后可重新选择新座位</t>
+        </is>
+      </c>
+      <c r="J589" s="25" t="inlineStr">
+        <is>
+          <t>需求2.5：最多4座限制+取消已选座位交互</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="8" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B590" s="8" t="inlineStr"/>
+      <c r="C590" s="8" t="inlineStr">
+        <is>
+          <t>dypw-bl-002</t>
+        </is>
+      </c>
+      <c r="D590" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E590" s="8" t="n"/>
+      <c r="F590" s="8" t="inlineStr">
+        <is>
+          <t>验证已过开场时间的场次不可购买</t>
+        </is>
+      </c>
+      <c r="G590" s="8" t="inlineStr">
+        <is>
+          <t>1. 某影片有一个已过开场时间的场次（如开场时间14:00，当前15:00）</t>
+        </is>
+      </c>
+      <c r="H590" s="8" t="inlineStr">
+        <is>
+          <t>1. 查看该影片的场次列表。
+2. 观察已过开场时间的场次展示。
+3. 尝试点击该场次</t>
+        </is>
+      </c>
+      <c r="I590" s="8" t="inlineStr">
+        <is>
+          <t>1. 已过场次显示为灰色/置灰状态。
+2. 标注"已过期"或"已开场"。
+3. 点击后无法进入选座页面，或提示"该场次已开场"</t>
+        </is>
+      </c>
+      <c r="J590" s="8" t="inlineStr">
+        <is>
+          <t>需求2.5测试关注点：场次已过开场时间的处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="25" t="inlineStr">
+        <is>
+          <t>商家端</t>
+        </is>
+      </c>
+      <c r="B591" s="25" t="inlineStr"/>
+      <c r="C591" s="25" t="inlineStr">
+        <is>
+          <t>sjmd-bl-001</t>
+        </is>
+      </c>
+      <c r="D591" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E591" s="25" t="inlineStr">
+        <is>
+          <t>商家端-数据统计
+(复盘补漏)</t>
+        </is>
+      </c>
+      <c r="F591" s="25" t="inlineStr">
+        <is>
+          <t>验证今日流水/本月流水统计的时间起止点（0:00-23:59）</t>
+        </is>
+      </c>
+      <c r="G591" s="25" t="inlineStr">
+        <is>
+          <t>1. 商家端已登录
+2. 有跨日期的订单数据（如23:58下单和00:02下单）</t>
+        </is>
+      </c>
+      <c r="H591" s="25" t="inlineStr">
+        <is>
+          <t>1. 查看"今日流水"数据。
+2. 确认23:58的订单是否计入今日。
+3. 确认00:02的订单是否计入今日（次日查看时）。
+4. 查看"本月流水"，确认月初和月末边界</t>
+        </is>
+      </c>
+      <c r="I591" s="25" t="inlineStr">
+        <is>
+          <t>1. 今日统计范围：当日00:00:00至23:59:59。
+2. 23:58的订单计入当日。
+3. 00:02的订单计入次日。
+4. 本月统计：当月1日00:00至当月最后一日23:59:59</t>
+        </is>
+      </c>
+      <c r="J591" s="25" t="inlineStr">
+        <is>
+          <t>需求3.4测试关注点：统计时间起止点</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="25" t="inlineStr">
+        <is>
+          <t>管理后台</t>
+        </is>
+      </c>
+      <c r="B592" s="25" t="inlineStr"/>
+      <c r="C592" s="25" t="inlineStr">
+        <is>
+          <t>fyxt-bl-001</t>
+        </is>
+      </c>
+      <c r="D592" s="25" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E592" s="25" t="inlineStr">
+        <is>
+          <t>分佣系统
+(复盘补漏)</t>
+        </is>
+      </c>
+      <c r="F592" s="25" t="inlineStr">
+        <is>
+          <t>验证利润为0（实付=成本）时所有角色佣金均为0</t>
+        </is>
+      </c>
+      <c r="G592" s="25" t="inlineStr">
+        <is>
+          <t>1. 后台已配置平台50%/代理商50%
+2. 有一级分销员10%</t>
+        </is>
+      </c>
+      <c r="H592" s="25" t="inlineStr">
+        <is>
+          <t>1. 创建一笔订单：实付金额50元，投入成本50元。
+2. 支付完成后查看分佣明细</t>
+        </is>
+      </c>
+      <c r="I592" s="25" t="inlineStr">
+        <is>
+          <t>1. 利润=50-50=0元。
+2. 平台佣金=0×50%=0.00元。
+3. 代理商佣金=0×50%=0.00元。
+4. 一级分销员佣金=0×10%=0.00元。
+5. 所有角色佣金均为0.00元，分佣记录正常生成但金额为0</t>
+        </is>
+      </c>
+      <c r="J592" s="25" t="inlineStr">
+        <is>
+          <t>需求4.5.8分佣边界：利润为0所有人佣金为0</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="8" t="inlineStr">
+        <is>
+          <t>管理后台</t>
+        </is>
+      </c>
+      <c r="B593" s="8" t="inlineStr"/>
+      <c r="C593" s="8" t="inlineStr">
+        <is>
+          <t>fyxt-bl-002</t>
+        </is>
+      </c>
+      <c r="D593" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E593" s="8" t="n"/>
+      <c r="F593" s="8" t="inlineStr">
+        <is>
+          <t>验证利润为负（投入&gt;实付）时后端校验拦截</t>
+        </is>
+      </c>
+      <c r="G593" s="8" t="inlineStr">
+        <is>
+          <t>1. 管理后台已登录</t>
+        </is>
+      </c>
+      <c r="H593" s="8" t="inlineStr">
+        <is>
+          <t>1. 尝试在后台创建/配置一个商品：售价30元，成本50元。
+2. 保存商品配置。
+3. 如果保存成功，用户下单该商品后查看分佣</t>
+        </is>
+      </c>
+      <c r="I593" s="8" t="inlineStr">
+        <is>
+          <t>1. 后端校验拦截：提示"售价不能低于成本"或"利润不能为负"。
+2. 不允许保存该配置。
+3. 如果系统允许（异常情况），分佣计算不应产生负数佣金</t>
+        </is>
+      </c>
+      <c r="J593" s="8" t="inlineStr">
+        <is>
+          <t>需求4.5.8：利润为负不应出现，需后端校验拦截</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J453"/>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="E67:E90"/>
     <mergeCell ref="A552:J552"/>
+    <mergeCell ref="A584:J584"/>
     <mergeCell ref="E20:E37"/>
     <mergeCell ref="E38:E56"/>
     <mergeCell ref="A582:J582"/>
@@ -27291,7 +27751,7 @@
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>563</v>
+        <v>572</v>
       </c>
     </row>
     <row r="74">
